--- a/data/ships.xlsx
+++ b/data/ships.xlsx
@@ -3883,7 +3883,7 @@
         <v>30</v>
       </c>
       <c r="G2">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="H2">
         <v>0.65</v>
@@ -3892,11 +3892,11 @@
         <v>0.18</v>
       </c>
       <c r="J2">
+        <v>3.7</v>
+      </c>
+      <c r="K2">
         <v>2</v>
       </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
       <c r="L2">
         <v>1</v>
       </c>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A raft with a mast and one gun. She floats, she fires, and she is yours.</t>
+          <t xml:space="preserve">A raft with a mast and two guns a side. She floats, she fires, and she is yours.</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -4019,10 +4019,10 @@
         <v>40</v>
       </c>
       <c r="AU2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -5320,7 +5320,7 @@
         <v>3</v>
       </c>
       <c r="AH10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heavy frigate</t>
+          <t xml:space="preserve">Frigate heavy</t>
         </is>
       </c>
       <c r="D13">
@@ -11638,7 +11638,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heavy frigate</t>
+          <t xml:space="preserve">Frigate heavy</t>
         </is>
       </c>
       <c r="D52">

--- a/data/ships.xlsx
+++ b/data/ships.xlsx
@@ -4891,7 +4891,7 @@
         <v>180</v>
       </c>
       <c r="G8">
-        <v>0.97</v>
+        <v>1.015</v>
       </c>
       <c r="H8">
         <v>1.07</v>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowsprit/small/headsails fore/medium/lateen main/medium/lateen</t>
+          <t xml:space="preserve">bowsprit/small/headsails fore/small/lateen main/small/lateen</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">

--- a/data/ships.xlsx
+++ b/data/ships.xlsx
@@ -582,1314 +582,1377 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowsprit    yes or no. Whether she carries the spar at all.</t>
+          <t xml:space="preserve">            A fourth figure is the fewest sails a mast stepped there must carry: "fore/large/square/2"</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">blurb       one line a captain reads. May be left empty.</t>
+          <t xml:space="preserve">            takes a topmast or taller and never a bare lower mast. Size alone cannot say it, since</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            a lower mast and a topmast are both medium. Leave it off and any mast that fits goes in.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">A BLANK IN speed, hand, canvas OR tons IS NOT A DERIVATION. Each falls back to 1, which describes</t>
+          <t xml:space="preserve">bowsprit    yes or no. Whether she carries the spar at all.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">a quick, handy, easily driven ship that can carry nothing, and is right for no class above a boat.</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fill them in. Every other gameplay column has to be filled as well.</t>
+          <t xml:space="preserve">blurb       one line a captain reads. May be left empty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A BLANK IN speed, hand, canvas OR tons IS NOT A DERIVATION. Each falls back to 1, which describes</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">THE REFERENCE COLUMNS. Everything from `era` rightward is what the class WAS rather than what she</t>
+          <t xml:space="preserve">a quick, handy, easily driven ship that can carry nothing, and is right for no class above a boat.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">does in a fight: no fight reads any of it, `npm run import` writes it to src/shipref.js, and</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">`hullform.js` is the one reader. The fourteen marked (drawn) are how she is DRAWN, in the menu</t>
+          <t xml:space="preserve">Fill them in. Every other gameplay column has to be filled as well.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">model and at sea. The rest are recorded for whoever comes to refine her form and are read by</t>
+          <t xml:space="preserve">THE REFERENCE COLUMNS. Everything from `era` rightward is what the class WAS rather than what she</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">nothing yet, which is not the same as being free to invent: a wrong figure here is a wrong hull</t>
+          <t xml:space="preserve">does in a fight: no fight reads any of it, `npm run import` writes it to src/shipref.js, and</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">the day somebody does read it.</t>
+          <t xml:space="preserve">`hullform.js` is the one reader. The fourteen marked (drawn) are how she is DRAWN, in the menu</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">model and at sea. The rest are recorded for whoever comes to refine her form and are read by</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lengths are feet and weights are tons. bowFine, tumblehome, deadrise, sheer and castle are 1 to 5</t>
+          <t xml:space="preserve">nothing yet, which is not the same as being free to invent: a wrong figure here is a wrong hull</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">judgement scores, 1 for least and 5 for most.</t>
+          <t xml:space="preserve">the day somebody does read it.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">era         the years she was in service, written as a range. Text rather than a number.</t>
+          <t xml:space="preserve">Lengths are feet and weights are tons. bowFine, tumblehome, deadrise, sheer and castle are 1 to 5</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">region      where she was built and sailed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">role        what she was for.</t>
+          <t xml:space="preserve">judgement scores, 1 for least and 5 for most.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve">lod         (drawn) length on deck, feet. With beam, how big she is drawn in both views. Sizes are</t>
+          <t xml:space="preserve">era         the years she was in service, written as a range. Text rather than a number.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">            compressed around the galleon, so twice the length is not twice the ship on screen.</t>
+          <t xml:space="preserve">region      where she was built and sailed.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">lbp         length between perpendiculars, feet. The measured length, shorter than on deck.</t>
+          <t xml:space="preserve">role        what she was for.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">beam        (drawn) extreme breadth, feet. Her drawn width, and with her length her collision</t>
+          <t xml:space="preserve">lod         (drawn) length on deck, feet. With beam, how big she is drawn in both views. Sizes are</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">            ellipse in a fight.</t>
+          <t xml:space="preserve">            compressed around the galleon, so twice the length is not twice the ship on screen.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">draft       how deep she floats, feet.</t>
+          <t xml:space="preserve">lbp         length between perpendiculars, feet. The measured length, shorter than on deck.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">depth       depth of hold, feet: keelson to the deck above it.</t>
+          <t xml:space="preserve">beam        (drawn) extreme breadth, feet. Her drawn width, and with her length her collision</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">freeboard   (drawn) height of side above the water amidships, feet. The depth of side in the model.</t>
+          <t xml:space="preserve">            ellipse in a fight.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">lb          length to beam, as a ratio. High is long and lean, low is short and beamy.</t>
+          <t xml:space="preserve">depth       depth of hold, feet: keelson to the deck above it.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd          beam to depth, as a ratio. High is shallow and beamy, low is deep and narrow.</t>
+          <t xml:space="preserve">freeboard   (drawn) height of side above the water amidships, feet. The depth of side in the model.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">burthen     builder's old measurement tons: what she was rated to carry.</t>
+          <t xml:space="preserve">lb          length to beam, as a ratio. High is long and lean, low is short and beamy.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">disp        displacement, tons: what she actually weighs afloat.</t>
+          <t xml:space="preserve">bd          beam to depth, as a ratio. High is shallow and beamy, low is deep and narrow.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowFine     (drawn) how fine her entry is. 5 is a clipper's bow and 1 a carrack's. It narrows her</t>
+          <t xml:space="preserve">burthen     builder's old measurement tons: what she was rated to carry.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">            bow and pulls her shoulders aft.</t>
+          <t xml:space="preserve">disp        displacement, tons: what she actually weighs afloat.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">tumblehome  (drawn) how far her sides roll inward above the waterline. 5 is a fluyt.</t>
+          <t xml:space="preserve">bowFine     (drawn) how fine her entry is. 5 is a clipper's bow and 1 a carrack's. It narrows her</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">deadrise    how sharply her bottom rises from the keel. 1 is a flat floor.</t>
+          <t xml:space="preserve">            bow and pulls her shoulders aft.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">sheer       (drawn) how much her deck sweeps up towards bow and stern.</t>
+          <t xml:space="preserve">tumblehome  (drawn) how far her sides roll inward above the waterline. 5 is a fluyt.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">castle      (drawn) how built up her ends are. 1 is an open boat, 2 raises a quarterdeck, 3 and up</t>
+          <t xml:space="preserve">deadrise    how sharply her bottom rises from the keel. 1 is a flat floor.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">            add a forecastle. It is also what a windowed stern needs before it shows any lights.</t>
+          <t xml:space="preserve">sheer       (drawn) how much her deck sweeps up towards bow and stern.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">stern       (drawn) the shape of her stern, as one of the named types. Scow, Round, Pear,</t>
+          <t xml:space="preserve">castle      (drawn) how built up her ends are. 1 is an open boat, 2 raises a quarterdeck, 3 and up</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Elliptical, Raking transom, Overhanging and Square each have geometry of their own,</t>
+          <t xml:space="preserve">            add a forecastle. It is also what a windowed stern needs before it shows any lights.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">            and any other name draws a plain transom, which is what Transom and Gallery do. A name</t>
+          <t xml:space="preserve">stern       (drawn) the shape of her stern, as one of the named types. Scow, Round, Pear,</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">            holding "gallery" or "castle" lights her stern windows if her castle is 3 or more.</t>
+          <t xml:space="preserve">            Elliptical, Raking transom, Overhanging and Square each have geometry of their own,</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">mastHeight  (drawn) how tall her rig stands, as a multiple of the galleon's. Scales her masts in</t>
+          <t xml:space="preserve">            and any other name draws a plain transom, which is what Transom and Gallery do. A name</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">            both views.</t>
+          <t xml:space="preserve">            holding "gallery" or "castle" lights her stern windows if her castle is 3 or more.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">decks       how many of her decks carry guns: 1, 1-2, 2, 2-3 or 3. Text, because a range is not a</t>
+          <t xml:space="preserve">mastHeight  (drawn) how tall her rig stands, as a multiple of the galleon's. Scales her masts in</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">            number. Recorded description now: `battery` says deck by deck where her guns actually</t>
+          <t xml:space="preserve">            both views.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">            stood, and that is what her ports are drawn from.</t>
+          <t xml:space="preserve">decks       how many of her decks carry guns: 1, 1-2, 2, 2-3 or 3. Text, because a range is not a</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">wale        the thickness of her main wale, inches: the heavy belt of timber along her side.</t>
+          <t xml:space="preserve">            number. Recorded description now: `battery` says deck by deck where her guns actually</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">topside     the thickness of her topside planking, inches.</t>
+          <t xml:space="preserve">            stood, and that is what her ports are drawn from.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">roomSpace   (drawn) room and space, feet: from one frame to the next. A gunport was framed on it,</t>
+          <t xml:space="preserve">wale        the thickness of her main wale, inches: the heavy belt of timber along her side.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">            running a little over one space wide, so this is the size of every port she shows.</t>
+          <t xml:space="preserve">topside     the thickness of her topside planking, inches.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">species     (drawn) what she was built of, which is also her colour: Oak, Live oak, Teak, Cedar or</t>
+          <t xml:space="preserve">roomSpace   (drawn) room and space, feet: from one frame to the next. A gunport was framed on it,</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Pine. Any other name is painted as oak.</t>
+          <t xml:space="preserve">            running a little over one space wide, so this is the size of every port she shows.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">timber      (drawn) how dense that timber is, oak being 1. Denser timber reads a little darker.</t>
+          <t xml:space="preserve">species     (drawn) what she was built of, which is also her colour: Oak, Live oak, Teak, Cedar or</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">crewMin     the fewest hands she could be worked with, as against the battle complement in `crew`.</t>
+          <t xml:space="preserve">            Pine. Any other name is painted as oak.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">cruise      her everyday speed, knots.</t>
+          <t xml:space="preserve">timber      (drawn) how dense that timber is, oak being 1. Denser timber reads a little darker.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve">topSpeed    the best she was ever driven, knots.</t>
+          <t xml:space="preserve">crewMin     the fewest hands she could be worked with, as against the battle complement in `crew`.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t xml:space="preserve">manoeuvre   how handy she was, 0 to 100. The reference's own score, and what `hand` came out of.</t>
+          <t xml:space="preserve">cruise      her everyday speed, knots.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t xml:space="preserve">histGuns    (drawn) how many guns she really carried, of every sort. Half of them is exactly her</t>
+          <t xml:space="preserve">topSpeed    the best she was ever driven, knots.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t xml:space="preserve">            `broadside` bearing for every class in the fleet, which is how the ports and the guns</t>
+          <t xml:space="preserve">manoeuvre   how handy she was, 0 to 100. The reference's own score, and what `hand` came out of.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t xml:space="preserve">            that fire out of them agree without the catalogue and the reference ever meeting.</t>
+          <t xml:space="preserve">histGuns    (drawn) how many guns she really carried, of every sort. Half of them is exactly her</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t xml:space="preserve">            `battery` says where those guns stood and has to add up to this.</t>
+          <t xml:space="preserve">            `broadside` bearing for every class in the fleet, which is how the ports and the guns</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery     (drawn) her establishment, deck by deck, as guns aboard rather than a side. Gun decks</t>
+          <t xml:space="preserve">            that fire out of them agree without the catalogue and the reference ever meeting.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t xml:space="preserve">            first and lowest deck first, then what she carried on her upper works after a plus:</t>
+          <t xml:space="preserve">            `battery` says where those guns stood and has to add up to this.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t xml:space="preserve">            "10" is a cutter's ten on one open deck, "28+8/2" a frigate with a gun deck of 28 and</t>
+          <t xml:space="preserve">battery     (drawn) her establishment, deck by deck, as guns aboard rather than a side. Gun decks</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t xml:space="preserve">            ten more on her quarterdeck and forecastle, "28/28/30+12/2" a first rate. The figures</t>
+          <t xml:space="preserve">            first and lowest deck first, then what she carried on her upper works after a plus:</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t xml:space="preserve">            sum to histGuns and every gun deck takes an even number, half of them a side.</t>
+          <t xml:space="preserve">            "10" is a cutter's ten on one open deck, "28+8/2" a frigate with a gun deck of 28 and</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t xml:space="preserve">            A GUN DECK AND AN UPPER WORKS ARE NOT THE SAME FITTING, which is the whole reason this</t>
+          <t xml:space="preserve">            ten more on her quarterdeck and forecastle, "28/28/28+12/4" a first rate. The figures</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t xml:space="preserve">            column exists. A gun deck is a continuous battery pierced through her side, so its</t>
+          <t xml:space="preserve">            sum to histGuns and every gun deck takes an even number, half of them a side.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t xml:space="preserve">            ports run the length of her, under the castles the way a lower deck really did. Her</t>
+          <t xml:space="preserve">            A GUN DECK AND AN UPPER WORKS ARE NOT THE SAME FITTING, which is the whole reason this</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t xml:space="preserve">            quarterdeck and forecastle guns stood in the open behind a bulwark, with no lidded</t>
+          <t xml:space="preserve">            column exists. A gun deck is a continuous battery pierced through her side, so its</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t xml:space="preserve">            port to show, and drawn as such they are what leaves a two-decker's waist empty.</t>
+          <t xml:space="preserve">            ports run the length of her, under the castles the way a lower deck really did. Her</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t xml:space="preserve">            After the plus, two figures are the quarterdeck and the forecastle in that order, with</t>
+          <t xml:space="preserve">            quarterdeck and forecastle guns stood in the open behind a bulwark, with no lidded</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t xml:space="preserve">            her waist bare between them. One figure is a battery that ran the whole length of her</t>
+          <t xml:space="preserve">            port to show, and drawn as such they are what leaves a two-decker's waist empty.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t xml:space="preserve">            upper works, which is what a spar-decked heavy frigate had. Write "2/0" rather than</t>
+          <t xml:space="preserve">            After the plus, two figures are the quarterdeck and the forecastle in that order, with</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t xml:space="preserve">            "2" for a ship who carried hers aft only.</t>
+          <t xml:space="preserve">            her waist bare between them. One figure is a battery that ran the whole length of her</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t xml:space="preserve">            A BOAT IS NOT PIERCED AT ALL. A lidded port is cut through her topside under the deck</t>
+          <t xml:space="preserve">            upper works, which is what a spar-decked heavy frigate had. Write "2/0" rather than</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t xml:space="preserve">            above it, and a hull with a castle score of 1 has neither, so her whole battery is</t>
+          <t xml:space="preserve">            "2" for a ship who carried hers aft only.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t xml:space="preserve">            drawn standing at her rail however this column is written.</t>
+          <t xml:space="preserve">            A BOAT IS NOT PIERCED AT ALL. A lidded port is cut through her topside under the deck</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            above it, and a hull with a castle score of 1 has neither, so her whole battery is</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Masts, from data/masts.tsv</t>
+          <t xml:space="preserve">            drawn standing at her rail however this column is written.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">drawnLength (drawn) the length of her BESPOKE 3D model, in metres, stem to stern at the rail, and</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t xml:space="preserve">THE MASTS. One row per type, and a type is a SHAPE OF RIG, not a size.</t>
+          <t xml:space="preserve">drawnBeam   (drawn) its extreme beam. Only a class with a model of her own in</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edit here, then: npm run import &amp;&amp; npm run catalogue</t>
+          <t xml:space="preserve">            src/render3d/bespoke/ carries them; everybody else leaves both blank and is drawn from</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            the figures above. Her collision ellipse at sea keeps the length the fleet's</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t xml:space="preserve">A mast's berths are fixed the moment it is built and never change. That is the whole point of the</t>
+          <t xml:space="preserve">            compression gives her and takes its beam from these two in proportion, so a ball bites</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t xml:space="preserve">part: buying a mast is choosing what she will be able to carry, so a mast with one lugsail berth</t>
+          <t xml:space="preserve">            where her planking is drawn and not outside it. The bespoke test holds them to the</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t xml:space="preserve">will never carry two square ones however much a captain spends. It is why the fleet wants a type</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t xml:space="preserve">per configuration rather than one mast with a number of slots.</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A TYPE IS NOT TIED TO A STATION. A mast that carries three square sails is that mast wherever she</t>
+          <t xml:space="preserve">            model's own figures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Masts, from data/masts.tsv</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t xml:space="preserve">steps it, so the fore and main of a brig are one part bought twice rather than two parts. What</t>
+          <t xml:space="preserve">THE MASTS. One row per type, and a type is a SHAPE OF RIG, not a size.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t xml:space="preserve">decides where it can go is the size rung and nothing else.</t>
+          <t xml:space="preserve">Edit here, then: npm run import &amp;&amp; npm run catalogue</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t xml:space="preserve">BERTHS RUN DECK UPWARD, and a fore-and-aft driving sail sharing the lowest level with a course</t>
+          <t xml:space="preserve">A mast's berths are fixed the moment it is built and never change. That is the whole point of the</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t xml:space="preserve">takes berth 0 with the square canvas above it. A spanker and a course are both set at the deck, one</t>
+          <t xml:space="preserve">part: buying a mast is choosing what she will be able to carry, so a mast with one lugsail berth</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t xml:space="preserve">abaft the mast and one on a yard across it, and the model has one sail to a band: putting the</t>
+          <t xml:space="preserve">will never carry two square ones however much a captain spends. It is why the fleet wants a type</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t xml:space="preserve">spanker lowest is what keeps a brig's rig reading bottom to top the way she is really rigged.</t>
+          <t xml:space="preserve">per configuration rather than one mast with a number of slots.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t xml:space="preserve">id       short camelCase name, unique.</t>
+          <t xml:space="preserve">A TYPE IS NOT TIED TO A STATION. A mast that carries three square sails is that mast wherever she</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t xml:space="preserve">name     what a captain reads.</t>
+          <t xml:space="preserve">steps it, so the fore and main of a brig are one part bought twice rather than two parts. What</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t xml:space="preserve">price    coins.</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t xml:space="preserve">size     the SMALLEST socket it fits. A mast also fits any larger socket, which is a legal poor</t>
+          <t xml:space="preserve">decides where it can go is the size rung and nothing else.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t xml:space="preserve">         choice rather than an error: sizes are boat, small, medium, large, heavy.</t>
+          <t xml:space="preserve">BERTHS RUN DECK UPWARD, and a fore-and-aft driving sail sharing the lowest level with a course</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t xml:space="preserve">spar     yes for a SPAR rather than a mast: a jibboom or a spritsail yard, which goes on the</t>
+          <t xml:space="preserve">takes berth 0 with the square canvas above it. A spanker and a course are both set at the deck, one</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t xml:space="preserve">         bowsprit and nowhere else. A spar and a mast are different sorts of thing and are</t>
+          <t xml:space="preserve">abaft the mast and one on a yard across it, and the model has one sail to a band: putting the</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t xml:space="preserve">         matched as such, or a jibboom would be legal as somebody's main mast.</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t xml:space="preserve">family   the shape of rig this mast is, and a hull's socket says which families it takes, so a</t>
+          <t xml:space="preserve">spanker lowest is what keeps a brig's rig reading bottom to top the way she is really rigged.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t xml:space="preserve">         lug mast never steps in a frigate and a topgallant mast never steps in a lugger. One</t>
+          <t xml:space="preserve">id       short camelCase name, unique.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t xml:space="preserve">         family to a mast, matched before the size rung is consulted:</t>
+          <t xml:space="preserve">name     what a captain reads.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t xml:space="preserve">           square     lower mast up to skysail mast, all square canvas: a ship's fore and main</t>
+          <t xml:space="preserve">price    coins.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t xml:space="preserve">           spanker    a fore-and-aft driver under square canvas: a ship's mizzen, a cutter's main</t>
+          <t xml:space="preserve">size     the SMALLEST socket it fits. A mast also fits any larger socket, which is a legal poor</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t xml:space="preserve">           schooner   gaff sail with a square topsail over it</t>
+          <t xml:space="preserve">         choice rather than an error: sizes are boat, small, medium, large, heavy.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t xml:space="preserve">           gaff       gaff mainsail and gaff topsail</t>
+          <t xml:space="preserve">spar     yes for a SPAR rather than a mast: a jibboom or a spritsail yard, which goes on the</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t xml:space="preserve">           bermuda    one tall triangle</t>
+          <t xml:space="preserve">         bowsprit and nowhere else. A spar and a mast are different sorts of thing and are</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t xml:space="preserve">           lateen     the lateen yard and the lateen mast</t>
+          <t xml:space="preserve">         matched as such, or a jibboom would be legal as somebody's main mast.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t xml:space="preserve">           lug        lug mast and lug topmast</t>
+          <t xml:space="preserve">family   the shape of rig this mast is, and a hull's socket says which families it takes, so a</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t xml:space="preserve">           boat       pole and sprit masts, what an open boat steps</t>
+          <t xml:space="preserve">         lug mast never steps in a frigate and a topgallant mast never steps in a lugger. One</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t xml:space="preserve">           headsails  the bowsprit spars that carry jibs and staysails</t>
+          <t xml:space="preserve">         family to a mast, matched before the size rung is consulted:</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t xml:space="preserve">           spritsail  the old headgear slung under the bowsprit, a carrack's and a galleon's</t>
+          <t xml:space="preserve">           square     lower mast up to skysail mast, all square canvas: a ship's fore and main</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t xml:space="preserve">         Studdingsails boom out from square and schooner rig only; the other families never</t>
+          <t xml:space="preserve">           spanker    a fore-and-aft driver under square canvas: a ship's mizzen, a cutter's main</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t xml:space="preserve">         carried the booms for them.</t>
+          <t xml:space="preserve">           schooner   gaff sail with a square topsail over it</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t xml:space="preserve">height   how tall she stands as a share of a full mast at her station, 0 to 1. The renderer cuts</t>
+          <t xml:space="preserve">           gaff       gaff mainsail and gaff topsail</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t xml:space="preserve">         the pole down to the canvas actually bent on it, so this is an upper bound, not a look.</t>
+          <t xml:space="preserve">           bermuda    one tall triangle</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t xml:space="preserve">berths   the sails she can carry, DECK UPWARD, as category labels separated by spaces.</t>
+          <t xml:space="preserve">           lateen     the lateen yard and the lateen mast</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t xml:space="preserve">         LSQ large square   SSQ small square   TRI headsail   LAT lateen   GAF gaff   LUG lugsail</t>
+          <t xml:space="preserve">           lug        lug mast and lug topmast</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t xml:space="preserve">         Five is the most the renderer can place up one mast in bands of their own, and the bench</t>
+          <t xml:space="preserve">           boat       pole and sprit masts, what an open boat steps</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t xml:space="preserve">         fails a mast that asks for more.</t>
+          <t xml:space="preserve">           headsails  the bowsprit spars that carry jibs and staysails</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t xml:space="preserve">         STU is a studdingsail and is NOT a berth. It booms out beyond a square sail already set,</t>
+          <t xml:space="preserve">           spritsail  the old headgear slung under the bowsprit, a carrack's and a galleon's</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t xml:space="preserve">         so it attaches to a sail rather than filling a place in the rig, and the bench refuses it.</t>
+          <t xml:space="preserve">         Studdingsails boom out from square and schooner rig only; the other families never</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t xml:space="preserve">blurb    one line a captain reads.</t>
+          <t xml:space="preserve">         carried the booms for them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">height   how tall she stands as a share of a full mast at her station, 0 to 1. The renderer cuts</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sails, from data/sails.tsv</t>
+          <t xml:space="preserve">         the pole down to the canvas actually bent on it, so this is an upper bound, not a look.</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">berths   the sails she can carry, DECK UPWARD, as category labels separated by spaces.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t xml:space="preserve">THE SAILS. One row per sail a captain can buy.</t>
+          <t xml:space="preserve">         LSQ large square   SSQ small square   TRI headsail   LAT lateen   GAF gaff   LUG lugsail</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edit here, then: npm run import &amp;&amp; npm run catalogue</t>
+          <t xml:space="preserve">         Five is the most the renderer can place up one mast in bands of their own, and the bench</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">         fails a mast that asks for more.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t xml:space="preserve">A sail belongs to ONE category and fits a berth of that category. That is the whole fitting rule.</t>
+          <t xml:space="preserve">         STU is a studdingsail and is NOT a berth. It booms out beyond a square sail already set,</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Area is not the category: a topgallant is nearly four times a skysail and both are SSQ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  LSQ  Large square    courses, lower topsails            driving power, low on the mast</t>
+          <t xml:space="preserve">         so it attaches to a sail rather than filling a place in the rig, and the bench refuses it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blurb    one line a captain reads.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t xml:space="preserve">  SSQ  Small square    topgallants, royals, skysails,     light-air lift, high up</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                       spritsails, sprit-topsails</t>
+          <t xml:space="preserve">Sails, from data/sails.tsv</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TRI  Headsail        jibs, flying jibs, staysails       set on a stay forward: balance, pointing</t>
+          <t xml:space="preserve">THE SAILS. One row per sail a captain can buy.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t xml:space="preserve">  LAT  Lateen          lateen yards, Bermuda mainsails    triangular canvas driving from a mast</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  GAF  Gaff            gaff mainsails, spankers,          fore-and-aft drive aft, manoeuvre</t>
+          <t xml:space="preserve">Edit here, then: npm run import &amp;&amp; npm run catalogue</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t xml:space="preserve">                       drivers, trysails, gaff topsails</t>
+          <t xml:space="preserve">A sail belongs to ONE category and fits a berth of that category. That is the whole fitting rule.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t xml:space="preserve">  LUG  Lugsail         dipping and standing lug,          the main drive of a lugger</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                       lug topsail</t>
+          <t xml:space="preserve">Area is not the category: a topgallant is nearly four times a skysail and both are SSQ.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STU  Studdingsail    boomed-out extensions             ADDITIVE. Not a berth: see below.</t>
+          <t xml:space="preserve">  LSQ  Large square    courses, lower topsails            driving power, low on the mast</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SSQ  Small square    topgallants, royals, skysails,     light-air lift, high up</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t xml:space="preserve">A LATEEN IS NOT A HEADSAIL. Both are triangles and they were one category until the bowsprit became</t>
+          <t xml:space="preserve">                       spritsails, sprit-topsails</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t xml:space="preserve">a station: the moment a jib had a berth of its own a lateen fitted it and pulled better, so the</t>
+          <t xml:space="preserve">  TRI  Headsail        jibs, flying jibs, staysails       set on a stay forward: balance, pointing</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t xml:space="preserve">choice made itself. They do different work, so they are different categories.</t>
+          <t xml:space="preserve">  LAT  Lateen          lateen yards, Bermuda mainsails    triangular canvas driving from a mast</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  GAF  Gaff            gaff mainsails, spankers,          fore-and-aft drive aft, manoeuvre</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t xml:space="preserve">STU does not go in a berth. A studdingsail booms out beyond a square sail that is already set and</t>
+          <t xml:space="preserve">                       drivers, trysails, gaff topsails</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t xml:space="preserve">its area comes off that sail, so it is an attachment rather than a place in the rig: a square sail</t>
+          <t xml:space="preserve">  LUG  Lugsail         dipping and standing lug,          the main drive of a lugger</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t xml:space="preserve">carries at most one, matched by LEVEL, and `npm run catalogue` still refuses a berth that asks for</t>
+          <t xml:space="preserve">                       lug topsail</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t xml:space="preserve">one, deliberately, so that a mast cannot pretend to carry studdingsails in a slot.</t>
+          <t xml:space="preserve">  STU  Studdingsail    boomed-out extensions             ADDITIVE. Not a berth: see below.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t xml:space="preserve">id      short camelCase name, unique.</t>
+          <t xml:space="preserve">A LATEEN IS NOT A HEADSAIL. Both are triangles and they were one category until the bowsprit became</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t xml:space="preserve">name    what a captain reads.</t>
+          <t xml:space="preserve">a station: the moment a jib had a berth of its own a lateen fitted it and pulled better, so the</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t xml:space="preserve">kind    one of the seven labels above.</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">price   coins.</t>
+          <t xml:space="preserve">choice made itself. They do different work, so they are different categories.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t xml:space="preserve">drive   what she pulls, as a share of a course's, which is why a course is exactly 1. Physical area</t>
+          <t xml:space="preserve">STU does not go in a berth. A studdingsail booms out beyond a square sail that is already set and</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t xml:space="preserve">        is where this number starts and the proportions are: course 1.00, lower topsail 0.70,</t>
+          <t xml:space="preserve">its area comes off that sail, so it is an attachment rather than a place in the rig: a square sail</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t xml:space="preserve">        topgallant 0.40, royal 0.22, skysail 0.12. Better cloth holds its shape and adds to it,</t>
+          <t xml:space="preserve">carries at most one, matched by LEVEL, and `npm run catalogue` still refuses a berth that asks for</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t xml:space="preserve">        which is why two sails of one area can differ here.</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        FOR A STUDDINGSAIL ONLY, drive is a share of the sail it booms out from (0.50 to 0.80),</t>
+          <t xml:space="preserve">one, deliberately, so that a mast cannot pretend to carry studdingsails in a slot.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t xml:space="preserve">        because its area comes off that sail rather than off a place in the rig.</t>
+          <t xml:space="preserve">id      short camelCase name, unique.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t xml:space="preserve">hand    what it does to her helm. Square canvas stiffens her, so it is negative; fore-and-aft</t>
+          <t xml:space="preserve">name    what a captain reads.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t xml:space="preserve">        canvas helps her round, so it is positive.</t>
+          <t xml:space="preserve">kind    one of the seven labels above.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t xml:space="preserve">level   STU only, and blank everywhere else. Which square sail up the mast it booms out from,</t>
+          <t xml:space="preserve">price   coins.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t xml:space="preserve">        counting square canvas from the deck: 0 is the lowest, a course; 1 the topsail over it;</t>
+          <t xml:space="preserve">drive   what she pulls, as a share of a course's, which is why a course is exactly 1. Physical area</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t xml:space="preserve">        2 the topgallant. The berth number is not the level, because a driver mast's course sits</t>
+          <t xml:space="preserve">        is where this number starts and the proportions are: course 1.00, lower topsail 0.70,</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t xml:space="preserve">        at berth 1 with a spanker under it.</t>
+          <t xml:space="preserve">        topgallant 0.40, royal 0.22, skysail 0.12. Better cloth holds its shape and adds to it,</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t xml:space="preserve">blurb   one line a captain reads.</t>
+          <t xml:space="preserve">        which is why two sails of one area can differ here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        FOR A STUDDINGSAIL ONLY, drive is a share of the sail it booms out from (0.50 to 0.80),</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Two grades of most of them: the plain one a captain can afford early, and a fine one in heavier</t>
+          <t xml:space="preserve">        because its area comes off that sail rather than off a place in the rig.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t xml:space="preserve">cloth that is strictly better and priced for it. Prices are placed against each other and have not</t>
+          <t xml:space="preserve">hand    what it does to her helm. Square canvas stiffens her, so it is negative; fore-and-aft</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t xml:space="preserve">been tuned against what a voyage actually pays.</t>
+          <t xml:space="preserve">        canvas helps her round, so it is positive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">level   STU only, and blank everywhere else. Which square sail up the mast it booms out from,</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guns, from data/guns.tsv</t>
+          <t xml:space="preserve">        counting square canvas from the deck: 0 is the lowest, a course; 1 the topsail over it;</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        2 the topgallant. The berth number is not the level, because a driver mast's course sits</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t xml:space="preserve">THE GUNS. One row per piece a captain can buy.</t>
+          <t xml:space="preserve">        at berth 1 with a spanker under it.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edit here, then: npm run import &amp;&amp; npm run catalogue</t>
+          <t xml:space="preserve">blurb   one line a captain reads.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guns fit BY THE PIECE up to what the hull bears, and `mount` says which of her counts a gun draws</t>
+          <t xml:space="preserve">Two grades of most of them: the plain one a captain can afford early, and a fine one in heavier</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t xml:space="preserve">against. Broadside is counted A SIDE and mirrored, because that is how a volley fires: one</t>
+          <t xml:space="preserve">cloth that is strictly better and priced for it. Prices are placed against each other and have not</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t xml:space="preserve">carriage gun bought is one gun each side and two guns aboard.</t>
+          <t xml:space="preserve">been tuned against what a voyage actually pays.</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Muskets are not in this table and never will be. Small arms come off the crew she musters, with the</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t xml:space="preserve">swivels on her rail firing in the same volley, which is `rate()`'s business.</t>
+          <t xml:space="preserve">Guns, from data/guns.tsv</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THE GUNS. One row per piece a captain can buy.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t xml:space="preserve">id      short camelCase name, unique.</t>
-        </is>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t xml:space="preserve">name    what a captain reads. A GUN IS NAMED BY THE WEIGHT OF HER BALL, IN NUMERALS: `32-pounder`,</t>
+          <t xml:space="preserve">Edit here, then: npm run import &amp;&amp; npm run catalogue</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t xml:space="preserve">        not `Thirty two pounder`. A captain reads this list to compare ten pieces, and comparing</t>
+          <t xml:space="preserve">Guns fit BY THE PIECE up to what the hull bears, and `mount` says which of her counts a gun draws</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t xml:space="preserve">        them is arithmetic she should not have to do in words. It is the game's own rule about</t>
+          <t xml:space="preserve">against. Broadside is counted A SIDE and mirrored, because that is how a volley fires: one</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t xml:space="preserve">        numerals, and a shelf of guns is where the cost of breaking it shows worst.</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mount   broadside, bow or swivel.</t>
+          <t xml:space="preserve">carriage gun bought is one gun each side and two guns aboard.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t xml:space="preserve">price   coins.</t>
+          <t xml:space="preserve">Muskets are not in this table and never will be. Small arms come off the crew she musters, with the</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t xml:space="preserve">damage  what one ball takes off a hull.</t>
-        </is>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reload  seconds between rounds. A mixed battery serves at the pace of its slowest piece.</t>
+          <t xml:space="preserve">swivels on her rail firing in the same volley, which is `rate()`'s business.</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t xml:space="preserve">weight  what she carries for it. Enough of it takes the edge off her handling, which is the reason</t>
+          <t xml:space="preserve">id      short camelCase name, unique.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t xml:space="preserve">        to leave a port empty.</t>
+          <t xml:space="preserve">name    what a captain reads. A GUN IS NAMED BY THE WEIGHT OF HER BALL, IN NUMERALS: `32-pounder`,</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t xml:space="preserve">group   swivels only, and blank everywhere else. How true one throws, as a share of a musket's own</t>
+          <t xml:space="preserve">        not `Thirty two pounder`. A captain reads this list to compare ten pieces, and comparing</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t xml:space="preserve">        scatter: 1 is no better than the hands beside it, and smaller is tighter. A better swivel</t>
+          <t xml:space="preserve">        them is arithmetic she should not have to do in words. It is the game's own rule about</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t xml:space="preserve">        never adds a ball to the volley; what quality buys is that the volley hits harder and lands</t>
+          <t xml:space="preserve">        numerals, and a shelf of guns is where the cost of breaking it shows worst.</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t xml:space="preserve">        closer to where the bow points, and this is the second half of that.</t>
+          <t xml:space="preserve">mount   broadside, bow or swivel.</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
+        <is>
+          <t xml:space="preserve">price   coins.</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">damage  what one ball takes off a hull.</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reload  seconds between rounds. A mixed battery serves at the pace of its slowest piece.</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weight  what she carries for it. Enough of it takes the edge off her handling, which is the reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        to leave a port empty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">group   swivels only, and blank everywhere else. How true one throws, as a share of a musket's own</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        scatter: 1 is no better than the hands beside it, and smaller is tighter. A better swivel</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        never adds a ball to the volley; what quality buys is that the volley hits harder and lands</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        closer to where the bow points, and this is the second half of that.</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
         <is>
           <t xml:space="preserve">blurb   one line a captain reads.</t>
         </is>
@@ -2234,7 +2297,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">where she can step one, "station/size/family", space separated, bow aft. stations: bowsprit fore main mizzen bonaventure sizes:    boat small medium large heavy families: the shapes of rig the socket takes, joined with a plus: "main/medium/gaff+spanker". A mast carries one family in masts.tsv and only a mast of one of these goes in, so a frigate's fore takes square rig and nothing else however small the mast. families: square spanker schooner gaff bermuda lateen lug boat headsails spritsail The bowsprit takes a SPAR rather than a mast, which is what her headsails hang on. A socket that names no family takes any mast of its size, which is how the laid-up rows stand; the bench asks every class that sails to say what she takes.</t>
+          <t xml:space="preserve">where she can step one, "station/size/family", space separated, bow aft. stations: bowsprit fore main mizzen bonaventure sizes:    boat small medium large heavy families: the shapes of rig the socket takes, joined with a plus: "main/medium/gaff+spanker". A mast carries one family in masts.tsv and only a mast of one of these goes in, so a frigate's fore takes square rig and nothing else however small the mast. families: square spanker schooner gaff bermuda lateen lug boat headsails spritsail The bowsprit takes a SPAR rather than a mast, which is what her headsails hang on. A socket that names no family takes any mast of its size, which is how the laid-up rows stand; the bench asks every class that sails to say what she takes. A fourth figure is the fewest sails a mast stepped there must carry: "fore/large/square/2" takes a topmast or taller and never a bare lower mast. Size alone cannot say it, since a lower mast and a topmast are both medium. Leave it off and any mast that fits goes in.</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2485,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">draft</t>
+          <t xml:space="preserve">depth</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2432,7 +2495,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">how deep she floats, feet.</t>
+          <t xml:space="preserve">depth of hold, feet: keelson to the deck above it.</t>
         </is>
       </c>
     </row>
@@ -2444,17 +2507,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">depth</t>
+          <t xml:space="preserve">freeboard</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recorded only</t>
+          <t xml:space="preserve">Her drawing</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">depth of hold, feet: keelson to the deck above it.</t>
+          <t xml:space="preserve">height of side above the water amidships, feet. The depth of side in the model.</t>
         </is>
       </c>
     </row>
@@ -2466,17 +2529,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">freeboard</t>
+          <t xml:space="preserve">lb</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Her drawing</t>
+          <t xml:space="preserve">Recorded only</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">height of side above the water amidships, feet. The depth of side in the model.</t>
+          <t xml:space="preserve">length to beam, as a ratio. High is long and lean, low is short and beamy.</t>
         </is>
       </c>
     </row>
@@ -2488,7 +2551,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">lb</t>
+          <t xml:space="preserve">bd</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2498,7 +2561,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">length to beam, as a ratio. High is long and lean, low is short and beamy.</t>
+          <t xml:space="preserve">beam to depth, as a ratio. High is shallow and beamy, low is deep and narrow.</t>
         </is>
       </c>
     </row>
@@ -2510,7 +2573,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd</t>
+          <t xml:space="preserve">burthen</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2520,7 +2583,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">beam to depth, as a ratio. High is shallow and beamy, low is deep and narrow.</t>
+          <t xml:space="preserve">builder's old measurement tons: what she was rated to carry.</t>
         </is>
       </c>
     </row>
@@ -2532,7 +2595,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">burthen</t>
+          <t xml:space="preserve">disp</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2542,7 +2605,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">builder's old measurement tons: what she was rated to carry.</t>
+          <t xml:space="preserve">displacement, tons: what she actually weighs afloat.</t>
         </is>
       </c>
     </row>
@@ -2554,17 +2617,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">disp</t>
+          <t xml:space="preserve">bowFine</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recorded only</t>
+          <t xml:space="preserve">Her drawing</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">displacement, tons: what she actually weighs afloat.</t>
+          <t xml:space="preserve">how fine her entry is. 5 is a clipper's bow and 1 a carrack's. It narrows her bow and pulls her shoulders aft.</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2639,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowFine</t>
+          <t xml:space="preserve">tumblehome</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2586,7 +2649,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">how fine her entry is. 5 is a clipper's bow and 1 a carrack's. It narrows her bow and pulls her shoulders aft.</t>
+          <t xml:space="preserve">how far her sides roll inward above the waterline. 5 is a fluyt.</t>
         </is>
       </c>
     </row>
@@ -2598,17 +2661,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">tumblehome</t>
+          <t xml:space="preserve">deadrise</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Her drawing</t>
+          <t xml:space="preserve">Recorded only</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">how far her sides roll inward above the waterline. 5 is a fluyt.</t>
+          <t xml:space="preserve">how sharply her bottom rises from the keel. 1 is a flat floor.</t>
         </is>
       </c>
     </row>
@@ -2620,17 +2683,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">deadrise</t>
+          <t xml:space="preserve">sheer</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recorded only</t>
+          <t xml:space="preserve">Her drawing</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">how sharply her bottom rises from the keel. 1 is a flat floor.</t>
+          <t xml:space="preserve">how much her deck sweeps up towards bow and stern.</t>
         </is>
       </c>
     </row>
@@ -2642,7 +2705,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">sheer</t>
+          <t xml:space="preserve">castle</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2652,7 +2715,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">how much her deck sweeps up towards bow and stern.</t>
+          <t xml:space="preserve">how built up her ends are. 1 is an open boat, 2 raises a quarterdeck, 3 and up add a forecastle. It is also what a windowed stern needs before it shows any lights.</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2727,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">castle</t>
+          <t xml:space="preserve">stern</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2674,7 +2737,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">how built up her ends are. 1 is an open boat, 2 raises a quarterdeck, 3 and up add a forecastle. It is also what a windowed stern needs before it shows any lights.</t>
+          <t xml:space="preserve">the shape of her stern, as one of the named types. Scow, Round, Pear, Elliptical, Raking transom, Overhanging and Square each have geometry of their own, and any other name draws a plain transom, which is what Transom and Gallery do. A name holding "gallery" or "castle" lights her stern windows if her castle is 3 or more.</t>
         </is>
       </c>
     </row>
@@ -2686,7 +2749,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">stern</t>
+          <t xml:space="preserve">mastHeight</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2696,7 +2759,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">the shape of her stern, as one of the named types. Scow, Round, Pear, Elliptical, Raking transom, Overhanging and Square each have geometry of their own, and any other name draws a plain transom, which is what Transom and Gallery do. A name holding "gallery" or "castle" lights her stern windows if her castle is 3 or more.</t>
+          <t xml:space="preserve">how tall her rig stands, as a multiple of the galleon's. Scales her masts in both views.</t>
         </is>
       </c>
     </row>
@@ -2708,17 +2771,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">mastHeight</t>
+          <t xml:space="preserve">decks</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Her drawing</t>
+          <t xml:space="preserve">Recorded only</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">how tall her rig stands, as a multiple of the galleon's. Scales her masts in both views.</t>
+          <t xml:space="preserve">how many of her decks carry guns: 1, 1-2, 2, 2-3 or 3. Text, because a range is not a number. Recorded description now: `battery` says deck by deck where her guns actually stood, and that is what her ports are drawn from.</t>
         </is>
       </c>
     </row>
@@ -2730,7 +2793,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">decks</t>
+          <t xml:space="preserve">wale</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2740,7 +2803,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">how many of her decks carry guns: 1, 1-2, 2, 2-3 or 3. Text, because a range is not a number. Recorded description now: `battery` says deck by deck where her guns actually stood, and that is what her ports are drawn from.</t>
+          <t xml:space="preserve">the thickness of her main wale, inches: the heavy belt of timber along her side.</t>
         </is>
       </c>
     </row>
@@ -2752,7 +2815,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">wale</t>
+          <t xml:space="preserve">topside</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2762,7 +2825,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">the thickness of her main wale, inches: the heavy belt of timber along her side.</t>
+          <t xml:space="preserve">the thickness of her topside planking, inches.</t>
         </is>
       </c>
     </row>
@@ -2774,17 +2837,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">topside</t>
+          <t xml:space="preserve">roomSpace</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recorded only</t>
+          <t xml:space="preserve">Her drawing</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">the thickness of her topside planking, inches.</t>
+          <t xml:space="preserve">room and space, feet: from one frame to the next. A gunport was framed on it, running a little over one space wide, so this is the size of every port she shows.</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2859,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">roomSpace</t>
+          <t xml:space="preserve">species</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2806,7 +2869,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">room and space, feet: from one frame to the next. A gunport was framed on it, running a little over one space wide, so this is the size of every port she shows.</t>
+          <t xml:space="preserve">what she was built of, which is also her colour: Oak, Live oak, Teak, Cedar or Pine. Any other name is painted as oak.</t>
         </is>
       </c>
     </row>
@@ -2818,7 +2881,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">species</t>
+          <t xml:space="preserve">timber</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2828,7 +2891,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">what she was built of, which is also her colour: Oak, Live oak, Teak, Cedar or Pine. Any other name is painted as oak.</t>
+          <t xml:space="preserve">how dense that timber is, oak being 1. Denser timber reads a little darker.</t>
         </is>
       </c>
     </row>
@@ -2840,17 +2903,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">timber</t>
+          <t xml:space="preserve">crewMin</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Her drawing</t>
+          <t xml:space="preserve">Recorded only</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">how dense that timber is, oak being 1. Denser timber reads a little darker.</t>
+          <t xml:space="preserve">the fewest hands she could be worked with, as against the battle complement in `crew`.</t>
         </is>
       </c>
     </row>
@@ -2862,7 +2925,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">crewMin</t>
+          <t xml:space="preserve">cruise</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2872,7 +2935,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">the fewest hands she could be worked with, as against the battle complement in `crew`.</t>
+          <t xml:space="preserve">her everyday speed, knots.</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2947,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">cruise</t>
+          <t xml:space="preserve">topSpeed</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2894,7 +2957,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">her everyday speed, knots.</t>
+          <t xml:space="preserve">the best she was ever driven, knots.</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2969,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">topSpeed</t>
+          <t xml:space="preserve">manoeuvre</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2916,7 +2979,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">the best she was ever driven, knots.</t>
+          <t xml:space="preserve">how handy she was, 0 to 100. The reference's own score, and what `hand` came out of.</t>
         </is>
       </c>
     </row>
@@ -2928,17 +2991,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">manoeuvre</t>
+          <t xml:space="preserve">histGuns</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recorded only</t>
+          <t xml:space="preserve">Her drawing</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">how handy she was, 0 to 100. The reference's own score, and what `hand` came out of.</t>
+          <t xml:space="preserve">how many guns she really carried, of every sort. Half of them is exactly her `broadside` bearing for every class in the fleet, which is how the ports and the guns that fire out of them agree without the catalogue and the reference ever meeting. `battery` says where those guns stood and has to add up to this.</t>
         </is>
       </c>
     </row>
@@ -2950,7 +3013,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">histGuns</t>
+          <t xml:space="preserve">battery</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2960,7 +3023,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">how many guns she really carried, of every sort. Half of them is exactly her `broadside` bearing for every class in the fleet, which is how the ports and the guns that fire out of them agree without the catalogue and the reference ever meeting. `battery` says where those guns stood and has to add up to this.</t>
+          <t xml:space="preserve">her establishment, deck by deck, as guns aboard rather than a side. Gun decks first and lowest deck first, then what she carried on her upper works after a plus: "10" is a cutter's ten on one open deck, "28+8/2" a frigate with a gun deck of 28 and ten more on her quarterdeck and forecastle, "28/28/28+12/4" a first rate. The figures sum to histGuns and every gun deck takes an even number, half of them a side. A GUN DECK AND AN UPPER WORKS ARE NOT THE SAME FITTING, which is the whole reason this column exists. A gun deck is a continuous battery pierced through her side, so its ports run the length of her, under the castles the way a lower deck really did. Her quarterdeck and forecastle guns stood in the open behind a bulwark, with no lidded port to show, and drawn as such they are what leaves a two-decker's waist empty. After the plus, two figures are the quarterdeck and the forecastle in that order, with her waist bare between them. One figure is a battery that ran the whole length of her upper works, which is what a spar-decked heavy frigate had. Write "2/0" rather than "2" for a ship who carried hers aft only. A BOAT IS NOT PIERCED AT ALL. A lidded port is cut through her topside under the deck above it, and a hull with a castle score of 1 has neither, so her whole battery is drawn standing at her rail however this column is written.</t>
         </is>
       </c>
     </row>
@@ -2972,39 +3035,34 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery</t>
+          <t xml:space="preserve">drawnLength</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
           <t xml:space="preserve">Her drawing</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">her establishment, deck by deck, as guns aboard rather than a side. Gun decks first and lowest deck first, then what she carried on her upper works after a plus: "10" is a cutter's ten on one open deck, "28+8/2" a frigate with a gun deck of 28 and ten more on her quarterdeck and forecastle, "28/28/30+12/2" a first rate. The figures sum to histGuns and every gun deck takes an even number, half of them a side. A GUN DECK AND AN UPPER WORKS ARE NOT THE SAME FITTING, which is the whole reason this column exists. A gun deck is a continuous battery pierced through her side, so its ports run the length of her, under the castles the way a lower deck really did. Her quarterdeck and forecastle guns stood in the open behind a bulwark, with no lidded port to show, and drawn as such they are what leaves a two-decker's waist empty. After the plus, two figures are the quarterdeck and the forecastle in that order, with her waist bare between them. One figure is a battery that ran the whole length of her upper works, which is what a spar-decked heavy frigate had. Write "2/0" rather than "2" for a ship who carried hers aft only. A BOAT IS NOT PIERCED AT ALL. A lidded port is cut through her topside under the deck above it, and a hull with a castle score of 1 has neither, so her whole battery is drawn standing at her rail however this column is written.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Masts</t>
+          <t xml:space="preserve">Hulls</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">drawnBeam</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">The fight</t>
+          <t xml:space="preserve">Her drawing</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">short camelCase name, unique.</t>
+          <t xml:space="preserve">its extreme beam. Only a class with a model of her own in src/render3d/bespoke/ carries them; everybody else leaves both blank and is drawn from the figures above. Her collision ellipse at sea keeps the length the fleet's compression gives her and takes its beam from these two in proportion, so a ball bites where her planking is drawn and not outside it. The bespoke test holds them to the model's own figures.</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3074,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3026,7 +3084,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">what a captain reads.</t>
+          <t xml:space="preserve">short camelCase name, unique.</t>
         </is>
       </c>
     </row>
@@ -3038,7 +3096,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">price</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3048,7 +3106,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">coins.</t>
+          <t xml:space="preserve">what a captain reads.</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3118,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">size</t>
+          <t xml:space="preserve">price</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3070,7 +3128,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">the SMALLEST socket it fits. A mast also fits any larger socket, which is a legal poor choice rather than an error: sizes are boat, small, medium, large, heavy.</t>
+          <t xml:space="preserve">coins.</t>
         </is>
       </c>
     </row>
@@ -3082,7 +3140,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">spar</t>
+          <t xml:space="preserve">size</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3092,7 +3150,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes for a SPAR rather than a mast: a jibboom or a spritsail yard, which goes on the bowsprit and nowhere else. A spar and a mast are different sorts of thing and are matched as such, or a jibboom would be legal as somebody's main mast.</t>
+          <t xml:space="preserve">the SMALLEST socket it fits. A mast also fits any larger socket, which is a legal poor choice rather than an error: sizes are boat, small, medium, large, heavy.</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3162,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">family</t>
+          <t xml:space="preserve">spar</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3114,7 +3172,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">the shape of rig this mast is, and a hull's socket says which families it takes, so a lug mast never steps in a frigate and a topgallant mast never steps in a lugger. One family to a mast, matched before the size rung is consulted: square     lower mast up to skysail mast, all square canvas: a ship's fore and main spanker    a fore-and-aft driver under square canvas: a ship's mizzen, a cutter's main schooner   gaff sail with a square topsail over it gaff       gaff mainsail and gaff topsail bermuda    one tall triangle lateen     the lateen yard and the lateen mast lug        lug mast and lug topmast boat       pole and sprit masts, what an open boat steps headsails  the bowsprit spars that carry jibs and staysails spritsail  the old headgear slung under the bowsprit, a carrack's and a galleon's Studdingsails boom out from square and schooner rig only; the other families never carried the booms for them.</t>
+          <t xml:space="preserve">yes for a SPAR rather than a mast: a jibboom or a spritsail yard, which goes on the bowsprit and nowhere else. A spar and a mast are different sorts of thing and are matched as such, or a jibboom would be legal as somebody's main mast.</t>
         </is>
       </c>
     </row>
@@ -3126,7 +3184,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">height</t>
+          <t xml:space="preserve">family</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3136,7 +3194,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">how tall she stands as a share of a full mast at her station, 0 to 1. The renderer cuts the pole down to the canvas actually bent on it, so this is an upper bound, not a look.</t>
+          <t xml:space="preserve">the shape of rig this mast is, and a hull's socket says which families it takes, so a lug mast never steps in a frigate and a topgallant mast never steps in a lugger. One family to a mast, matched before the size rung is consulted: square     lower mast up to skysail mast, all square canvas: a ship's fore and main spanker    a fore-and-aft driver under square canvas: a ship's mizzen, a cutter's main schooner   gaff sail with a square topsail over it gaff       gaff mainsail and gaff topsail bermuda    one tall triangle lateen     the lateen yard and the lateen mast lug        lug mast and lug topmast boat       pole and sprit masts, what an open boat steps headsails  the bowsprit spars that carry jibs and staysails spritsail  the old headgear slung under the bowsprit, a carrack's and a galleon's Studdingsails boom out from square and schooner rig only; the other families never carried the booms for them.</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3206,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">berths</t>
+          <t xml:space="preserve">height</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3158,7 +3216,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">the sails she can carry, DECK UPWARD, as category labels separated by spaces. LSQ large square   SSQ small square   TRI headsail   LAT lateen   GAF gaff   LUG lugsail Five is the most the renderer can place up one mast in bands of their own, and the bench fails a mast that asks for more. STU is a studdingsail and is NOT a berth. It booms out beyond a square sail already set, so it attaches to a sail rather than filling a place in the rig, and the bench refuses it.</t>
+          <t xml:space="preserve">how tall she stands as a share of a full mast at her station, 0 to 1. The renderer cuts the pole down to the canvas actually bent on it, so this is an upper bound, not a look.</t>
         </is>
       </c>
     </row>
@@ -3170,7 +3228,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">blurb</t>
+          <t xml:space="preserve">berths</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3180,19 +3238,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">one line a captain reads.</t>
+          <t xml:space="preserve">the sails she can carry, DECK UPWARD, as category labels separated by spaces. LSQ large square   SSQ small square   TRI headsail   LAT lateen   GAF gaff   LUG lugsail Five is the most the renderer can place up one mast in bands of their own, and the bench fails a mast that asks for more. STU is a studdingsail and is NOT a berth. It booms out beyond a square sail already set, so it attaches to a sail rather than filling a place in the rig, and the bench refuses it.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sails</t>
+          <t xml:space="preserve">Masts</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">blurb</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3202,7 +3260,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">short camelCase name, unique.</t>
+          <t xml:space="preserve">one line a captain reads.</t>
         </is>
       </c>
     </row>
@@ -3214,7 +3272,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3224,7 +3282,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">what a captain reads.</t>
+          <t xml:space="preserve">short camelCase name, unique.</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3294,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">kind</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3246,7 +3304,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">one of the seven labels above.</t>
+          <t xml:space="preserve">what a captain reads.</t>
         </is>
       </c>
     </row>
@@ -3258,7 +3316,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">price</t>
+          <t xml:space="preserve">kind</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3268,7 +3326,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">coins.</t>
+          <t xml:space="preserve">one of the seven labels above.</t>
         </is>
       </c>
     </row>
@@ -3280,7 +3338,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">drive</t>
+          <t xml:space="preserve">price</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3290,7 +3348,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">what she pulls, as a share of a course's, which is why a course is exactly 1. Physical area is where this number starts and the proportions are: course 1.00, lower topsail 0.70, topgallant 0.40, royal 0.22, skysail 0.12. Better cloth holds its shape and adds to it, which is why two sails of one area can differ here. FOR A STUDDINGSAIL ONLY, drive is a share of the sail it booms out from (0.50 to 0.80), because its area comes off that sail rather than off a place in the rig.</t>
+          <t xml:space="preserve">coins.</t>
         </is>
       </c>
     </row>
@@ -3302,7 +3360,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">hand</t>
+          <t xml:space="preserve">drive</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3312,7 +3370,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">what it does to her helm. Square canvas stiffens her, so it is negative; fore-and-aft canvas helps her round, so it is positive.</t>
+          <t xml:space="preserve">what she pulls, as a share of a course's, which is why a course is exactly 1. Physical area is where this number starts and the proportions are: course 1.00, lower topsail 0.70, topgallant 0.40, royal 0.22, skysail 0.12. Better cloth holds its shape and adds to it, which is why two sails of one area can differ here. FOR A STUDDINGSAIL ONLY, drive is a share of the sail it booms out from (0.50 to 0.80), because its area comes off that sail rather than off a place in the rig.</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3382,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">level</t>
+          <t xml:space="preserve">hand</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3334,7 +3392,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">STU only, and blank everywhere else. Which square sail up the mast it booms out from, counting square canvas from the deck: 0 is the lowest, a course; 1 the topsail over it; 2 the topgallant. The berth number is not the level, because a driver mast's course sits at berth 1 with a spanker under it.</t>
+          <t xml:space="preserve">what it does to her helm. Square canvas stiffens her, so it is negative; fore-and-aft canvas helps her round, so it is positive.</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3404,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">blurb</t>
+          <t xml:space="preserve">level</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3356,19 +3414,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">one line a captain reads.</t>
+          <t xml:space="preserve">STU only, and blank everywhere else. Which square sail up the mast it booms out from, counting square canvas from the deck: 0 is the lowest, a course; 1 the topsail over it; 2 the topgallant. The berth number is not the level, because a driver mast's course sits at berth 1 with a spanker under it.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guns</t>
+          <t xml:space="preserve">Sails</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">blurb</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3378,7 +3436,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">short camelCase name, unique.</t>
+          <t xml:space="preserve">one line a captain reads.</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3448,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3400,7 +3458,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">what a captain reads. A GUN IS NAMED BY THE WEIGHT OF HER BALL, IN NUMERALS: `32-pounder`, not `Thirty two pounder`. A captain reads this list to compare ten pieces, and comparing them is arithmetic she should not have to do in words. It is the game's own rule about numerals, and a shelf of guns is where the cost of breaking it shows worst.</t>
+          <t xml:space="preserve">short camelCase name, unique.</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3470,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">mount</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3422,7 +3480,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">broadside, bow or swivel.</t>
+          <t xml:space="preserve">what a captain reads. A GUN IS NAMED BY THE WEIGHT OF HER BALL, IN NUMERALS: `32-pounder`, not `Thirty two pounder`. A captain reads this list to compare ten pieces, and comparing them is arithmetic she should not have to do in words. It is the game's own rule about numerals, and a shelf of guns is where the cost of breaking it shows worst.</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3492,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">price</t>
+          <t xml:space="preserve">mount</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3444,7 +3502,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">coins.</t>
+          <t xml:space="preserve">broadside, bow or swivel.</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3514,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">damage</t>
+          <t xml:space="preserve">price</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3466,7 +3524,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">what one ball takes off a hull.</t>
+          <t xml:space="preserve">coins.</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3536,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">reload</t>
+          <t xml:space="preserve">damage</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3488,7 +3546,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">seconds between rounds. A mixed battery serves at the pace of its slowest piece.</t>
+          <t xml:space="preserve">what one ball takes off a hull.</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3558,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">weight</t>
+          <t xml:space="preserve">reload</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3510,7 +3568,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">what she carries for it. Enough of it takes the edge off her handling, which is the reason to leave a port empty.</t>
+          <t xml:space="preserve">seconds between rounds. A mixed battery serves at the pace of its slowest piece.</t>
         </is>
       </c>
     </row>
@@ -3522,7 +3580,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">group</t>
+          <t xml:space="preserve">weight</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3532,7 +3590,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">swivels only, and blank everywhere else. How true one throws, as a share of a musket's own scatter: 1 is no better than the hands beside it, and smaller is tighter. A better swivel never adds a ball to the volley; what quality buys is that the volley hits harder and lands closer to where the bow points, and this is the second half of that.</t>
+          <t xml:space="preserve">what she carries for it. Enough of it takes the edge off her handling, which is the reason to leave a port empty.</t>
         </is>
       </c>
     </row>
@@ -3544,15 +3602,37 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
+          <t xml:space="preserve">group</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The fight</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">swivels only, and blank everywhere else. How true one throws, as a share of a musket's own scatter: 1 is no better than the hands beside it, and smaller is tighter. A better swivel never adds a ball to the volley; what quality buys is that the volley hits harder and lands closer to where the bow points, and this is the second half of that.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Guns</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
           <t xml:space="preserve">blurb</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t xml:space="preserve">The fight</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t xml:space="preserve">one line a captain reads.</t>
         </is>
@@ -3572,7 +3652,7 @@
     <col min="5" max="5" width="6.00" customWidth="1"/>
     <col min="6" max="6" width="6.00" customWidth="1"/>
     <col min="7" max="7" width="7.00" customWidth="1"/>
-    <col min="8" max="8" width="6.00" customWidth="1"/>
+    <col min="8" max="8" width="7.00" customWidth="1"/>
     <col min="9" max="9" width="8.00" customWidth="1"/>
     <col min="10" max="10" width="7.00" customWidth="1"/>
     <col min="11" max="11" width="11.00" customWidth="1"/>
@@ -3588,31 +3668,32 @@
     <col min="21" max="21" width="6.00" customWidth="1"/>
     <col min="22" max="22" width="6.00" customWidth="1"/>
     <col min="23" max="23" width="7.00" customWidth="1"/>
-    <col min="24" max="24" width="7.00" customWidth="1"/>
-    <col min="25" max="25" width="11.00" customWidth="1"/>
+    <col min="24" max="24" width="11.00" customWidth="1"/>
+    <col min="25" max="25" width="6.00" customWidth="1"/>
     <col min="26" max="26" width="6.00" customWidth="1"/>
-    <col min="27" max="27" width="6.00" customWidth="1"/>
-    <col min="28" max="28" width="9.00" customWidth="1"/>
-    <col min="29" max="29" width="6.00" customWidth="1"/>
-    <col min="30" max="30" width="9.00" customWidth="1"/>
-    <col min="31" max="31" width="12.00" customWidth="1"/>
-    <col min="32" max="32" width="10.00" customWidth="1"/>
-    <col min="33" max="33" width="7.00" customWidth="1"/>
-    <col min="34" max="34" width="8.00" customWidth="1"/>
-    <col min="35" max="35" width="16.00" customWidth="1"/>
-    <col min="36" max="36" width="12.00" customWidth="1"/>
-    <col min="37" max="37" width="7.00" customWidth="1"/>
-    <col min="38" max="38" width="6.00" customWidth="1"/>
-    <col min="39" max="39" width="9.00" customWidth="1"/>
-    <col min="40" max="40" width="11.00" customWidth="1"/>
-    <col min="41" max="41" width="10.00" customWidth="1"/>
-    <col min="42" max="42" width="8.00" customWidth="1"/>
-    <col min="43" max="43" width="9.00" customWidth="1"/>
-    <col min="44" max="44" width="8.00" customWidth="1"/>
-    <col min="45" max="45" width="10.00" customWidth="1"/>
-    <col min="46" max="46" width="11.00" customWidth="1"/>
-    <col min="47" max="47" width="10.00" customWidth="1"/>
-    <col min="48" max="48" width="15.00" customWidth="1"/>
+    <col min="27" max="27" width="9.00" customWidth="1"/>
+    <col min="28" max="28" width="6.00" customWidth="1"/>
+    <col min="29" max="29" width="9.00" customWidth="1"/>
+    <col min="30" max="30" width="12.00" customWidth="1"/>
+    <col min="31" max="31" width="10.00" customWidth="1"/>
+    <col min="32" max="32" width="7.00" customWidth="1"/>
+    <col min="33" max="33" width="8.00" customWidth="1"/>
+    <col min="34" max="34" width="16.00" customWidth="1"/>
+    <col min="35" max="35" width="12.00" customWidth="1"/>
+    <col min="36" max="36" width="7.00" customWidth="1"/>
+    <col min="37" max="37" width="6.00" customWidth="1"/>
+    <col min="38" max="38" width="9.00" customWidth="1"/>
+    <col min="39" max="39" width="11.00" customWidth="1"/>
+    <col min="40" max="40" width="10.00" customWidth="1"/>
+    <col min="41" max="41" width="8.00" customWidth="1"/>
+    <col min="42" max="42" width="9.00" customWidth="1"/>
+    <col min="43" max="43" width="8.00" customWidth="1"/>
+    <col min="44" max="44" width="10.00" customWidth="1"/>
+    <col min="45" max="45" width="11.00" customWidth="1"/>
+    <col min="46" max="46" width="10.00" customWidth="1"/>
+    <col min="47" max="47" width="15.00" customWidth="1"/>
+    <col min="48" max="48" width="13.00" customWidth="1"/>
+    <col min="49" max="49" width="11.00" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3728,132 +3809,137 @@
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">draft</t>
+          <t xml:space="preserve">depth</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">depth</t>
+          <t xml:space="preserve">freeboard</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">freeboard</t>
+          <t xml:space="preserve">lb</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">lb</t>
+          <t xml:space="preserve">bd</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd</t>
+          <t xml:space="preserve">burthen</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">burthen</t>
+          <t xml:space="preserve">disp</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">disp</t>
+          <t xml:space="preserve">bowFine</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowFine</t>
+          <t xml:space="preserve">tumblehome</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tumblehome</t>
+          <t xml:space="preserve">deadrise</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">deadrise</t>
+          <t xml:space="preserve">sheer</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">sheer</t>
+          <t xml:space="preserve">castle</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">castle</t>
+          <t xml:space="preserve">stern</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">stern</t>
+          <t xml:space="preserve">mastHeight</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">mastHeight</t>
+          <t xml:space="preserve">decks</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decks</t>
+          <t xml:space="preserve">wale</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">wale</t>
+          <t xml:space="preserve">topside</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">topside</t>
+          <t xml:space="preserve">roomSpace</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">roomSpace</t>
+          <t xml:space="preserve">species</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">species</t>
+          <t xml:space="preserve">timber</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">timber</t>
+          <t xml:space="preserve">crewMin</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">crewMin</t>
+          <t xml:space="preserve">cruise</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">cruise</t>
+          <t xml:space="preserve">topSpeed</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">topSpeed</t>
+          <t xml:space="preserve">manoeuvre</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">manoeuvre</t>
+          <t xml:space="preserve">histGuns</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">histGuns</t>
+          <t xml:space="preserve">battery</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery</t>
+          <t xml:space="preserve">drawnLength</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">drawnBeam</t>
         </is>
       </c>
     </row>
@@ -3943,87 +4029,84 @@
         <v>13</v>
       </c>
       <c r="W2">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="X2">
+        <v>2</v>
+      </c>
+      <c r="Y2">
+        <v>3.08</v>
+      </c>
+      <c r="Z2">
+        <v>3.25</v>
+      </c>
+      <c r="AA2">
+        <v>15</v>
+      </c>
+      <c r="AB2">
+        <v>20</v>
+      </c>
+      <c r="AC2">
+        <v>2</v>
+      </c>
+      <c r="AD2">
+        <v>1</v>
+      </c>
+      <c r="AE2">
+        <v>1</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>1</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scow</t>
+        </is>
+      </c>
+      <c r="AI2">
+        <v>0.7</v>
+      </c>
+      <c r="AJ2">
+        <v>1</v>
+      </c>
+      <c r="AK2">
+        <v>2</v>
+      </c>
+      <c r="AL2">
+        <v>1</v>
+      </c>
+      <c r="AM2">
+        <v>2</v>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pine</t>
+        </is>
+      </c>
+      <c r="AO2">
+        <v>1</v>
+      </c>
+      <c r="AP2">
+        <v>12</v>
+      </c>
+      <c r="AQ2">
+        <v>2</v>
+      </c>
+      <c r="AR2">
         <v>4</v>
       </c>
-      <c r="Y2">
-        <v>2</v>
-      </c>
-      <c r="Z2">
-        <v>3.08</v>
-      </c>
-      <c r="AA2">
-        <v>3.25</v>
-      </c>
-      <c r="AB2">
-        <v>15</v>
-      </c>
-      <c r="AC2">
-        <v>20</v>
-      </c>
-      <c r="AD2">
-        <v>2</v>
-      </c>
-      <c r="AE2">
-        <v>1</v>
-      </c>
-      <c r="AF2">
-        <v>1</v>
-      </c>
-      <c r="AG2">
-        <v>1</v>
-      </c>
-      <c r="AH2">
-        <v>1</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Scow</t>
-        </is>
-      </c>
-      <c r="AJ2">
-        <v>0.7</v>
-      </c>
-      <c r="AK2">
-        <v>1</v>
-      </c>
-      <c r="AL2">
-        <v>2</v>
-      </c>
-      <c r="AM2">
-        <v>1</v>
-      </c>
-      <c r="AN2">
-        <v>2</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pine</t>
-        </is>
-      </c>
-      <c r="AP2">
-        <v>1</v>
-      </c>
-      <c r="AQ2">
-        <v>12</v>
-      </c>
-      <c r="AR2">
-        <v>2</v>
-      </c>
       <c r="AS2">
+        <v>40</v>
+      </c>
+      <c r="AT2">
         <v>4</v>
-      </c>
-      <c r="AT2">
-        <v>40</v>
       </c>
       <c r="AU2">
         <v>4</v>
       </c>
-      <c r="AV2">
-        <v>4</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4111,87 +4194,84 @@
         <v>16</v>
       </c>
       <c r="W3">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="X3">
+        <v>3</v>
+      </c>
+      <c r="Y3">
+        <v>2.88</v>
+      </c>
+      <c r="Z3">
+        <v>2</v>
+      </c>
+      <c r="AA3">
+        <v>30</v>
+      </c>
+      <c r="AB3">
+        <v>39</v>
+      </c>
+      <c r="AC3">
+        <v>4</v>
+      </c>
+      <c r="AD3">
+        <v>2</v>
+      </c>
+      <c r="AE3">
+        <v>4</v>
+      </c>
+      <c r="AF3">
+        <v>3</v>
+      </c>
+      <c r="AG3">
+        <v>1</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transom</t>
+        </is>
+      </c>
+      <c r="AI3">
+        <v>1.5</v>
+      </c>
+      <c r="AJ3">
+        <v>1</v>
+      </c>
+      <c r="AK3">
+        <v>2.5</v>
+      </c>
+      <c r="AL3">
+        <v>1.5</v>
+      </c>
+      <c r="AM3">
+        <v>1.7</v>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cedar</t>
+        </is>
+      </c>
+      <c r="AO3">
+        <v>1</v>
+      </c>
+      <c r="AP3">
+        <v>10</v>
+      </c>
+      <c r="AQ3">
         <v>8</v>
       </c>
-      <c r="Y3">
-        <v>3</v>
-      </c>
-      <c r="Z3">
-        <v>2.88</v>
-      </c>
-      <c r="AA3">
-        <v>2</v>
-      </c>
-      <c r="AB3">
-        <v>30</v>
-      </c>
-      <c r="AC3">
-        <v>39</v>
-      </c>
-      <c r="AD3">
-        <v>4</v>
-      </c>
-      <c r="AE3">
-        <v>2</v>
-      </c>
-      <c r="AF3">
-        <v>4</v>
-      </c>
-      <c r="AG3">
-        <v>3</v>
-      </c>
-      <c r="AH3">
-        <v>1</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transom</t>
-        </is>
-      </c>
-      <c r="AJ3">
-        <v>1.5</v>
-      </c>
-      <c r="AK3">
-        <v>1</v>
-      </c>
-      <c r="AL3">
-        <v>2.5</v>
-      </c>
-      <c r="AM3">
-        <v>1.5</v>
-      </c>
-      <c r="AN3">
-        <v>1.7</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cedar</t>
-        </is>
-      </c>
-      <c r="AP3">
-        <v>1</v>
-      </c>
-      <c r="AQ3">
-        <v>10</v>
-      </c>
       <c r="AR3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AS3">
-        <v>12</v>
+        <v>87</v>
       </c>
       <c r="AT3">
-        <v>87</v>
+        <v>6</v>
       </c>
       <c r="AU3">
         <v>6</v>
       </c>
-      <c r="AV3">
-        <v>6</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4279,87 +4359,84 @@
         <v>18</v>
       </c>
       <c r="W4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X4">
-        <v>8</v>
+        <v>3.5</v>
       </c>
       <c r="Y4">
-        <v>3.5</v>
+        <v>2.78</v>
       </c>
       <c r="Z4">
-        <v>2.78</v>
+        <v>2.25</v>
       </c>
       <c r="AA4">
-        <v>2.25</v>
+        <v>40</v>
       </c>
       <c r="AB4">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="AC4">
-        <v>52</v>
+        <v>3</v>
       </c>
       <c r="AD4">
+        <v>2</v>
+      </c>
+      <c r="AE4">
         <v>3</v>
-      </c>
-      <c r="AE4">
-        <v>2</v>
       </c>
       <c r="AF4">
         <v>3</v>
       </c>
       <c r="AG4">
-        <v>3</v>
-      </c>
-      <c r="AH4">
-        <v>1</v>
-      </c>
-      <c r="AI4" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="AH4" t="inlineStr">
         <is>
           <t xml:space="preserve">Transom</t>
         </is>
       </c>
+      <c r="AI4">
+        <v>1.4</v>
+      </c>
       <c r="AJ4">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AK4">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="AL4">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="AM4">
-        <v>1.5</v>
-      </c>
-      <c r="AN4">
         <v>1.7</v>
       </c>
-      <c r="AO4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t xml:space="preserve">Oak</t>
         </is>
       </c>
+      <c r="AO4">
+        <v>1</v>
+      </c>
       <c r="AP4">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="AQ4">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AR4">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AS4">
-        <v>11</v>
+        <v>88</v>
       </c>
       <c r="AT4">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="AU4">
         <v>8</v>
       </c>
-      <c r="AV4">
-        <v>8</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4447,87 +4524,84 @@
         <v>20</v>
       </c>
       <c r="W5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X5">
-        <v>8</v>
+        <v>3.5</v>
       </c>
       <c r="Y5">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="Z5">
         <v>2.5</v>
       </c>
       <c r="AA5">
-        <v>2.5</v>
+        <v>50</v>
       </c>
       <c r="AB5">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="AC5">
-        <v>66</v>
+        <v>3</v>
       </c>
       <c r="AD5">
+        <v>2</v>
+      </c>
+      <c r="AE5">
         <v>3</v>
       </c>
-      <c r="AE5">
+      <c r="AF5">
         <v>2</v>
       </c>
-      <c r="AF5">
-        <v>3</v>
-      </c>
       <c r="AG5">
-        <v>2</v>
-      </c>
-      <c r="AH5">
-        <v>1</v>
-      </c>
-      <c r="AI5" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="AH5" t="inlineStr">
         <is>
           <t xml:space="preserve">Transom</t>
         </is>
       </c>
+      <c r="AI5">
+        <v>1.4</v>
+      </c>
       <c r="AJ5">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AK5">
-        <v>1</v>
+        <v>2.75</v>
       </c>
       <c r="AL5">
-        <v>2.75</v>
+        <v>1.6</v>
       </c>
       <c r="AM5">
-        <v>1.6</v>
-      </c>
-      <c r="AN5">
         <v>1.7</v>
       </c>
-      <c r="AO5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t xml:space="preserve">Oak</t>
         </is>
       </c>
+      <c r="AO5">
+        <v>1</v>
+      </c>
       <c r="AP5">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="AQ5">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="AR5">
-        <v>7.5</v>
+        <v>11.5</v>
       </c>
       <c r="AS5">
-        <v>11.5</v>
+        <v>89</v>
       </c>
       <c r="AT5">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="AU5">
         <v>10</v>
       </c>
-      <c r="AV5">
-        <v>10</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4615,87 +4689,84 @@
         <v>22</v>
       </c>
       <c r="W6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X6">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Y6">
+        <v>3.64</v>
+      </c>
+      <c r="Z6">
+        <v>2.75</v>
+      </c>
+      <c r="AA6">
+        <v>120</v>
+      </c>
+      <c r="AB6">
+        <v>158</v>
+      </c>
+      <c r="AC6">
+        <v>5</v>
+      </c>
+      <c r="AD6">
+        <v>2</v>
+      </c>
+      <c r="AE6">
         <v>4</v>
       </c>
-      <c r="Z6">
-        <v>3.64</v>
-      </c>
-      <c r="AA6">
-        <v>2.75</v>
-      </c>
-      <c r="AB6">
-        <v>120</v>
-      </c>
-      <c r="AC6">
-        <v>158</v>
-      </c>
-      <c r="AD6">
-        <v>5</v>
-      </c>
-      <c r="AE6">
-        <v>2</v>
-      </c>
       <c r="AF6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG6">
+        <v>1</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Raking transom</t>
+        </is>
+      </c>
+      <c r="AI6">
+        <v>1.3</v>
+      </c>
+      <c r="AJ6">
+        <v>1</v>
+      </c>
+      <c r="AK6">
         <v>3</v>
       </c>
-      <c r="AH6">
-        <v>1</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Raking transom</t>
-        </is>
-      </c>
-      <c r="AJ6">
-        <v>1.3</v>
-      </c>
-      <c r="AK6">
-        <v>1</v>
-      </c>
       <c r="AL6">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="AM6">
-        <v>1.75</v>
-      </c>
-      <c r="AN6">
         <v>1.7</v>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t xml:space="preserve">Oak</t>
         </is>
       </c>
+      <c r="AO6">
+        <v>1</v>
+      </c>
       <c r="AP6">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="AQ6">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="AR6">
-        <v>9</v>
+        <v>14.5</v>
       </c>
       <c r="AS6">
-        <v>14.5</v>
+        <v>86</v>
       </c>
       <c r="AT6">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="AU6">
         <v>12</v>
       </c>
-      <c r="AV6">
-        <v>12</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4783,25 +4854,25 @@
         <v>23</v>
       </c>
       <c r="W7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="X7">
-        <v>10</v>
+        <v>4.5</v>
       </c>
       <c r="Y7">
-        <v>4.5</v>
+        <v>3.57</v>
       </c>
       <c r="Z7">
-        <v>3.57</v>
+        <v>2.3</v>
       </c>
       <c r="AA7">
-        <v>2.3</v>
+        <v>170</v>
       </c>
       <c r="AB7">
-        <v>170</v>
+        <v>228</v>
       </c>
       <c r="AC7">
-        <v>228</v>
+        <v>3</v>
       </c>
       <c r="AD7">
         <v>3</v>
@@ -4813,57 +4884,54 @@
         <v>3</v>
       </c>
       <c r="AG7">
+        <v>2</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transom</t>
+        </is>
+      </c>
+      <c r="AI7">
+        <v>1.1</v>
+      </c>
+      <c r="AJ7">
+        <v>1</v>
+      </c>
+      <c r="AK7">
         <v>3</v>
       </c>
-      <c r="AH7">
-        <v>2</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transom</t>
-        </is>
-      </c>
-      <c r="AJ7">
-        <v>1.1</v>
-      </c>
-      <c r="AK7">
-        <v>1</v>
-      </c>
       <c r="AL7">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="AM7">
-        <v>1.75</v>
-      </c>
-      <c r="AN7">
         <v>1.8</v>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t xml:space="preserve">Oak</t>
         </is>
       </c>
+      <c r="AO7">
+        <v>1</v>
+      </c>
       <c r="AP7">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="AQ7">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="AR7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AS7">
-        <v>10</v>
+        <v>68</v>
       </c>
       <c r="AT7">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="AU7">
         <v>14</v>
       </c>
-      <c r="AV7">
-        <v>14</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4954,84 +5022,81 @@
         <v>8</v>
       </c>
       <c r="X8">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Y8">
+        <v>4.25</v>
+      </c>
+      <c r="Z8">
+        <v>2.5</v>
+      </c>
+      <c r="AA8">
+        <v>140</v>
+      </c>
+      <c r="AB8">
+        <v>186</v>
+      </c>
+      <c r="AC8">
+        <v>5</v>
+      </c>
+      <c r="AD8">
+        <v>1</v>
+      </c>
+      <c r="AE8">
         <v>4</v>
       </c>
-      <c r="Z8">
-        <v>4.25</v>
-      </c>
-      <c r="AA8">
-        <v>2.5</v>
-      </c>
-      <c r="AB8">
-        <v>140</v>
-      </c>
-      <c r="AC8">
-        <v>186</v>
-      </c>
-      <c r="AD8">
-        <v>5</v>
-      </c>
-      <c r="AE8">
-        <v>1</v>
-      </c>
       <c r="AF8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG8">
+        <v>2</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Overhanging</t>
+        </is>
+      </c>
+      <c r="AI8">
+        <v>1.2</v>
+      </c>
+      <c r="AJ8">
+        <v>1</v>
+      </c>
+      <c r="AK8">
         <v>3</v>
       </c>
-      <c r="AH8">
-        <v>2</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Overhanging</t>
-        </is>
-      </c>
-      <c r="AJ8">
-        <v>1.2</v>
-      </c>
-      <c r="AK8">
-        <v>1</v>
-      </c>
       <c r="AL8">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="AM8">
         <v>1.75</v>
       </c>
-      <c r="AN8">
-        <v>1.75</v>
-      </c>
-      <c r="AO8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t xml:space="preserve">Oak</t>
         </is>
       </c>
+      <c r="AO8">
+        <v>1</v>
+      </c>
       <c r="AP8">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="AQ8">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="AR8">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AS8">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="AT8">
-        <v>82</v>
+        <v>18</v>
       </c>
       <c r="AU8">
         <v>18</v>
       </c>
-      <c r="AV8">
-        <v>18</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5119,28 +5184,28 @@
         <v>28</v>
       </c>
       <c r="W9">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="X9">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="Y9">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="Z9">
-        <v>3.75</v>
+        <v>2.33</v>
       </c>
       <c r="AA9">
-        <v>2.33</v>
+        <v>330</v>
       </c>
       <c r="AB9">
-        <v>330</v>
+        <v>455</v>
       </c>
       <c r="AC9">
-        <v>455</v>
+        <v>4</v>
       </c>
       <c r="AD9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE9">
         <v>3</v>
@@ -5149,57 +5214,54 @@
         <v>3</v>
       </c>
       <c r="AG9">
-        <v>3</v>
-      </c>
-      <c r="AH9">
         <v>2</v>
       </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
         <is>
           <t xml:space="preserve">Round</t>
         </is>
       </c>
+      <c r="AI9">
+        <v>1.2</v>
+      </c>
       <c r="AJ9">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AK9">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="AL9">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="AM9">
-        <v>2</v>
-      </c>
-      <c r="AN9">
         <v>1.85</v>
       </c>
-      <c r="AO9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t xml:space="preserve">Oak</t>
         </is>
       </c>
+      <c r="AO9">
+        <v>1</v>
+      </c>
       <c r="AP9">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="AQ9">
-        <v>60</v>
+        <v>6.5</v>
       </c>
       <c r="AR9">
-        <v>6.5</v>
+        <v>11</v>
       </c>
       <c r="AS9">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="AT9">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="AU9">
         <v>20</v>
       </c>
-      <c r="AV9">
-        <v>20</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5287,28 +5349,28 @@
         <v>32</v>
       </c>
       <c r="W10">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="X10">
-        <v>11</v>
+        <v>5.5</v>
       </c>
       <c r="Y10">
-        <v>5.5</v>
+        <v>3.56</v>
       </c>
       <c r="Z10">
-        <v>3.56</v>
+        <v>2.91</v>
       </c>
       <c r="AA10">
-        <v>2.91</v>
+        <v>450</v>
       </c>
       <c r="AB10">
-        <v>450</v>
+        <v>630</v>
       </c>
       <c r="AC10">
-        <v>630</v>
+        <v>4</v>
       </c>
       <c r="AD10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE10">
         <v>3</v>
@@ -5319,53 +5381,50 @@
       <c r="AG10">
         <v>3</v>
       </c>
-      <c r="AH10">
-        <v>3</v>
-      </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AH10" t="inlineStr">
         <is>
           <t xml:space="preserve">Round</t>
         </is>
       </c>
+      <c r="AI10">
+        <v>1.2</v>
+      </c>
       <c r="AJ10">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AK10">
-        <v>1</v>
+        <v>3.75</v>
       </c>
       <c r="AL10">
-        <v>3.75</v>
+        <v>2.25</v>
       </c>
       <c r="AM10">
-        <v>2.25</v>
-      </c>
-      <c r="AN10">
         <v>1.9</v>
       </c>
-      <c r="AO10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t xml:space="preserve">Oak</t>
         </is>
       </c>
+      <c r="AO10">
+        <v>1</v>
+      </c>
       <c r="AP10">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="AQ10">
-        <v>90</v>
+        <v>6.5</v>
       </c>
       <c r="AR10">
-        <v>6.5</v>
+        <v>10.5</v>
       </c>
       <c r="AS10">
-        <v>10.5</v>
+        <v>62</v>
       </c>
       <c r="AT10">
-        <v>62</v>
-      </c>
-      <c r="AU10">
         <v>24</v>
       </c>
-      <c r="AV10" t="inlineStr">
+      <c r="AU10" t="inlineStr">
         <is>
           <t xml:space="preserve">22+2/0</t>
         </is>
@@ -5457,87 +5516,84 @@
         <v>29</v>
       </c>
       <c r="W11">
+        <v>11</v>
+      </c>
+      <c r="X11">
+        <v>5</v>
+      </c>
+      <c r="Y11">
+        <v>4.14</v>
+      </c>
+      <c r="Z11">
+        <v>2.64</v>
+      </c>
+      <c r="AA11">
+        <v>380</v>
+      </c>
+      <c r="AB11">
+        <v>525</v>
+      </c>
+      <c r="AC11">
+        <v>5</v>
+      </c>
+      <c r="AD11">
+        <v>1</v>
+      </c>
+      <c r="AE11">
+        <v>4</v>
+      </c>
+      <c r="AF11">
+        <v>3</v>
+      </c>
+      <c r="AG11">
+        <v>2</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Overhanging</t>
+        </is>
+      </c>
+      <c r="AI11">
+        <v>1.2</v>
+      </c>
+      <c r="AJ11">
+        <v>1</v>
+      </c>
+      <c r="AK11">
+        <v>3.5</v>
+      </c>
+      <c r="AL11">
+        <v>2</v>
+      </c>
+      <c r="AM11">
+        <v>1.8</v>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oak</t>
+        </is>
+      </c>
+      <c r="AO11">
+        <v>1</v>
+      </c>
+      <c r="AP11">
+        <v>110</v>
+      </c>
+      <c r="AQ11">
+        <v>7</v>
+      </c>
+      <c r="AR11">
         <v>12</v>
       </c>
-      <c r="X11">
-        <v>11</v>
-      </c>
-      <c r="Y11">
-        <v>5</v>
-      </c>
-      <c r="Z11">
-        <v>4.14</v>
-      </c>
-      <c r="AA11">
-        <v>2.64</v>
-      </c>
-      <c r="AB11">
-        <v>380</v>
-      </c>
-      <c r="AC11">
-        <v>525</v>
-      </c>
-      <c r="AD11">
-        <v>5</v>
-      </c>
-      <c r="AE11">
-        <v>1</v>
-      </c>
-      <c r="AF11">
-        <v>4</v>
-      </c>
-      <c r="AG11">
-        <v>3</v>
-      </c>
-      <c r="AH11">
-        <v>2</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Overhanging</t>
-        </is>
-      </c>
-      <c r="AJ11">
-        <v>1.2</v>
-      </c>
-      <c r="AK11">
-        <v>1</v>
-      </c>
-      <c r="AL11">
-        <v>3.5</v>
-      </c>
-      <c r="AM11">
-        <v>2</v>
-      </c>
-      <c r="AN11">
-        <v>1.8</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Oak</t>
-        </is>
-      </c>
-      <c r="AP11">
-        <v>1</v>
-      </c>
-      <c r="AQ11">
-        <v>110</v>
-      </c>
-      <c r="AR11">
-        <v>7</v>
-      </c>
       <c r="AS11">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="AT11">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="AU11">
         <v>32</v>
       </c>
-      <c r="AV11">
-        <v>32</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5625,28 +5681,28 @@
         <v>39</v>
       </c>
       <c r="W12">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="X12">
-        <v>13</v>
+        <v>6.5</v>
       </c>
       <c r="Y12">
-        <v>6.5</v>
+        <v>3.74</v>
       </c>
       <c r="Z12">
-        <v>3.74</v>
+        <v>3</v>
       </c>
       <c r="AA12">
+        <v>860</v>
+      </c>
+      <c r="AB12">
+        <v>1230</v>
+      </c>
+      <c r="AC12">
+        <v>4</v>
+      </c>
+      <c r="AD12">
         <v>3</v>
-      </c>
-      <c r="AB12">
-        <v>860</v>
-      </c>
-      <c r="AC12">
-        <v>1230</v>
-      </c>
-      <c r="AD12">
-        <v>4</v>
       </c>
       <c r="AE12">
         <v>3</v>
@@ -5657,53 +5713,50 @@
       <c r="AG12">
         <v>3</v>
       </c>
-      <c r="AH12">
-        <v>3</v>
-      </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AH12" t="inlineStr">
         <is>
           <t xml:space="preserve">Gallery</t>
         </is>
       </c>
+      <c r="AI12">
+        <v>1.2</v>
+      </c>
       <c r="AJ12">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="AK12">
-        <v>2</v>
+        <v>4.25</v>
       </c>
       <c r="AL12">
-        <v>4.25</v>
+        <v>2.5</v>
       </c>
       <c r="AM12">
-        <v>2.5</v>
-      </c>
-      <c r="AN12">
         <v>1.9</v>
       </c>
-      <c r="AO12" t="inlineStr">
+      <c r="AN12" t="inlineStr">
         <is>
           <t xml:space="preserve">Oak</t>
         </is>
       </c>
+      <c r="AO12">
+        <v>1</v>
+      </c>
       <c r="AP12">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="AQ12">
-        <v>170</v>
+        <v>8</v>
       </c>
       <c r="AR12">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AS12">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="AT12">
-        <v>59</v>
-      </c>
-      <c r="AU12">
         <v>38</v>
       </c>
-      <c r="AV12" t="inlineStr">
+      <c r="AU12" t="inlineStr">
         <is>
           <t xml:space="preserve">28+8/2</t>
         </is>
@@ -5795,28 +5848,28 @@
         <v>43</v>
       </c>
       <c r="W13">
-        <v>22</v>
+        <v>13.5</v>
       </c>
       <c r="X13">
-        <v>13.5</v>
+        <v>7</v>
       </c>
       <c r="Y13">
-        <v>7</v>
+        <v>3.91</v>
       </c>
       <c r="Z13">
-        <v>3.91</v>
+        <v>3.19</v>
       </c>
       <c r="AA13">
-        <v>3.19</v>
+        <v>1350</v>
       </c>
       <c r="AB13">
-        <v>1350</v>
+        <v>1920</v>
       </c>
       <c r="AC13">
-        <v>1920</v>
+        <v>4</v>
       </c>
       <c r="AD13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE13">
         <v>3</v>
@@ -5827,53 +5880,50 @@
       <c r="AG13">
         <v>3</v>
       </c>
-      <c r="AH13">
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gallery</t>
+        </is>
+      </c>
+      <c r="AI13">
+        <v>1.3</v>
+      </c>
+      <c r="AJ13">
+        <v>2</v>
+      </c>
+      <c r="AK13">
+        <v>5.25</v>
+      </c>
+      <c r="AL13">
         <v>3</v>
       </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gallery</t>
-        </is>
-      </c>
-      <c r="AJ13">
-        <v>1.3</v>
-      </c>
-      <c r="AK13">
-        <v>2</v>
-      </c>
-      <c r="AL13">
-        <v>5.25</v>
-      </c>
       <c r="AM13">
-        <v>3</v>
-      </c>
-      <c r="AN13">
         <v>1.9</v>
       </c>
-      <c r="AO13" t="inlineStr">
+      <c r="AN13" t="inlineStr">
         <is>
           <t xml:space="preserve">Live oak</t>
         </is>
       </c>
+      <c r="AO13">
+        <v>1</v>
+      </c>
       <c r="AP13">
-        <v>1</v>
+        <v>280</v>
       </c>
       <c r="AQ13">
-        <v>280</v>
+        <v>8</v>
       </c>
       <c r="AR13">
-        <v>8</v>
+        <v>13.5</v>
       </c>
       <c r="AS13">
-        <v>13.5</v>
+        <v>55</v>
       </c>
       <c r="AT13">
-        <v>55</v>
-      </c>
-      <c r="AU13">
         <v>50</v>
       </c>
-      <c r="AV13" t="inlineStr">
+      <c r="AU13" t="inlineStr">
         <is>
           <t xml:space="preserve">30+20</t>
         </is>
@@ -5965,85 +6015,82 @@
         <v>42</v>
       </c>
       <c r="W14">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="X14">
-        <v>17.5</v>
+        <v>7.5</v>
       </c>
       <c r="Y14">
-        <v>7.5</v>
+        <v>3.57</v>
       </c>
       <c r="Z14">
-        <v>3.57</v>
+        <v>2.4</v>
       </c>
       <c r="AA14">
-        <v>2.4</v>
+        <v>980</v>
       </c>
       <c r="AB14">
-        <v>980</v>
+        <v>1470</v>
       </c>
       <c r="AC14">
-        <v>1470</v>
+        <v>3</v>
       </c>
       <c r="AD14">
+        <v>4</v>
+      </c>
+      <c r="AE14">
         <v>3</v>
       </c>
-      <c r="AE14">
+      <c r="AF14">
         <v>4</v>
       </c>
-      <c r="AF14">
+      <c r="AG14">
         <v>3</v>
       </c>
-      <c r="AG14">
-        <v>4</v>
-      </c>
-      <c r="AH14">
-        <v>3</v>
-      </c>
-      <c r="AI14" t="inlineStr">
+      <c r="AH14" t="inlineStr">
         <is>
           <t xml:space="preserve">Gallery</t>
         </is>
       </c>
+      <c r="AI14">
+        <v>1.1</v>
+      </c>
       <c r="AJ14">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="AK14">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="AL14">
-        <v>5.5</v>
+        <v>3.25</v>
       </c>
       <c r="AM14">
-        <v>3.25</v>
-      </c>
-      <c r="AN14">
         <v>1.95</v>
       </c>
-      <c r="AO14" t="inlineStr">
+      <c r="AN14" t="inlineStr">
         <is>
           <t xml:space="preserve">Oak</t>
         </is>
       </c>
+      <c r="AO14">
+        <v>1</v>
+      </c>
       <c r="AP14">
-        <v>1</v>
+        <v>240</v>
       </c>
       <c r="AQ14">
-        <v>240</v>
+        <v>6</v>
       </c>
       <c r="AR14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AS14">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="AT14">
-        <v>52</v>
-      </c>
-      <c r="AU14">
         <v>54</v>
       </c>
-      <c r="AV14" t="inlineStr">
+      <c r="AU14" t="inlineStr">
         <is>
           <t xml:space="preserve">24/22+6/2</t>
         </is>
@@ -6097,7 +6144,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowsprit/large/headsails fore/heavy/square main/heavy/square mizzen/large/spanker</t>
+          <t xml:space="preserve">bowsprit/small/headsails fore/large/square/2 main/large/square/2 mizzen/heavy/spanker</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -6126,97 +6173,100 @@
         </is>
       </c>
       <c r="T15">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="U15">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="V15">
+        <v>44.5</v>
+      </c>
+      <c r="W15">
+        <v>19</v>
+      </c>
+      <c r="X15">
+        <v>8</v>
+      </c>
+      <c r="Y15">
+        <v>3.6</v>
+      </c>
+      <c r="Z15">
+        <v>2.34</v>
+      </c>
+      <c r="AA15">
+        <v>1400</v>
+      </c>
+      <c r="AB15">
+        <v>2170</v>
+      </c>
+      <c r="AC15">
+        <v>3</v>
+      </c>
+      <c r="AD15">
+        <v>4</v>
+      </c>
+      <c r="AE15">
+        <v>3</v>
+      </c>
+      <c r="AF15">
+        <v>4</v>
+      </c>
+      <c r="AG15">
+        <v>3</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gallery</t>
+        </is>
+      </c>
+      <c r="AI15">
+        <v>1.15</v>
+      </c>
+      <c r="AJ15">
+        <v>2</v>
+      </c>
+      <c r="AK15">
+        <v>6.25</v>
+      </c>
+      <c r="AL15">
+        <v>3.75</v>
+      </c>
+      <c r="AM15">
+        <v>1.95</v>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oak</t>
+        </is>
+      </c>
+      <c r="AO15">
+        <v>1</v>
+      </c>
+      <c r="AP15">
+        <v>320</v>
+      </c>
+      <c r="AQ15">
+        <v>6</v>
+      </c>
+      <c r="AR15">
+        <v>10.5</v>
+      </c>
+      <c r="AS15">
         <v>45</v>
       </c>
-      <c r="W15">
-        <v>22</v>
-      </c>
-      <c r="X15">
-        <v>19</v>
-      </c>
-      <c r="Y15">
-        <v>8</v>
-      </c>
-      <c r="Z15">
-        <v>3.67</v>
-      </c>
-      <c r="AA15">
-        <v>2.37</v>
-      </c>
-      <c r="AB15">
-        <v>1400</v>
-      </c>
-      <c r="AC15">
-        <v>2170</v>
-      </c>
-      <c r="AD15">
-        <v>3</v>
-      </c>
-      <c r="AE15">
-        <v>4</v>
-      </c>
-      <c r="AF15">
-        <v>3</v>
-      </c>
-      <c r="AG15">
-        <v>4</v>
-      </c>
-      <c r="AH15">
-        <v>3</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gallery</t>
-        </is>
-      </c>
-      <c r="AJ15">
-        <v>1.15</v>
-      </c>
-      <c r="AK15">
-        <v>2</v>
-      </c>
-      <c r="AL15">
-        <v>6.25</v>
-      </c>
-      <c r="AM15">
-        <v>3.75</v>
-      </c>
-      <c r="AN15">
-        <v>1.95</v>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Oak</t>
-        </is>
-      </c>
-      <c r="AP15">
-        <v>1</v>
-      </c>
-      <c r="AQ15">
-        <v>320</v>
-      </c>
-      <c r="AR15">
-        <v>6</v>
-      </c>
-      <c r="AS15">
-        <v>10.5</v>
-      </c>
       <c r="AT15">
-        <v>45</v>
-      </c>
-      <c r="AU15">
         <v>64</v>
       </c>
-      <c r="AV15" t="inlineStr">
+      <c r="AU15" t="inlineStr">
         <is>
           <t xml:space="preserve">26/26+10/2</t>
         </is>
+      </c>
+      <c r="AV15">
+        <v>50.16</v>
+      </c>
+      <c r="AW15">
+        <v>13.57</v>
       </c>
     </row>
     <row r="16">
@@ -6267,7 +6317,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowsprit/large/headsails fore/heavy/square main/heavy/square mizzen/large/spanker</t>
+          <t xml:space="preserve">bowsprit/small/headsails fore/large/square/2 main/large/square/2 mizzen/heavy/spanker</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -6296,97 +6346,100 @@
         </is>
       </c>
       <c r="T16">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="U16">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="V16">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="W16">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="X16">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="Y16">
-        <v>11</v>
+        <v>3.59</v>
       </c>
       <c r="Z16">
-        <v>3.6</v>
+        <v>2.33</v>
       </c>
       <c r="AA16">
-        <v>2.38</v>
+        <v>1900</v>
       </c>
       <c r="AB16">
-        <v>1900</v>
+        <v>3000</v>
       </c>
       <c r="AC16">
-        <v>3000</v>
+        <v>2</v>
       </c>
       <c r="AD16">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE16">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AF16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG16">
         <v>4</v>
       </c>
-      <c r="AH16">
-        <v>4</v>
-      </c>
-      <c r="AI16" t="inlineStr">
+      <c r="AH16" t="inlineStr">
         <is>
           <t xml:space="preserve">Gallery</t>
         </is>
       </c>
+      <c r="AI16">
+        <v>1.1</v>
+      </c>
       <c r="AJ16">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="AK16">
-        <v>3</v>
+        <v>6.75</v>
       </c>
       <c r="AL16">
-        <v>6.75</v>
+        <v>4.25</v>
       </c>
       <c r="AM16">
-        <v>4.25</v>
-      </c>
-      <c r="AN16">
         <v>2</v>
       </c>
-      <c r="AO16" t="inlineStr">
+      <c r="AN16" t="inlineStr">
         <is>
           <t xml:space="preserve">Oak</t>
         </is>
       </c>
+      <c r="AO16">
+        <v>1</v>
+      </c>
       <c r="AP16">
-        <v>1</v>
+        <v>450</v>
       </c>
       <c r="AQ16">
-        <v>450</v>
+        <v>5</v>
       </c>
       <c r="AR16">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AS16">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="AT16">
-        <v>41</v>
-      </c>
-      <c r="AU16">
         <v>90</v>
       </c>
-      <c r="AV16" t="inlineStr">
+      <c r="AU16" t="inlineStr">
         <is>
           <t xml:space="preserve">26/26/26+10/2</t>
         </is>
+      </c>
+      <c r="AV16">
+        <v>55.57</v>
+      </c>
+      <c r="AW16">
+        <v>14.94</v>
       </c>
     </row>
     <row r="17">
@@ -6415,10 +6468,10 @@
         <v>800</v>
       </c>
       <c r="G17">
-        <v>0.79</v>
+        <v>0.796</v>
       </c>
       <c r="H17">
-        <v>0.62</v>
+        <v>0.629</v>
       </c>
       <c r="I17">
         <v>5.68</v>
@@ -6437,7 +6490,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowsprit/large/headsails fore/heavy/square main/heavy/square mizzen/large/spanker</t>
+          <t xml:space="preserve">bowsprit/small/headsails fore/large/square/2 main/large/square/2 mizzen/heavy/spanker</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -6475,88 +6528,91 @@
         <v>51</v>
       </c>
       <c r="W17">
-        <v>28.5</v>
+        <v>22</v>
       </c>
       <c r="X17">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="Y17">
-        <v>12</v>
+        <v>3.73</v>
       </c>
       <c r="Z17">
-        <v>3.73</v>
+        <v>2.32</v>
       </c>
       <c r="AA17">
-        <v>2.32</v>
+        <v>2150</v>
       </c>
       <c r="AB17">
-        <v>2150</v>
+        <v>3500</v>
       </c>
       <c r="AC17">
-        <v>3500</v>
+        <v>2</v>
       </c>
       <c r="AD17">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE17">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AF17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG17">
         <v>4</v>
       </c>
-      <c r="AH17">
-        <v>4</v>
-      </c>
-      <c r="AI17" t="inlineStr">
+      <c r="AH17" t="inlineStr">
         <is>
           <t xml:space="preserve">Gallery</t>
         </is>
       </c>
+      <c r="AI17">
+        <v>1.1</v>
+      </c>
       <c r="AJ17">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="AK17">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AL17">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="AM17">
-        <v>4.5</v>
-      </c>
-      <c r="AN17">
         <v>2</v>
       </c>
-      <c r="AO17" t="inlineStr">
+      <c r="AN17" t="inlineStr">
         <is>
           <t xml:space="preserve">Oak</t>
         </is>
       </c>
+      <c r="AO17">
+        <v>1</v>
+      </c>
       <c r="AP17">
-        <v>1</v>
+        <v>520</v>
       </c>
       <c r="AQ17">
-        <v>520</v>
+        <v>5</v>
       </c>
       <c r="AR17">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AS17">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="AT17">
-        <v>38</v>
-      </c>
-      <c r="AU17">
         <v>100</v>
       </c>
-      <c r="AV17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28/28/30+12/2</t>
-        </is>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28/28/28+12/4</t>
+        </is>
+      </c>
+      <c r="AV17">
+        <v>58.7</v>
+      </c>
+      <c r="AW17">
+        <v>15.8</v>
       </c>
     </row>
     <row r="20">
@@ -6640,82 +6696,79 @@
         <v>8</v>
       </c>
       <c r="W20">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="X20">
+        <v>1.5</v>
+      </c>
+      <c r="Y20">
+        <v>4</v>
+      </c>
+      <c r="Z20">
+        <v>3.2</v>
+      </c>
+      <c r="AA20">
+        <v>6</v>
+      </c>
+      <c r="AB20">
+        <v>8</v>
+      </c>
+      <c r="AC20">
         <v>3</v>
       </c>
-      <c r="Y20">
-        <v>1.5</v>
-      </c>
-      <c r="Z20">
-        <v>4</v>
-      </c>
-      <c r="AA20">
-        <v>3.2</v>
-      </c>
-      <c r="AB20">
-        <v>6</v>
-      </c>
-      <c r="AC20">
-        <v>8</v>
-      </c>
       <c r="AD20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF20">
         <v>2</v>
       </c>
       <c r="AG20">
+        <v>1</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transom</t>
+        </is>
+      </c>
+      <c r="AI20">
+        <v>0.9</v>
+      </c>
+      <c r="AJ20">
+        <v>1</v>
+      </c>
+      <c r="AK20">
+        <v>1.5</v>
+      </c>
+      <c r="AL20">
+        <v>1</v>
+      </c>
+      <c r="AM20">
+        <v>1.2</v>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pine</t>
+        </is>
+      </c>
+      <c r="AO20">
+        <v>0.85</v>
+      </c>
+      <c r="AP20">
+        <v>6</v>
+      </c>
+      <c r="AQ20">
         <v>2</v>
       </c>
-      <c r="AH20">
-        <v>1</v>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transom</t>
-        </is>
-      </c>
-      <c r="AJ20">
-        <v>0.9</v>
-      </c>
-      <c r="AK20">
-        <v>1</v>
-      </c>
-      <c r="AL20">
-        <v>1.5</v>
-      </c>
-      <c r="AM20">
-        <v>1</v>
-      </c>
-      <c r="AN20">
-        <v>1.2</v>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pine</t>
-        </is>
-      </c>
-      <c r="AP20">
-        <v>0.85</v>
-      </c>
-      <c r="AQ20">
-        <v>6</v>
-      </c>
       <c r="AR20">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AS20">
-        <v>5</v>
+        <v>92</v>
       </c>
       <c r="AT20">
-        <v>92</v>
-      </c>
-      <c r="AU20">
         <v>1</v>
       </c>
     </row>
@@ -6800,82 +6853,79 @@
         <v>10</v>
       </c>
       <c r="W21">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="X21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y21">
+        <v>3.4</v>
+      </c>
+      <c r="Z21">
+        <v>2.9</v>
+      </c>
+      <c r="AA21">
+        <v>15</v>
+      </c>
+      <c r="AB21">
+        <v>20</v>
+      </c>
+      <c r="AC21">
+        <v>3</v>
+      </c>
+      <c r="AD21">
+        <v>1</v>
+      </c>
+      <c r="AE21">
         <v>2</v>
-      </c>
-      <c r="Z21">
-        <v>3.4</v>
-      </c>
-      <c r="AA21">
-        <v>2.9</v>
-      </c>
-      <c r="AB21">
-        <v>15</v>
-      </c>
-      <c r="AC21">
-        <v>20</v>
-      </c>
-      <c r="AD21">
-        <v>3</v>
-      </c>
-      <c r="AE21">
-        <v>1</v>
       </c>
       <c r="AF21">
         <v>2</v>
       </c>
       <c r="AG21">
+        <v>1</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transom</t>
+        </is>
+      </c>
+      <c r="AI21">
+        <v>0.8</v>
+      </c>
+      <c r="AJ21">
+        <v>1</v>
+      </c>
+      <c r="AK21">
         <v>2</v>
       </c>
-      <c r="AH21">
-        <v>1</v>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transom</t>
-        </is>
-      </c>
-      <c r="AJ21">
-        <v>0.8</v>
-      </c>
-      <c r="AK21">
-        <v>1</v>
-      </c>
       <c r="AL21">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AM21">
-        <v>1.25</v>
-      </c>
-      <c r="AN21">
         <v>1.4</v>
       </c>
-      <c r="AO21" t="inlineStr">
+      <c r="AN21" t="inlineStr">
         <is>
           <t xml:space="preserve">Oak</t>
         </is>
       </c>
+      <c r="AO21">
+        <v>1</v>
+      </c>
       <c r="AP21">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AQ21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR21">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AS21">
-        <v>6</v>
+        <v>92</v>
       </c>
       <c r="AT21">
-        <v>92</v>
-      </c>
-      <c r="AU21">
         <v>2</v>
       </c>
     </row>
@@ -6963,79 +7013,76 @@
         <v>2.5</v>
       </c>
       <c r="X22">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="Y22">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="Z22">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="AA22">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="AB22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC22">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AD22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF22">
         <v>2</v>
       </c>
       <c r="AG22">
+        <v>1</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transom</t>
+        </is>
+      </c>
+      <c r="AI22">
+        <v>0.8</v>
+      </c>
+      <c r="AJ22">
+        <v>1</v>
+      </c>
+      <c r="AK22">
+        <v>1.25</v>
+      </c>
+      <c r="AL22">
+        <v>1</v>
+      </c>
+      <c r="AM22">
+        <v>1.1</v>
+      </c>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pine</t>
+        </is>
+      </c>
+      <c r="AO22">
+        <v>0.85</v>
+      </c>
+      <c r="AP22">
+        <v>3</v>
+      </c>
+      <c r="AQ22">
         <v>2</v>
       </c>
-      <c r="AH22">
-        <v>1</v>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transom</t>
-        </is>
-      </c>
-      <c r="AJ22">
-        <v>0.8</v>
-      </c>
-      <c r="AK22">
-        <v>1</v>
-      </c>
-      <c r="AL22">
-        <v>1.25</v>
-      </c>
-      <c r="AM22">
-        <v>1</v>
-      </c>
-      <c r="AN22">
-        <v>1.1</v>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pine</t>
-        </is>
-      </c>
-      <c r="AP22">
-        <v>0.85</v>
-      </c>
-      <c r="AQ22">
-        <v>3</v>
-      </c>
       <c r="AR22">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AS22">
-        <v>5</v>
+        <v>93</v>
       </c>
       <c r="AT22">
-        <v>93</v>
-      </c>
-      <c r="AU22">
         <v>1</v>
       </c>
     </row>
@@ -7123,79 +7170,76 @@
         <v>8</v>
       </c>
       <c r="X23">
+        <v>3</v>
+      </c>
+      <c r="Y23">
+        <v>3.5</v>
+      </c>
+      <c r="Z23">
+        <v>1.9</v>
+      </c>
+      <c r="AA23">
+        <v>55</v>
+      </c>
+      <c r="AB23">
+        <v>70</v>
+      </c>
+      <c r="AC23">
+        <v>3</v>
+      </c>
+      <c r="AD23">
+        <v>2</v>
+      </c>
+      <c r="AE23">
+        <v>3</v>
+      </c>
+      <c r="AF23">
+        <v>2</v>
+      </c>
+      <c r="AG23">
+        <v>1</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transom</t>
+        </is>
+      </c>
+      <c r="AI23">
+        <v>1.1</v>
+      </c>
+      <c r="AJ23">
+        <v>1</v>
+      </c>
+      <c r="AK23">
+        <v>2.5</v>
+      </c>
+      <c r="AL23">
+        <v>1.5</v>
+      </c>
+      <c r="AM23">
+        <v>1.6</v>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oak</t>
+        </is>
+      </c>
+      <c r="AO23">
+        <v>1</v>
+      </c>
+      <c r="AP23">
         <v>8</v>
       </c>
-      <c r="Y23">
-        <v>3</v>
-      </c>
-      <c r="Z23">
-        <v>3.5</v>
-      </c>
-      <c r="AA23">
-        <v>1.9</v>
-      </c>
-      <c r="AB23">
-        <v>55</v>
-      </c>
-      <c r="AC23">
-        <v>70</v>
-      </c>
-      <c r="AD23">
-        <v>3</v>
-      </c>
-      <c r="AE23">
-        <v>2</v>
-      </c>
-      <c r="AF23">
-        <v>3</v>
-      </c>
-      <c r="AG23">
-        <v>2</v>
-      </c>
-      <c r="AH23">
-        <v>1</v>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transom</t>
-        </is>
-      </c>
-      <c r="AJ23">
-        <v>1.1</v>
-      </c>
-      <c r="AK23">
-        <v>1</v>
-      </c>
-      <c r="AL23">
-        <v>2.5</v>
-      </c>
-      <c r="AM23">
-        <v>1.5</v>
-      </c>
-      <c r="AN23">
-        <v>1.6</v>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Oak</t>
-        </is>
-      </c>
-      <c r="AP23">
-        <v>1</v>
-      </c>
       <c r="AQ23">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AR23">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AS23">
-        <v>9</v>
+        <v>91</v>
       </c>
       <c r="AT23">
-        <v>91</v>
-      </c>
-      <c r="AU23">
         <v>4</v>
       </c>
     </row>
@@ -7280,25 +7324,25 @@
         <v>18</v>
       </c>
       <c r="W24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X24">
-        <v>8</v>
+        <v>3.5</v>
       </c>
       <c r="Y24">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="Z24">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="AA24">
-        <v>2.6</v>
+        <v>75</v>
       </c>
       <c r="AB24">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AC24">
-        <v>95</v>
+        <v>2</v>
       </c>
       <c r="AD24">
         <v>2</v>
@@ -7310,52 +7354,49 @@
         <v>2</v>
       </c>
       <c r="AG24">
-        <v>2</v>
-      </c>
-      <c r="AH24">
-        <v>1</v>
-      </c>
-      <c r="AI24" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="AH24" t="inlineStr">
         <is>
           <t xml:space="preserve">Round</t>
         </is>
       </c>
+      <c r="AI24">
+        <v>0.9</v>
+      </c>
       <c r="AJ24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AK24">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="AL24">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="AM24">
-        <v>1.5</v>
-      </c>
-      <c r="AN24">
         <v>1.7</v>
       </c>
-      <c r="AO24" t="inlineStr">
+      <c r="AN24" t="inlineStr">
         <is>
           <t xml:space="preserve">Oak</t>
         </is>
       </c>
+      <c r="AO24">
+        <v>1</v>
+      </c>
       <c r="AP24">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AQ24">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AR24">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AS24">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="AT24">
-        <v>83</v>
-      </c>
-      <c r="AU24">
         <v>4</v>
       </c>
     </row>
@@ -7440,82 +7481,79 @@
         <v>15</v>
       </c>
       <c r="W25">
+        <v>5</v>
+      </c>
+      <c r="X25">
+        <v>2.5</v>
+      </c>
+      <c r="Y25">
+        <v>3.6</v>
+      </c>
+      <c r="Z25">
+        <v>3.8</v>
+      </c>
+      <c r="AA25">
+        <v>45</v>
+      </c>
+      <c r="AB25">
+        <v>60</v>
+      </c>
+      <c r="AC25">
+        <v>2</v>
+      </c>
+      <c r="AD25">
+        <v>1</v>
+      </c>
+      <c r="AE25">
+        <v>1</v>
+      </c>
+      <c r="AF25">
+        <v>1</v>
+      </c>
+      <c r="AG25">
+        <v>1</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scow</t>
+        </is>
+      </c>
+      <c r="AI25">
+        <v>0.7</v>
+      </c>
+      <c r="AJ25">
+        <v>1</v>
+      </c>
+      <c r="AK25">
+        <v>2.5</v>
+      </c>
+      <c r="AL25">
+        <v>1.5</v>
+      </c>
+      <c r="AM25">
+        <v>1.8</v>
+      </c>
+      <c r="AN25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pine</t>
+        </is>
+      </c>
+      <c r="AO25">
+        <v>0.85</v>
+      </c>
+      <c r="AP25">
+        <v>20</v>
+      </c>
+      <c r="AQ25">
+        <v>2</v>
+      </c>
+      <c r="AR25">
         <v>4</v>
       </c>
-      <c r="X25">
-        <v>5</v>
-      </c>
-      <c r="Y25">
-        <v>2.5</v>
-      </c>
-      <c r="Z25">
-        <v>3.6</v>
-      </c>
-      <c r="AA25">
-        <v>3.8</v>
-      </c>
-      <c r="AB25">
-        <v>45</v>
-      </c>
-      <c r="AC25">
-        <v>60</v>
-      </c>
-      <c r="AD25">
-        <v>2</v>
-      </c>
-      <c r="AE25">
-        <v>1</v>
-      </c>
-      <c r="AF25">
-        <v>1</v>
-      </c>
-      <c r="AG25">
-        <v>1</v>
-      </c>
-      <c r="AH25">
-        <v>1</v>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Scow</t>
-        </is>
-      </c>
-      <c r="AJ25">
-        <v>0.7</v>
-      </c>
-      <c r="AK25">
-        <v>1</v>
-      </c>
-      <c r="AL25">
-        <v>2.5</v>
-      </c>
-      <c r="AM25">
-        <v>1.5</v>
-      </c>
-      <c r="AN25">
-        <v>1.8</v>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pine</t>
-        </is>
-      </c>
-      <c r="AP25">
-        <v>0.85</v>
-      </c>
-      <c r="AQ25">
-        <v>20</v>
-      </c>
-      <c r="AR25">
-        <v>2</v>
-      </c>
       <c r="AS25">
-        <v>4</v>
+        <v>63</v>
       </c>
       <c r="AT25">
-        <v>63</v>
-      </c>
-      <c r="AU25">
         <v>3</v>
       </c>
     </row>
@@ -7603,79 +7641,76 @@
         <v>7</v>
       </c>
       <c r="X26">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Y26">
+        <v>3.4</v>
+      </c>
+      <c r="Z26">
+        <v>2.3</v>
+      </c>
+      <c r="AA26">
+        <v>60</v>
+      </c>
+      <c r="AB26">
+        <v>80</v>
+      </c>
+      <c r="AC26">
         <v>3</v>
       </c>
-      <c r="Z26">
-        <v>3.4</v>
-      </c>
-      <c r="AA26">
-        <v>2.3</v>
-      </c>
-      <c r="AB26">
-        <v>60</v>
-      </c>
-      <c r="AC26">
-        <v>80</v>
-      </c>
       <c r="AD26">
+        <v>2</v>
+      </c>
+      <c r="AE26">
         <v>3</v>
       </c>
-      <c r="AE26">
+      <c r="AF26">
         <v>2</v>
       </c>
-      <c r="AF26">
-        <v>3</v>
-      </c>
       <c r="AG26">
-        <v>2</v>
-      </c>
-      <c r="AH26">
-        <v>1</v>
-      </c>
-      <c r="AI26" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="AH26" t="inlineStr">
         <is>
           <t xml:space="preserve">Transom</t>
         </is>
       </c>
+      <c r="AI26">
+        <v>1</v>
+      </c>
       <c r="AJ26">
         <v>1</v>
       </c>
       <c r="AK26">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="AL26">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="AM26">
-        <v>1.5</v>
-      </c>
-      <c r="AN26">
         <v>1.6</v>
       </c>
-      <c r="AO26" t="inlineStr">
+      <c r="AN26" t="inlineStr">
         <is>
           <t xml:space="preserve">Oak</t>
         </is>
       </c>
+      <c r="AO26">
+        <v>1</v>
+      </c>
       <c r="AP26">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AQ26">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AR26">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AS26">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="AT26">
-        <v>81</v>
-      </c>
-      <c r="AU26">
         <v>6</v>
       </c>
     </row>
@@ -7760,82 +7795,79 @@
         <v>16</v>
       </c>
       <c r="W27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X27">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Y27">
+        <v>3.75</v>
+      </c>
+      <c r="Z27">
+        <v>3.2</v>
+      </c>
+      <c r="AA27">
+        <v>70</v>
+      </c>
+      <c r="AB27">
+        <v>90</v>
+      </c>
+      <c r="AC27">
         <v>3</v>
       </c>
-      <c r="Z27">
-        <v>3.75</v>
-      </c>
-      <c r="AA27">
-        <v>3.2</v>
-      </c>
-      <c r="AB27">
-        <v>70</v>
-      </c>
-      <c r="AC27">
-        <v>90</v>
-      </c>
       <c r="AD27">
+        <v>1</v>
+      </c>
+      <c r="AE27">
+        <v>2</v>
+      </c>
+      <c r="AF27">
+        <v>1</v>
+      </c>
+      <c r="AG27">
+        <v>1</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transom</t>
+        </is>
+      </c>
+      <c r="AI27">
+        <v>0.9</v>
+      </c>
+      <c r="AJ27">
+        <v>1</v>
+      </c>
+      <c r="AK27">
         <v>3</v>
       </c>
-      <c r="AE27">
-        <v>1</v>
-      </c>
-      <c r="AF27">
-        <v>2</v>
-      </c>
-      <c r="AG27">
-        <v>1</v>
-      </c>
-      <c r="AH27">
-        <v>1</v>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transom</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>0.9</v>
-      </c>
-      <c r="AK27">
-        <v>1</v>
-      </c>
       <c r="AL27">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="AM27">
-        <v>1.75</v>
-      </c>
-      <c r="AN27">
         <v>1.7</v>
       </c>
-      <c r="AO27" t="inlineStr">
+      <c r="AN27" t="inlineStr">
         <is>
           <t xml:space="preserve">Oak</t>
         </is>
       </c>
+      <c r="AO27">
+        <v>1</v>
+      </c>
       <c r="AP27">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="AQ27">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="AR27">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AS27">
-        <v>7</v>
+        <v>84</v>
       </c>
       <c r="AT27">
-        <v>84</v>
-      </c>
-      <c r="AU27">
         <v>2</v>
       </c>
     </row>
@@ -7923,79 +7955,76 @@
         <v>10</v>
       </c>
       <c r="X28">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Y28">
+        <v>3.5</v>
+      </c>
+      <c r="Z28">
+        <v>2</v>
+      </c>
+      <c r="AA28">
+        <v>110</v>
+      </c>
+      <c r="AB28">
+        <v>140</v>
+      </c>
+      <c r="AC28">
         <v>4</v>
       </c>
-      <c r="Z28">
-        <v>3.5</v>
-      </c>
-      <c r="AA28">
+      <c r="AD28">
         <v>2</v>
       </c>
-      <c r="AB28">
-        <v>110</v>
-      </c>
-      <c r="AC28">
-        <v>140</v>
-      </c>
-      <c r="AD28">
+      <c r="AE28">
         <v>4</v>
       </c>
-      <c r="AE28">
+      <c r="AF28">
+        <v>3</v>
+      </c>
+      <c r="AG28">
+        <v>1</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transom</t>
+        </is>
+      </c>
+      <c r="AI28">
+        <v>1.5</v>
+      </c>
+      <c r="AJ28">
+        <v>1</v>
+      </c>
+      <c r="AK28">
+        <v>3</v>
+      </c>
+      <c r="AL28">
         <v>2</v>
       </c>
-      <c r="AF28">
-        <v>4</v>
-      </c>
-      <c r="AG28">
-        <v>3</v>
-      </c>
-      <c r="AH28">
-        <v>1</v>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transom</t>
-        </is>
-      </c>
-      <c r="AJ28">
-        <v>1.5</v>
-      </c>
-      <c r="AK28">
-        <v>1</v>
-      </c>
-      <c r="AL28">
-        <v>3</v>
-      </c>
       <c r="AM28">
-        <v>2</v>
-      </c>
-      <c r="AN28">
         <v>1.7</v>
       </c>
-      <c r="AO28" t="inlineStr">
+      <c r="AN28" t="inlineStr">
         <is>
           <t xml:space="preserve">Cedar</t>
         </is>
       </c>
+      <c r="AO28">
+        <v>1</v>
+      </c>
       <c r="AP28">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="AQ28">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="AR28">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AS28">
-        <v>12</v>
+        <v>89</v>
       </c>
       <c r="AT28">
-        <v>89</v>
-      </c>
-      <c r="AU28">
         <v>12</v>
       </c>
     </row>
@@ -8083,79 +8112,76 @@
         <v>6</v>
       </c>
       <c r="X29">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Y29">
+        <v>3.3</v>
+      </c>
+      <c r="Z29">
+        <v>2.5</v>
+      </c>
+      <c r="AA29">
+        <v>50</v>
+      </c>
+      <c r="AB29">
+        <v>65</v>
+      </c>
+      <c r="AC29">
         <v>3</v>
       </c>
-      <c r="Z29">
-        <v>3.3</v>
-      </c>
-      <c r="AA29">
+      <c r="AD29">
+        <v>2</v>
+      </c>
+      <c r="AE29">
+        <v>3</v>
+      </c>
+      <c r="AF29">
+        <v>2</v>
+      </c>
+      <c r="AG29">
+        <v>1</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transom</t>
+        </is>
+      </c>
+      <c r="AI29">
+        <v>0.9</v>
+      </c>
+      <c r="AJ29">
+        <v>1</v>
+      </c>
+      <c r="AK29">
         <v>2.5</v>
       </c>
-      <c r="AB29">
-        <v>50</v>
-      </c>
-      <c r="AC29">
-        <v>65</v>
-      </c>
-      <c r="AD29">
-        <v>3</v>
-      </c>
-      <c r="AE29">
-        <v>2</v>
-      </c>
-      <c r="AF29">
-        <v>3</v>
-      </c>
-      <c r="AG29">
-        <v>2</v>
-      </c>
-      <c r="AH29">
-        <v>1</v>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transom</t>
-        </is>
-      </c>
-      <c r="AJ29">
-        <v>0.9</v>
-      </c>
-      <c r="AK29">
-        <v>1</v>
-      </c>
       <c r="AL29">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="AM29">
-        <v>1.5</v>
-      </c>
-      <c r="AN29">
         <v>1.6</v>
       </c>
-      <c r="AO29" t="inlineStr">
+      <c r="AN29" t="inlineStr">
         <is>
           <t xml:space="preserve">Oak</t>
         </is>
       </c>
+      <c r="AO29">
+        <v>1</v>
+      </c>
       <c r="AP29">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="AQ29">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="AR29">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AS29">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="AT29">
-        <v>81</v>
-      </c>
-      <c r="AU29">
         <v>6</v>
       </c>
     </row>
@@ -8243,79 +8269,76 @@
         <v>11</v>
       </c>
       <c r="X30">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="Y30">
+        <v>3.1</v>
+      </c>
+      <c r="Z30">
+        <v>2.2</v>
+      </c>
+      <c r="AA30">
+        <v>200</v>
+      </c>
+      <c r="AB30">
+        <v>260</v>
+      </c>
+      <c r="AC30">
         <v>4</v>
       </c>
-      <c r="Z30">
-        <v>3.1</v>
-      </c>
-      <c r="AA30">
-        <v>2.2</v>
-      </c>
-      <c r="AB30">
-        <v>200</v>
-      </c>
-      <c r="AC30">
-        <v>260</v>
-      </c>
       <c r="AD30">
+        <v>2</v>
+      </c>
+      <c r="AE30">
         <v>4</v>
       </c>
-      <c r="AE30">
+      <c r="AF30">
         <v>2</v>
       </c>
-      <c r="AF30">
-        <v>4</v>
-      </c>
       <c r="AG30">
+        <v>1</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transom</t>
+        </is>
+      </c>
+      <c r="AI30">
+        <v>1.4</v>
+      </c>
+      <c r="AJ30">
+        <v>1</v>
+      </c>
+      <c r="AK30">
+        <v>3.5</v>
+      </c>
+      <c r="AL30">
         <v>2</v>
       </c>
-      <c r="AH30">
-        <v>1</v>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transom</t>
-        </is>
-      </c>
-      <c r="AJ30">
-        <v>1.4</v>
-      </c>
-      <c r="AK30">
-        <v>1</v>
-      </c>
-      <c r="AL30">
-        <v>3.5</v>
-      </c>
       <c r="AM30">
-        <v>2</v>
-      </c>
-      <c r="AN30">
         <v>1.8</v>
       </c>
-      <c r="AO30" t="inlineStr">
+      <c r="AN30" t="inlineStr">
         <is>
           <t xml:space="preserve">Oak</t>
         </is>
       </c>
+      <c r="AO30">
+        <v>1</v>
+      </c>
       <c r="AP30">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="AQ30">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="AR30">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AS30">
-        <v>12</v>
+        <v>87</v>
       </c>
       <c r="AT30">
-        <v>87</v>
-      </c>
-      <c r="AU30">
         <v>14</v>
       </c>
     </row>
@@ -8398,79 +8421,76 @@
         <v>10</v>
       </c>
       <c r="X31">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Y31">
+        <v>3.5</v>
+      </c>
+      <c r="Z31">
+        <v>2.2</v>
+      </c>
+      <c r="AA31">
+        <v>150</v>
+      </c>
+      <c r="AB31">
+        <v>190</v>
+      </c>
+      <c r="AC31">
         <v>4</v>
       </c>
-      <c r="Z31">
-        <v>3.5</v>
-      </c>
-      <c r="AA31">
-        <v>2.2</v>
-      </c>
-      <c r="AB31">
-        <v>150</v>
-      </c>
-      <c r="AC31">
-        <v>190</v>
-      </c>
       <c r="AD31">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE31">
+        <v>3</v>
+      </c>
+      <c r="AF31">
         <v>2</v>
       </c>
-      <c r="AF31">
+      <c r="AG31">
+        <v>1</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transom</t>
+        </is>
+      </c>
+      <c r="AI31">
+        <v>1</v>
+      </c>
+      <c r="AJ31">
+        <v>1</v>
+      </c>
+      <c r="AK31">
         <v>3</v>
       </c>
-      <c r="AG31">
-        <v>2</v>
-      </c>
-      <c r="AH31">
-        <v>1</v>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transom</t>
-        </is>
-      </c>
-      <c r="AJ31">
-        <v>1</v>
-      </c>
-      <c r="AK31">
-        <v>1</v>
-      </c>
       <c r="AL31">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="AM31">
-        <v>1.75</v>
-      </c>
-      <c r="AN31">
         <v>1.7</v>
       </c>
-      <c r="AO31" t="inlineStr">
+      <c r="AN31" t="inlineStr">
         <is>
           <t xml:space="preserve">Oak</t>
         </is>
       </c>
+      <c r="AO31">
+        <v>1</v>
+      </c>
       <c r="AP31">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="AQ31">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="AR31">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AS31">
-        <v>11</v>
+        <v>84</v>
       </c>
       <c r="AT31">
-        <v>84</v>
-      </c>
-      <c r="AU31">
         <v>14</v>
       </c>
     </row>
@@ -8553,22 +8573,22 @@
         <v>12</v>
       </c>
       <c r="X32">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="Y32">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="Z32">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="AA32">
-        <v>2.2</v>
+        <v>250</v>
       </c>
       <c r="AB32">
-        <v>250</v>
+        <v>320</v>
       </c>
       <c r="AC32">
-        <v>320</v>
+        <v>3</v>
       </c>
       <c r="AD32">
         <v>3</v>
@@ -8580,54 +8600,51 @@
         <v>3</v>
       </c>
       <c r="AG32">
-        <v>3</v>
-      </c>
-      <c r="AH32">
         <v>2</v>
       </c>
-      <c r="AI32" t="inlineStr">
+      <c r="AH32" t="inlineStr">
         <is>
           <t xml:space="preserve">Round</t>
         </is>
       </c>
-      <c r="AJ32">
+      <c r="AI32">
         <v>1.1</v>
       </c>
-      <c r="AK32" t="inlineStr">
+      <c r="AJ32" t="inlineStr">
         <is>
           <t xml:space="preserve">1-2</t>
         </is>
       </c>
+      <c r="AK32">
+        <v>3.5</v>
+      </c>
       <c r="AL32">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="AM32">
-        <v>2</v>
-      </c>
-      <c r="AN32">
         <v>1.9</v>
       </c>
-      <c r="AO32" t="inlineStr">
+      <c r="AN32" t="inlineStr">
         <is>
           <t xml:space="preserve">Oak</t>
         </is>
       </c>
+      <c r="AO32">
+        <v>1</v>
+      </c>
       <c r="AP32">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="AQ32">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="AR32">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AS32">
-        <v>9</v>
+        <v>78</v>
       </c>
       <c r="AT32">
-        <v>78</v>
-      </c>
-      <c r="AU32">
         <v>10</v>
       </c>
     </row>
@@ -8715,22 +8732,22 @@
         <v>12</v>
       </c>
       <c r="X33">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="Y33">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="Z33">
-        <v>3.7</v>
+        <v>2.1</v>
       </c>
       <c r="AA33">
-        <v>2.1</v>
+        <v>230</v>
       </c>
       <c r="AB33">
-        <v>230</v>
+        <v>300</v>
       </c>
       <c r="AC33">
-        <v>300</v>
+        <v>3</v>
       </c>
       <c r="AD33">
         <v>3</v>
@@ -8742,52 +8759,49 @@
         <v>3</v>
       </c>
       <c r="AG33">
-        <v>3</v>
-      </c>
-      <c r="AH33">
         <v>2</v>
       </c>
-      <c r="AI33" t="inlineStr">
+      <c r="AH33" t="inlineStr">
         <is>
           <t xml:space="preserve">Transom</t>
         </is>
       </c>
+      <c r="AI33">
+        <v>1.1</v>
+      </c>
       <c r="AJ33">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AK33">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="AL33">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="AM33">
-        <v>2</v>
-      </c>
-      <c r="AN33">
         <v>1.9</v>
       </c>
-      <c r="AO33" t="inlineStr">
+      <c r="AN33" t="inlineStr">
         <is>
           <t xml:space="preserve">Oak</t>
         </is>
       </c>
+      <c r="AO33">
+        <v>1</v>
+      </c>
       <c r="AP33">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="AQ33">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="AR33">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AS33">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="AT33">
-        <v>70</v>
-      </c>
-      <c r="AU33">
         <v>14</v>
       </c>
     </row>
@@ -8875,79 +8889,76 @@
         <v>11</v>
       </c>
       <c r="X34">
+        <v>4.5</v>
+      </c>
+      <c r="Y34">
+        <v>4</v>
+      </c>
+      <c r="Z34">
+        <v>2.2</v>
+      </c>
+      <c r="AA34">
+        <v>210</v>
+      </c>
+      <c r="AB34">
+        <v>270</v>
+      </c>
+      <c r="AC34">
+        <v>4</v>
+      </c>
+      <c r="AD34">
+        <v>2</v>
+      </c>
+      <c r="AE34">
+        <v>3</v>
+      </c>
+      <c r="AF34">
+        <v>2</v>
+      </c>
+      <c r="AG34">
+        <v>1</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transom</t>
+        </is>
+      </c>
+      <c r="AI34">
+        <v>1.2</v>
+      </c>
+      <c r="AJ34">
+        <v>1</v>
+      </c>
+      <c r="AK34">
+        <v>3.5</v>
+      </c>
+      <c r="AL34">
+        <v>2</v>
+      </c>
+      <c r="AM34">
+        <v>1.8</v>
+      </c>
+      <c r="AN34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oak</t>
+        </is>
+      </c>
+      <c r="AO34">
+        <v>1</v>
+      </c>
+      <c r="AP34">
+        <v>30</v>
+      </c>
+      <c r="AQ34">
+        <v>7</v>
+      </c>
+      <c r="AR34">
         <v>11</v>
       </c>
-      <c r="Y34">
-        <v>4.5</v>
-      </c>
-      <c r="Z34">
-        <v>4</v>
-      </c>
-      <c r="AA34">
-        <v>2.2</v>
-      </c>
-      <c r="AB34">
-        <v>210</v>
-      </c>
-      <c r="AC34">
-        <v>270</v>
-      </c>
-      <c r="AD34">
-        <v>4</v>
-      </c>
-      <c r="AE34">
-        <v>2</v>
-      </c>
-      <c r="AF34">
-        <v>3</v>
-      </c>
-      <c r="AG34">
-        <v>2</v>
-      </c>
-      <c r="AH34">
-        <v>1</v>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transom</t>
-        </is>
-      </c>
-      <c r="AJ34">
-        <v>1.2</v>
-      </c>
-      <c r="AK34">
-        <v>1</v>
-      </c>
-      <c r="AL34">
-        <v>3.5</v>
-      </c>
-      <c r="AM34">
-        <v>2</v>
-      </c>
-      <c r="AN34">
-        <v>1.8</v>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Oak</t>
-        </is>
-      </c>
-      <c r="AP34">
-        <v>1</v>
-      </c>
-      <c r="AQ34">
-        <v>30</v>
-      </c>
-      <c r="AR34">
-        <v>7</v>
-      </c>
       <c r="AS34">
-        <v>11</v>
+        <v>85</v>
       </c>
       <c r="AT34">
-        <v>85</v>
-      </c>
-      <c r="AU34">
         <v>12</v>
       </c>
     </row>
@@ -9035,79 +9046,76 @@
         <v>11</v>
       </c>
       <c r="X35">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="Y35">
+        <v>4.2</v>
+      </c>
+      <c r="Z35">
+        <v>2.2</v>
+      </c>
+      <c r="AA35">
+        <v>230</v>
+      </c>
+      <c r="AB35">
+        <v>300</v>
+      </c>
+      <c r="AC35">
+        <v>5</v>
+      </c>
+      <c r="AD35">
+        <v>2</v>
+      </c>
+      <c r="AE35">
         <v>4</v>
       </c>
-      <c r="Z35">
-        <v>4.2</v>
-      </c>
-      <c r="AA35">
-        <v>2.2</v>
-      </c>
-      <c r="AB35">
-        <v>230</v>
-      </c>
-      <c r="AC35">
-        <v>300</v>
-      </c>
-      <c r="AD35">
-        <v>5</v>
-      </c>
-      <c r="AE35">
+      <c r="AF35">
+        <v>3</v>
+      </c>
+      <c r="AG35">
+        <v>1</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Raking transom</t>
+        </is>
+      </c>
+      <c r="AI35">
+        <v>1.3</v>
+      </c>
+      <c r="AJ35">
+        <v>1</v>
+      </c>
+      <c r="AK35">
+        <v>3.5</v>
+      </c>
+      <c r="AL35">
         <v>2</v>
       </c>
-      <c r="AF35">
-        <v>4</v>
-      </c>
-      <c r="AG35">
-        <v>3</v>
-      </c>
-      <c r="AH35">
-        <v>1</v>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Raking transom</t>
-        </is>
-      </c>
-      <c r="AJ35">
-        <v>1.3</v>
-      </c>
-      <c r="AK35">
-        <v>1</v>
-      </c>
-      <c r="AL35">
-        <v>3.5</v>
-      </c>
       <c r="AM35">
-        <v>2</v>
-      </c>
-      <c r="AN35">
         <v>1.7</v>
       </c>
-      <c r="AO35" t="inlineStr">
+      <c r="AN35" t="inlineStr">
         <is>
           <t xml:space="preserve">Oak</t>
         </is>
       </c>
+      <c r="AO35">
+        <v>1</v>
+      </c>
       <c r="AP35">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="AQ35">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="AR35">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AS35">
-        <v>13</v>
+        <v>84</v>
       </c>
       <c r="AT35">
-        <v>84</v>
-      </c>
-      <c r="AU35">
         <v>12</v>
       </c>
     </row>
@@ -9190,22 +9198,22 @@
         <v>13</v>
       </c>
       <c r="X36">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="Y36">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="Z36">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="AA36">
-        <v>2.1</v>
+        <v>300</v>
       </c>
       <c r="AB36">
-        <v>300</v>
+        <v>380</v>
       </c>
       <c r="AC36">
-        <v>380</v>
+        <v>3</v>
       </c>
       <c r="AD36">
         <v>3</v>
@@ -9217,52 +9225,49 @@
         <v>3</v>
       </c>
       <c r="AG36">
-        <v>3</v>
-      </c>
-      <c r="AH36">
         <v>2</v>
       </c>
-      <c r="AI36" t="inlineStr">
+      <c r="AH36" t="inlineStr">
         <is>
           <t xml:space="preserve">Transom</t>
         </is>
       </c>
+      <c r="AI36">
+        <v>1.1</v>
+      </c>
       <c r="AJ36">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AK36">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AL36">
-        <v>4</v>
+        <v>2.25</v>
       </c>
       <c r="AM36">
-        <v>2.25</v>
-      </c>
-      <c r="AN36">
         <v>1.9</v>
       </c>
-      <c r="AO36" t="inlineStr">
+      <c r="AN36" t="inlineStr">
         <is>
           <t xml:space="preserve">Oak</t>
         </is>
       </c>
+      <c r="AO36">
+        <v>1</v>
+      </c>
       <c r="AP36">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="AQ36">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="AR36">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AS36">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="AT36">
-        <v>66</v>
-      </c>
-      <c r="AU36">
         <v>16</v>
       </c>
     </row>
@@ -9345,22 +9350,22 @@
         <v>13</v>
       </c>
       <c r="X37">
-        <v>13</v>
+        <v>5.5</v>
       </c>
       <c r="Y37">
-        <v>5.5</v>
+        <v>3.3</v>
       </c>
       <c r="Z37">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="AA37">
-        <v>2.3</v>
+        <v>380</v>
       </c>
       <c r="AB37">
-        <v>380</v>
+        <v>480</v>
       </c>
       <c r="AC37">
-        <v>480</v>
+        <v>3</v>
       </c>
       <c r="AD37">
         <v>3</v>
@@ -9372,52 +9377,49 @@
         <v>3</v>
       </c>
       <c r="AG37">
-        <v>3</v>
-      </c>
-      <c r="AH37">
         <v>2</v>
       </c>
-      <c r="AI37" t="inlineStr">
+      <c r="AH37" t="inlineStr">
         <is>
           <t xml:space="preserve">Round</t>
         </is>
       </c>
+      <c r="AI37">
+        <v>1.1</v>
+      </c>
       <c r="AJ37">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AK37">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AL37">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="AM37">
-        <v>2.5</v>
-      </c>
-      <c r="AN37">
         <v>1.9</v>
       </c>
-      <c r="AO37" t="inlineStr">
+      <c r="AN37" t="inlineStr">
         <is>
           <t xml:space="preserve">Oak</t>
         </is>
       </c>
+      <c r="AO37">
+        <v>1</v>
+      </c>
       <c r="AP37">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="AQ37">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="AR37">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AS37">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="AT37">
-        <v>65</v>
-      </c>
-      <c r="AU37">
         <v>18</v>
       </c>
     </row>
@@ -9500,79 +9502,76 @@
         <v>9</v>
       </c>
       <c r="X38">
+        <v>4</v>
+      </c>
+      <c r="Y38">
+        <v>3.8</v>
+      </c>
+      <c r="Z38">
+        <v>2.4</v>
+      </c>
+      <c r="AA38">
+        <v>180</v>
+      </c>
+      <c r="AB38">
+        <v>230</v>
+      </c>
+      <c r="AC38">
+        <v>3</v>
+      </c>
+      <c r="AD38">
+        <v>2</v>
+      </c>
+      <c r="AE38">
+        <v>3</v>
+      </c>
+      <c r="AF38">
+        <v>2</v>
+      </c>
+      <c r="AG38">
+        <v>1</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transom</t>
+        </is>
+      </c>
+      <c r="AI38">
+        <v>1</v>
+      </c>
+      <c r="AJ38">
+        <v>1</v>
+      </c>
+      <c r="AK38">
+        <v>3.5</v>
+      </c>
+      <c r="AL38">
+        <v>2</v>
+      </c>
+      <c r="AM38">
+        <v>1.8</v>
+      </c>
+      <c r="AN38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oak</t>
+        </is>
+      </c>
+      <c r="AO38">
+        <v>1</v>
+      </c>
+      <c r="AP38">
+        <v>40</v>
+      </c>
+      <c r="AQ38">
+        <v>5</v>
+      </c>
+      <c r="AR38">
         <v>9</v>
       </c>
-      <c r="Y38">
-        <v>4</v>
-      </c>
-      <c r="Z38">
-        <v>3.8</v>
-      </c>
-      <c r="AA38">
-        <v>2.4</v>
-      </c>
-      <c r="AB38">
-        <v>180</v>
-      </c>
-      <c r="AC38">
-        <v>230</v>
-      </c>
-      <c r="AD38">
-        <v>3</v>
-      </c>
-      <c r="AE38">
-        <v>2</v>
-      </c>
-      <c r="AF38">
-        <v>3</v>
-      </c>
-      <c r="AG38">
-        <v>2</v>
-      </c>
-      <c r="AH38">
-        <v>1</v>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transom</t>
-        </is>
-      </c>
-      <c r="AJ38">
-        <v>1</v>
-      </c>
-      <c r="AK38">
-        <v>1</v>
-      </c>
-      <c r="AL38">
-        <v>3.5</v>
-      </c>
-      <c r="AM38">
-        <v>2</v>
-      </c>
-      <c r="AN38">
-        <v>1.8</v>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Oak</t>
-        </is>
-      </c>
-      <c r="AP38">
-        <v>1</v>
-      </c>
-      <c r="AQ38">
-        <v>40</v>
-      </c>
-      <c r="AR38">
-        <v>5</v>
-      </c>
       <c r="AS38">
-        <v>9</v>
+        <v>71</v>
       </c>
       <c r="AT38">
-        <v>71</v>
-      </c>
-      <c r="AU38">
         <v>12</v>
       </c>
     </row>
@@ -9660,28 +9659,28 @@
         <v>13</v>
       </c>
       <c r="X39">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="Y39">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="Z39">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="AA39">
-        <v>2.2</v>
+        <v>380</v>
       </c>
       <c r="AB39">
-        <v>380</v>
+        <v>480</v>
       </c>
       <c r="AC39">
-        <v>480</v>
+        <v>2</v>
       </c>
       <c r="AD39">
+        <v>3</v>
+      </c>
+      <c r="AE39">
         <v>2</v>
-      </c>
-      <c r="AE39">
-        <v>3</v>
       </c>
       <c r="AF39">
         <v>2</v>
@@ -9689,50 +9688,47 @@
       <c r="AG39">
         <v>2</v>
       </c>
-      <c r="AH39">
-        <v>2</v>
-      </c>
-      <c r="AI39" t="inlineStr">
+      <c r="AH39" t="inlineStr">
         <is>
           <t xml:space="preserve">Round</t>
         </is>
       </c>
+      <c r="AI39">
+        <v>1</v>
+      </c>
       <c r="AJ39">
         <v>1</v>
       </c>
       <c r="AK39">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AL39">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AM39">
-        <v>3</v>
-      </c>
-      <c r="AN39">
         <v>1.9</v>
       </c>
-      <c r="AO39" t="inlineStr">
+      <c r="AN39" t="inlineStr">
         <is>
           <t xml:space="preserve">Oak</t>
         </is>
       </c>
+      <c r="AO39">
+        <v>1</v>
+      </c>
       <c r="AP39">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="AQ39">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="AR39">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AS39">
-        <v>8</v>
+        <v>68</v>
       </c>
       <c r="AT39">
-        <v>68</v>
-      </c>
-      <c r="AU39">
         <v>10</v>
       </c>
     </row>
@@ -9820,22 +9816,22 @@
         <v>7</v>
       </c>
       <c r="X40">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y40">
         <v>4</v>
       </c>
       <c r="Z40">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="AA40">
-        <v>2.1</v>
+        <v>60</v>
       </c>
       <c r="AB40">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AC40">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="AD40">
         <v>3</v>
@@ -9849,50 +9845,47 @@
       <c r="AG40">
         <v>3</v>
       </c>
-      <c r="AH40">
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Square</t>
+        </is>
+      </c>
+      <c r="AI40">
+        <v>1</v>
+      </c>
+      <c r="AJ40">
+        <v>1</v>
+      </c>
+      <c r="AK40">
         <v>3</v>
       </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Square</t>
-        </is>
-      </c>
-      <c r="AJ40">
-        <v>1</v>
-      </c>
-      <c r="AK40">
-        <v>1</v>
-      </c>
       <c r="AL40">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="AM40">
-        <v>1.75</v>
-      </c>
-      <c r="AN40">
         <v>1.8</v>
       </c>
-      <c r="AO40" t="inlineStr">
+      <c r="AN40" t="inlineStr">
         <is>
           <t xml:space="preserve">Oak</t>
         </is>
       </c>
+      <c r="AO40">
+        <v>1</v>
+      </c>
       <c r="AP40">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="AQ40">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="AR40">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AS40">
-        <v>9</v>
+        <v>66</v>
       </c>
       <c r="AT40">
-        <v>66</v>
-      </c>
-      <c r="AU40">
         <v>8</v>
       </c>
     </row>
@@ -9977,82 +9970,79 @@
         <v>28</v>
       </c>
       <c r="W41">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X41">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="Y41">
+        <v>4.1</v>
+      </c>
+      <c r="Z41">
+        <v>2.8</v>
+      </c>
+      <c r="AA41">
+        <v>350</v>
+      </c>
+      <c r="AB41">
+        <v>450</v>
+      </c>
+      <c r="AC41">
         <v>5</v>
       </c>
-      <c r="Z41">
-        <v>4.1</v>
-      </c>
-      <c r="AA41">
-        <v>2.8</v>
-      </c>
-      <c r="AB41">
-        <v>350</v>
-      </c>
-      <c r="AC41">
-        <v>450</v>
-      </c>
       <c r="AD41">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE41">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AF41">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG41">
-        <v>3</v>
-      </c>
-      <c r="AH41">
         <v>2</v>
       </c>
-      <c r="AI41" t="inlineStr">
+      <c r="AH41" t="inlineStr">
         <is>
           <t xml:space="preserve">Overhanging</t>
         </is>
       </c>
+      <c r="AI41">
+        <v>1.2</v>
+      </c>
       <c r="AJ41">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AK41">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="AL41">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="AM41">
-        <v>2</v>
-      </c>
-      <c r="AN41">
         <v>1.8</v>
       </c>
-      <c r="AO41" t="inlineStr">
+      <c r="AN41" t="inlineStr">
         <is>
           <t xml:space="preserve">Oak</t>
         </is>
       </c>
+      <c r="AO41">
+        <v>1</v>
+      </c>
       <c r="AP41">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="AQ41">
-        <v>120</v>
+        <v>7</v>
       </c>
       <c r="AR41">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AS41">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="AT41">
-        <v>82</v>
-      </c>
-      <c r="AU41">
         <v>32</v>
       </c>
     </row>
@@ -10132,84 +10122,81 @@
         <v>24</v>
       </c>
       <c r="W42">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X42">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="Y42">
+        <v>4.2</v>
+      </c>
+      <c r="Z42">
+        <v>2.2</v>
+      </c>
+      <c r="AA42">
+        <v>300</v>
+      </c>
+      <c r="AB42">
+        <v>400</v>
+      </c>
+      <c r="AC42">
+        <v>2</v>
+      </c>
+      <c r="AD42">
         <v>5</v>
       </c>
-      <c r="Z42">
-        <v>4.2</v>
-      </c>
-      <c r="AA42">
-        <v>2.2</v>
-      </c>
-      <c r="AB42">
-        <v>300</v>
-      </c>
-      <c r="AC42">
-        <v>400</v>
-      </c>
-      <c r="AD42">
+      <c r="AE42">
         <v>2</v>
       </c>
-      <c r="AE42">
-        <v>5</v>
-      </c>
       <c r="AF42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG42">
         <v>3</v>
       </c>
-      <c r="AH42">
-        <v>3</v>
-      </c>
-      <c r="AI42" t="inlineStr">
+      <c r="AH42" t="inlineStr">
         <is>
           <t xml:space="preserve">Pear</t>
         </is>
       </c>
-      <c r="AJ42">
-        <v>1</v>
-      </c>
-      <c r="AK42" t="inlineStr">
+      <c r="AI42">
+        <v>1</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
         <is>
           <t xml:space="preserve">1-2</t>
         </is>
       </c>
+      <c r="AK42">
+        <v>3.5</v>
+      </c>
       <c r="AL42">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="AM42">
-        <v>2</v>
-      </c>
-      <c r="AN42">
         <v>1.9</v>
       </c>
-      <c r="AO42" t="inlineStr">
+      <c r="AN42" t="inlineStr">
         <is>
           <t xml:space="preserve">Oak</t>
         </is>
       </c>
+      <c r="AO42">
+        <v>1</v>
+      </c>
       <c r="AP42">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="AQ42">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="AR42">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AS42">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="AT42">
-        <v>49</v>
-      </c>
-      <c r="AU42">
         <v>16</v>
       </c>
     </row>
@@ -10292,22 +10279,22 @@
         <v>13</v>
       </c>
       <c r="X43">
-        <v>13</v>
+        <v>5.5</v>
       </c>
       <c r="Y43">
-        <v>5.5</v>
+        <v>3.7</v>
       </c>
       <c r="Z43">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
       <c r="AA43">
-        <v>2.2</v>
+        <v>370</v>
       </c>
       <c r="AB43">
-        <v>370</v>
+        <v>470</v>
       </c>
       <c r="AC43">
-        <v>470</v>
+        <v>3</v>
       </c>
       <c r="AD43">
         <v>3</v>
@@ -10319,52 +10306,49 @@
         <v>3</v>
       </c>
       <c r="AG43">
-        <v>3</v>
-      </c>
-      <c r="AH43">
         <v>2</v>
       </c>
-      <c r="AI43" t="inlineStr">
+      <c r="AH43" t="inlineStr">
         <is>
           <t xml:space="preserve">Round</t>
         </is>
       </c>
+      <c r="AI43">
+        <v>1.1</v>
+      </c>
       <c r="AJ43">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AK43">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AL43">
-        <v>4</v>
+        <v>2.25</v>
       </c>
       <c r="AM43">
-        <v>2.25</v>
-      </c>
-      <c r="AN43">
         <v>1.9</v>
       </c>
-      <c r="AO43" t="inlineStr">
+      <c r="AN43" t="inlineStr">
         <is>
           <t xml:space="preserve">Oak</t>
         </is>
       </c>
+      <c r="AO43">
+        <v>1</v>
+      </c>
       <c r="AP43">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="AQ43">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="AR43">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AS43">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="AT43">
-        <v>63</v>
-      </c>
-      <c r="AU43">
         <v>14</v>
       </c>
     </row>
@@ -10452,25 +10436,25 @@
         <v>14</v>
       </c>
       <c r="X44">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="Y44">
-        <v>6</v>
+        <v>3.7</v>
       </c>
       <c r="Z44">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
       <c r="AA44">
-        <v>2.2</v>
+        <v>450</v>
       </c>
       <c r="AB44">
-        <v>450</v>
+        <v>570</v>
       </c>
       <c r="AC44">
-        <v>570</v>
+        <v>4</v>
       </c>
       <c r="AD44">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE44">
         <v>3</v>
@@ -10479,52 +10463,49 @@
         <v>3</v>
       </c>
       <c r="AG44">
-        <v>3</v>
-      </c>
-      <c r="AH44">
         <v>2</v>
       </c>
-      <c r="AI44" t="inlineStr">
+      <c r="AH44" t="inlineStr">
         <is>
           <t xml:space="preserve">Round</t>
         </is>
       </c>
+      <c r="AI44">
+        <v>1.2</v>
+      </c>
       <c r="AJ44">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AK44">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AL44">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="AM44">
-        <v>2.5</v>
-      </c>
-      <c r="AN44">
         <v>1.9</v>
       </c>
-      <c r="AO44" t="inlineStr">
+      <c r="AN44" t="inlineStr">
         <is>
           <t xml:space="preserve">Oak</t>
         </is>
       </c>
+      <c r="AO44">
+        <v>1</v>
+      </c>
       <c r="AP44">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="AQ44">
-        <v>90</v>
+        <v>7</v>
       </c>
       <c r="AR44">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AS44">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="AT44">
-        <v>65</v>
-      </c>
-      <c r="AU44">
         <v>22</v>
       </c>
     </row>
@@ -10604,84 +10585,81 @@
         <v>40</v>
       </c>
       <c r="W45">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="X45">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="Y45">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="Z45">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AA45">
-        <v>2.5</v>
+        <v>700</v>
       </c>
       <c r="AB45">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="AC45">
-        <v>900</v>
+        <v>1</v>
       </c>
       <c r="AD45">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE45">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AF45">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG45">
         <v>5</v>
       </c>
-      <c r="AH45">
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Square castle</t>
+        </is>
+      </c>
+      <c r="AI45">
+        <v>0.9</v>
+      </c>
+      <c r="AJ45">
+        <v>2</v>
+      </c>
+      <c r="AK45">
         <v>5</v>
       </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Square castle</t>
-        </is>
-      </c>
-      <c r="AJ45">
-        <v>0.9</v>
-      </c>
-      <c r="AK45">
+      <c r="AL45">
+        <v>3</v>
+      </c>
+      <c r="AM45">
         <v>2</v>
       </c>
-      <c r="AL45">
-        <v>5</v>
-      </c>
-      <c r="AM45">
+      <c r="AN45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oak</t>
+        </is>
+      </c>
+      <c r="AO45">
+        <v>1</v>
+      </c>
+      <c r="AP45">
+        <v>100</v>
+      </c>
+      <c r="AQ45">
         <v>3</v>
       </c>
-      <c r="AN45">
-        <v>2</v>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Oak</t>
-        </is>
-      </c>
-      <c r="AP45">
-        <v>1</v>
-      </c>
-      <c r="AQ45">
-        <v>100</v>
-      </c>
       <c r="AR45">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AS45">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="AT45">
         <v>30</v>
       </c>
-      <c r="AU45">
-        <v>30</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -10767,25 +10745,25 @@
         <v>12</v>
       </c>
       <c r="X46">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="Y46">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="Z46">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="AA46">
-        <v>2.8</v>
+        <v>520</v>
       </c>
       <c r="AB46">
-        <v>520</v>
+        <v>660</v>
       </c>
       <c r="AC46">
-        <v>660</v>
+        <v>4</v>
       </c>
       <c r="AD46">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE46">
         <v>3</v>
@@ -10794,54 +10772,51 @@
         <v>3</v>
       </c>
       <c r="AG46">
-        <v>3</v>
-      </c>
-      <c r="AH46">
         <v>2</v>
       </c>
-      <c r="AI46" t="inlineStr">
+      <c r="AH46" t="inlineStr">
         <is>
           <t xml:space="preserve">Round</t>
         </is>
       </c>
-      <c r="AJ46">
+      <c r="AI46">
         <v>1.2</v>
       </c>
-      <c r="AK46" t="inlineStr">
+      <c r="AJ46" t="inlineStr">
         <is>
           <t xml:space="preserve">1-2</t>
         </is>
       </c>
+      <c r="AK46">
+        <v>4</v>
+      </c>
       <c r="AL46">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="AM46">
-        <v>2.5</v>
-      </c>
-      <c r="AN46">
         <v>1.9</v>
       </c>
-      <c r="AO46" t="inlineStr">
+      <c r="AN46" t="inlineStr">
         <is>
           <t xml:space="preserve">Oak</t>
         </is>
       </c>
+      <c r="AO46">
+        <v>1</v>
+      </c>
       <c r="AP46">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="AQ46">
-        <v>120</v>
+        <v>7</v>
       </c>
       <c r="AR46">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AS46">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="AT46">
-        <v>62</v>
-      </c>
-      <c r="AU46">
         <v>28</v>
       </c>
     </row>
@@ -10921,82 +10896,79 @@
         <v>33</v>
       </c>
       <c r="W47">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X47">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="Y47">
-        <v>9</v>
+        <v>4.2</v>
       </c>
       <c r="Z47">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="AA47">
-        <v>2.2</v>
+        <v>500</v>
       </c>
       <c r="AB47">
-        <v>500</v>
+        <v>640</v>
       </c>
       <c r="AC47">
-        <v>640</v>
+        <v>4</v>
       </c>
       <c r="AD47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE47">
         <v>3</v>
       </c>
       <c r="AF47">
+        <v>4</v>
+      </c>
+      <c r="AG47">
         <v>3</v>
       </c>
-      <c r="AG47">
-        <v>4</v>
-      </c>
-      <c r="AH47">
-        <v>3</v>
-      </c>
-      <c r="AI47" t="inlineStr">
+      <c r="AH47" t="inlineStr">
         <is>
           <t xml:space="preserve">Square gallery</t>
         </is>
       </c>
+      <c r="AI47">
+        <v>1</v>
+      </c>
       <c r="AJ47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK47">
+        <v>4.5</v>
+      </c>
+      <c r="AL47">
+        <v>2.75</v>
+      </c>
+      <c r="AM47">
         <v>2</v>
       </c>
-      <c r="AL47">
-        <v>4.5</v>
-      </c>
-      <c r="AM47">
-        <v>2.75</v>
-      </c>
-      <c r="AN47">
-        <v>2</v>
-      </c>
-      <c r="AO47" t="inlineStr">
+      <c r="AN47" t="inlineStr">
         <is>
           <t xml:space="preserve">Oak</t>
         </is>
       </c>
+      <c r="AO47">
+        <v>1</v>
+      </c>
       <c r="AP47">
-        <v>1</v>
+        <v>150</v>
       </c>
       <c r="AQ47">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="AR47">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AS47">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="AT47">
-        <v>52</v>
-      </c>
-      <c r="AU47">
         <v>40</v>
       </c>
     </row>
@@ -11076,82 +11048,79 @@
         <v>38</v>
       </c>
       <c r="W48">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X48">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="Y48">
-        <v>12</v>
+        <v>3.4</v>
       </c>
       <c r="Z48">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="AA48">
-        <v>2.2</v>
+        <v>700</v>
       </c>
       <c r="AB48">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="AC48">
-        <v>900</v>
+        <v>3</v>
       </c>
       <c r="AD48">
+        <v>4</v>
+      </c>
+      <c r="AE48">
         <v>3</v>
       </c>
-      <c r="AE48">
+      <c r="AF48">
         <v>4</v>
-      </c>
-      <c r="AF48">
-        <v>3</v>
       </c>
       <c r="AG48">
         <v>4</v>
       </c>
-      <c r="AH48">
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Square gallery</t>
+        </is>
+      </c>
+      <c r="AI48">
+        <v>0.95</v>
+      </c>
+      <c r="AJ48">
+        <v>2</v>
+      </c>
+      <c r="AK48">
+        <v>5</v>
+      </c>
+      <c r="AL48">
+        <v>3</v>
+      </c>
+      <c r="AM48">
+        <v>2</v>
+      </c>
+      <c r="AN48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oak</t>
+        </is>
+      </c>
+      <c r="AO48">
+        <v>1</v>
+      </c>
+      <c r="AP48">
+        <v>180</v>
+      </c>
+      <c r="AQ48">
         <v>4</v>
       </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Square gallery</t>
-        </is>
-      </c>
-      <c r="AJ48">
-        <v>0.95</v>
-      </c>
-      <c r="AK48">
-        <v>2</v>
-      </c>
-      <c r="AL48">
-        <v>5</v>
-      </c>
-      <c r="AM48">
-        <v>3</v>
-      </c>
-      <c r="AN48">
-        <v>2</v>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Oak</t>
-        </is>
-      </c>
-      <c r="AP48">
-        <v>1</v>
-      </c>
-      <c r="AQ48">
-        <v>180</v>
-      </c>
       <c r="AR48">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AS48">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="AT48">
-        <v>43</v>
-      </c>
-      <c r="AU48">
         <v>48</v>
       </c>
     </row>
@@ -11239,25 +11208,25 @@
         <v>14</v>
       </c>
       <c r="X49">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="Y49">
-        <v>7</v>
+        <v>3.75</v>
       </c>
       <c r="Z49">
-        <v>3.75</v>
+        <v>2.9</v>
       </c>
       <c r="AA49">
-        <v>2.9</v>
+        <v>950</v>
       </c>
       <c r="AB49">
-        <v>950</v>
+        <v>1200</v>
       </c>
       <c r="AC49">
-        <v>1200</v>
+        <v>4</v>
       </c>
       <c r="AD49">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE49">
         <v>3</v>
@@ -11266,52 +11235,49 @@
         <v>3</v>
       </c>
       <c r="AG49">
-        <v>3</v>
-      </c>
-      <c r="AH49">
         <v>2</v>
       </c>
-      <c r="AI49" t="inlineStr">
+      <c r="AH49" t="inlineStr">
         <is>
           <t xml:space="preserve">Gallery</t>
         </is>
       </c>
+      <c r="AI49">
+        <v>1.2</v>
+      </c>
       <c r="AJ49">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="AK49">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="AL49">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
       <c r="AM49">
-        <v>2.75</v>
-      </c>
-      <c r="AN49">
         <v>1.9</v>
       </c>
-      <c r="AO49" t="inlineStr">
+      <c r="AN49" t="inlineStr">
         <is>
           <t xml:space="preserve">Oak</t>
         </is>
       </c>
+      <c r="AO49">
+        <v>1</v>
+      </c>
       <c r="AP49">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="AQ49">
-        <v>200</v>
+        <v>8</v>
       </c>
       <c r="AR49">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AS49">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="AT49">
-        <v>59</v>
-      </c>
-      <c r="AU49">
         <v>38</v>
       </c>
     </row>
@@ -11394,79 +11360,76 @@
         <v>21</v>
       </c>
       <c r="X50">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="Y50">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z50">
+        <v>1.9</v>
+      </c>
+      <c r="AA50">
+        <v>1100</v>
+      </c>
+      <c r="AB50">
+        <v>1400</v>
+      </c>
+      <c r="AC50">
         <v>5</v>
       </c>
-      <c r="AA50">
-        <v>1.9</v>
-      </c>
-      <c r="AB50">
-        <v>1100</v>
-      </c>
-      <c r="AC50">
-        <v>1400</v>
-      </c>
       <c r="AD50">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE50">
+        <v>4</v>
+      </c>
+      <c r="AF50">
+        <v>3</v>
+      </c>
+      <c r="AG50">
+        <v>1</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elliptical</t>
+        </is>
+      </c>
+      <c r="AI50">
+        <v>1.5</v>
+      </c>
+      <c r="AJ50">
         <v>2</v>
       </c>
-      <c r="AF50">
-        <v>4</v>
-      </c>
-      <c r="AG50">
-        <v>3</v>
-      </c>
-      <c r="AH50">
-        <v>1</v>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Elliptical</t>
-        </is>
-      </c>
-      <c r="AJ50">
-        <v>1.5</v>
-      </c>
       <c r="AK50">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="AL50">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
       <c r="AM50">
-        <v>2.75</v>
-      </c>
-      <c r="AN50">
         <v>1.8</v>
       </c>
-      <c r="AO50" t="inlineStr">
+      <c r="AN50" t="inlineStr">
         <is>
           <t xml:space="preserve">Teak</t>
         </is>
       </c>
+      <c r="AO50">
+        <v>1.12</v>
+      </c>
       <c r="AP50">
-        <v>1.12</v>
+        <v>40</v>
       </c>
       <c r="AQ50">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="AR50">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AS50">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="AT50">
-        <v>59</v>
-      </c>
-      <c r="AU50">
         <v>12</v>
       </c>
     </row>
@@ -11549,79 +11512,76 @@
         <v>18</v>
       </c>
       <c r="X51">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="Y51">
-        <v>8</v>
+        <v>3.9</v>
       </c>
       <c r="Z51">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="AA51">
-        <v>2.3</v>
+        <v>1200</v>
       </c>
       <c r="AB51">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="AC51">
-        <v>1500</v>
+        <v>3</v>
       </c>
       <c r="AD51">
+        <v>4</v>
+      </c>
+      <c r="AE51">
+        <v>2</v>
+      </c>
+      <c r="AF51">
         <v>3</v>
-      </c>
-      <c r="AE51">
-        <v>4</v>
-      </c>
-      <c r="AF51">
-        <v>2</v>
       </c>
       <c r="AG51">
         <v>3</v>
       </c>
-      <c r="AH51">
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gallery</t>
+        </is>
+      </c>
+      <c r="AI51">
+        <v>1.1</v>
+      </c>
+      <c r="AJ51">
+        <v>2</v>
+      </c>
+      <c r="AK51">
+        <v>5</v>
+      </c>
+      <c r="AL51">
         <v>3</v>
       </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gallery</t>
-        </is>
-      </c>
-      <c r="AJ51">
-        <v>1.1</v>
-      </c>
-      <c r="AK51">
+      <c r="AM51">
         <v>2</v>
       </c>
-      <c r="AL51">
+      <c r="AN51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Teak</t>
+        </is>
+      </c>
+      <c r="AO51">
+        <v>1.12</v>
+      </c>
+      <c r="AP51">
+        <v>80</v>
+      </c>
+      <c r="AQ51">
         <v>5</v>
       </c>
-      <c r="AM51">
-        <v>3</v>
-      </c>
-      <c r="AN51">
-        <v>2</v>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Teak</t>
-        </is>
-      </c>
-      <c r="AP51">
-        <v>1.12</v>
-      </c>
-      <c r="AQ51">
-        <v>80</v>
-      </c>
       <c r="AR51">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AS51">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="AT51">
-        <v>41</v>
-      </c>
-      <c r="AU51">
         <v>30</v>
       </c>
     </row>
@@ -11709,25 +11669,25 @@
         <v>14</v>
       </c>
       <c r="X52">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="Y52">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Z52">
+        <v>3.1</v>
+      </c>
+      <c r="AA52">
+        <v>1500</v>
+      </c>
+      <c r="AB52">
+        <v>1900</v>
+      </c>
+      <c r="AC52">
         <v>4</v>
       </c>
-      <c r="AA52">
-        <v>3.1</v>
-      </c>
-      <c r="AB52">
-        <v>1500</v>
-      </c>
-      <c r="AC52">
-        <v>1900</v>
-      </c>
       <c r="AD52">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE52">
         <v>3</v>
@@ -11736,52 +11696,49 @@
         <v>3</v>
       </c>
       <c r="AG52">
-        <v>3</v>
-      </c>
-      <c r="AH52">
         <v>2</v>
       </c>
-      <c r="AI52" t="inlineStr">
+      <c r="AH52" t="inlineStr">
         <is>
           <t xml:space="preserve">Gallery</t>
         </is>
       </c>
+      <c r="AI52">
+        <v>1.3</v>
+      </c>
       <c r="AJ52">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="AK52">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="AL52">
-        <v>5.5</v>
+        <v>3.25</v>
       </c>
       <c r="AM52">
-        <v>3.25</v>
-      </c>
-      <c r="AN52">
         <v>1.9</v>
       </c>
-      <c r="AO52" t="inlineStr">
+      <c r="AN52" t="inlineStr">
         <is>
           <t xml:space="preserve">Live oak</t>
         </is>
       </c>
+      <c r="AO52">
+        <v>1.2</v>
+      </c>
       <c r="AP52">
-        <v>1.2</v>
+        <v>300</v>
       </c>
       <c r="AQ52">
-        <v>300</v>
+        <v>8</v>
       </c>
       <c r="AR52">
-        <v>8</v>
+        <v>13.5</v>
       </c>
       <c r="AS52">
-        <v>13.5</v>
+        <v>55</v>
       </c>
       <c r="AT52">
-        <v>55</v>
-      </c>
-      <c r="AU52">
         <v>50</v>
       </c>
     </row>
@@ -11864,79 +11821,76 @@
         <v>20</v>
       </c>
       <c r="X53">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="Y53">
-        <v>8</v>
+        <v>3.6</v>
       </c>
       <c r="Z53">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="AA53">
-        <v>2.4</v>
+        <v>1450</v>
       </c>
       <c r="AB53">
-        <v>1450</v>
+        <v>1850</v>
       </c>
       <c r="AC53">
-        <v>1850</v>
+        <v>4</v>
       </c>
       <c r="AD53">
         <v>4</v>
       </c>
       <c r="AE53">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF53">
         <v>3</v>
       </c>
       <c r="AG53">
-        <v>3</v>
-      </c>
-      <c r="AH53">
         <v>2</v>
       </c>
-      <c r="AI53" t="inlineStr">
+      <c r="AH53" t="inlineStr">
         <is>
           <t xml:space="preserve">Gallery</t>
         </is>
       </c>
+      <c r="AI53">
+        <v>1.2</v>
+      </c>
       <c r="AJ53">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="AK53">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AL53">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="AM53">
-        <v>3.5</v>
-      </c>
-      <c r="AN53">
         <v>1.9</v>
       </c>
-      <c r="AO53" t="inlineStr">
+      <c r="AN53" t="inlineStr">
         <is>
           <t xml:space="preserve">Oak</t>
         </is>
       </c>
+      <c r="AO53">
+        <v>1</v>
+      </c>
       <c r="AP53">
-        <v>1</v>
+        <v>280</v>
       </c>
       <c r="AQ53">
-        <v>280</v>
+        <v>8</v>
       </c>
       <c r="AR53">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AS53">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="AT53">
-        <v>56</v>
-      </c>
-      <c r="AU53">
         <v>44</v>
       </c>
     </row>
@@ -12024,79 +11978,76 @@
         <v>18</v>
       </c>
       <c r="X54">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="Y54">
-        <v>8</v>
+        <v>3.6</v>
       </c>
       <c r="Z54">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="AA54">
-        <v>2.4</v>
+        <v>1050</v>
       </c>
       <c r="AB54">
-        <v>1050</v>
+        <v>1350</v>
       </c>
       <c r="AC54">
-        <v>1350</v>
+        <v>3</v>
       </c>
       <c r="AD54">
+        <v>4</v>
+      </c>
+      <c r="AE54">
         <v>3</v>
       </c>
-      <c r="AE54">
+      <c r="AF54">
         <v>4</v>
       </c>
-      <c r="AF54">
+      <c r="AG54">
         <v>3</v>
       </c>
-      <c r="AG54">
-        <v>4</v>
-      </c>
-      <c r="AH54">
-        <v>3</v>
-      </c>
-      <c r="AI54" t="inlineStr">
+      <c r="AH54" t="inlineStr">
         <is>
           <t xml:space="preserve">Gallery</t>
         </is>
       </c>
+      <c r="AI54">
+        <v>1.1</v>
+      </c>
       <c r="AJ54">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="AK54">
+        <v>5.5</v>
+      </c>
+      <c r="AL54">
+        <v>3.25</v>
+      </c>
+      <c r="AM54">
         <v>2</v>
       </c>
-      <c r="AL54">
-        <v>5.5</v>
-      </c>
-      <c r="AM54">
-        <v>3.25</v>
-      </c>
-      <c r="AN54">
-        <v>2</v>
-      </c>
-      <c r="AO54" t="inlineStr">
+      <c r="AN54" t="inlineStr">
         <is>
           <t xml:space="preserve">Oak</t>
         </is>
       </c>
+      <c r="AO54">
+        <v>1</v>
+      </c>
       <c r="AP54">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="AQ54">
-        <v>250</v>
+        <v>6</v>
       </c>
       <c r="AR54">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AS54">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="AT54">
-        <v>52</v>
-      </c>
-      <c r="AU54">
         <v>54</v>
       </c>
     </row>
@@ -12184,81 +12135,78 @@
         <v>21</v>
       </c>
       <c r="X55">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="Y55">
-        <v>9</v>
+        <v>3.7</v>
       </c>
       <c r="Z55">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="AA55">
-        <v>2.3</v>
+        <v>1700</v>
       </c>
       <c r="AB55">
-        <v>1700</v>
+        <v>2200</v>
       </c>
       <c r="AC55">
-        <v>2200</v>
+        <v>3</v>
       </c>
       <c r="AD55">
+        <v>4</v>
+      </c>
+      <c r="AE55">
         <v>3</v>
       </c>
-      <c r="AE55">
+      <c r="AF55">
         <v>4</v>
       </c>
-      <c r="AF55">
+      <c r="AG55">
         <v>3</v>
       </c>
-      <c r="AG55">
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gallery</t>
+        </is>
+      </c>
+      <c r="AI55">
+        <v>1.15</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2-3</t>
+        </is>
+      </c>
+      <c r="AK55">
+        <v>6.5</v>
+      </c>
+      <c r="AL55">
         <v>4</v>
       </c>
-      <c r="AH55">
-        <v>3</v>
-      </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gallery</t>
-        </is>
-      </c>
-      <c r="AJ55">
-        <v>1.15</v>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2-3</t>
-        </is>
-      </c>
-      <c r="AL55">
-        <v>6.5</v>
-      </c>
       <c r="AM55">
-        <v>4</v>
-      </c>
-      <c r="AN55">
         <v>2</v>
       </c>
-      <c r="AO55" t="inlineStr">
+      <c r="AN55" t="inlineStr">
         <is>
           <t xml:space="preserve">Oak</t>
         </is>
       </c>
+      <c r="AO55">
+        <v>1</v>
+      </c>
       <c r="AP55">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="AQ55">
-        <v>500</v>
+        <v>6</v>
       </c>
       <c r="AR55">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AS55">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="AT55">
-        <v>45</v>
-      </c>
-      <c r="AU55">
         <v>74</v>
       </c>
     </row>
@@ -12343,82 +12291,79 @@
         <v>51</v>
       </c>
       <c r="W56">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X56">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="Y56">
-        <v>12</v>
+        <v>3.8</v>
       </c>
       <c r="Z56">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="AA56">
-        <v>2.3</v>
+        <v>2200</v>
       </c>
       <c r="AB56">
-        <v>2200</v>
+        <v>2900</v>
       </c>
       <c r="AC56">
-        <v>2900</v>
+        <v>2</v>
       </c>
       <c r="AD56">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE56">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AF56">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG56">
         <v>4</v>
       </c>
-      <c r="AH56">
-        <v>4</v>
-      </c>
-      <c r="AI56" t="inlineStr">
+      <c r="AH56" t="inlineStr">
         <is>
           <t xml:space="preserve">Gallery</t>
         </is>
       </c>
+      <c r="AI56">
+        <v>1.1</v>
+      </c>
       <c r="AJ56">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="AK56">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AL56">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="AM56">
-        <v>4.5</v>
-      </c>
-      <c r="AN56">
         <v>2</v>
       </c>
-      <c r="AO56" t="inlineStr">
+      <c r="AN56" t="inlineStr">
         <is>
           <t xml:space="preserve">Oak</t>
         </is>
       </c>
+      <c r="AO56">
+        <v>1</v>
+      </c>
       <c r="AP56">
-        <v>1</v>
+        <v>650</v>
       </c>
       <c r="AQ56">
-        <v>650</v>
+        <v>5</v>
       </c>
       <c r="AR56">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AS56">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="AT56">
-        <v>41</v>
-      </c>
-      <c r="AU56">
         <v>98</v>
       </c>
     </row>
@@ -12503,82 +12448,79 @@
         <v>53</v>
       </c>
       <c r="W57">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X57">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="Y57">
-        <v>13</v>
+        <v>3.9</v>
       </c>
       <c r="Z57">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="AA57">
-        <v>2.3</v>
+        <v>2500</v>
       </c>
       <c r="AB57">
-        <v>2500</v>
+        <v>3400</v>
       </c>
       <c r="AC57">
-        <v>3400</v>
+        <v>2</v>
       </c>
       <c r="AD57">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE57">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AF57">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG57">
         <v>4</v>
       </c>
-      <c r="AH57">
-        <v>4</v>
-      </c>
-      <c r="AI57" t="inlineStr">
+      <c r="AH57" t="inlineStr">
         <is>
           <t xml:space="preserve">Gallery</t>
         </is>
       </c>
+      <c r="AI57">
+        <v>1.1</v>
+      </c>
       <c r="AJ57">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="AK57">
-        <v>3</v>
+        <v>7.5</v>
       </c>
       <c r="AL57">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="AM57">
+        <v>2</v>
+      </c>
+      <c r="AN57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oak</t>
+        </is>
+      </c>
+      <c r="AO57">
+        <v>1</v>
+      </c>
+      <c r="AP57">
+        <v>750</v>
+      </c>
+      <c r="AQ57">
         <v>5</v>
       </c>
-      <c r="AN57">
-        <v>2</v>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Oak</t>
-        </is>
-      </c>
-      <c r="AP57">
-        <v>1</v>
-      </c>
-      <c r="AQ57">
-        <v>750</v>
-      </c>
       <c r="AR57">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AS57">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="AT57">
-        <v>38</v>
-      </c>
-      <c r="AU57">
         <v>104</v>
       </c>
     </row>

--- a/data/ships.xlsx
+++ b/data/ships.xlsx
@@ -582,1377 +582,1419 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">            A fourth figure is the fewest sails a mast stepped there must carry: "fore/large/square/2"</t>
+          <t xml:space="preserve">            A fourth figure is how many sails a mast stepped there carries, counting every sail it</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">            takes a topmast or taller and never a bare lower mast. Size alone cannot say it, since</t>
+          <t xml:space="preserve">            can set: a square mast's square sails, a spanker mast's spanker and the square sails</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t xml:space="preserve">            a lower mast and a topmast are both medium. Leave it off and any mast that fits goes in.</t>
+          <t xml:space="preserve">            over it, a spar's headsails. "2" is two or more, so "fore/large/square/2" takes a</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowsprit    yes or no. Whether she carries the spar at all.</t>
+          <t xml:space="preserve">            topmast or taller and never a bare lower mast; "2-3" is two to three, so</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">blurb       one line a captain reads. May be left empty.</t>
+          <t xml:space="preserve">            "fore/large/square/2-3" takes a topmast or a topgallant mast and never a royal mast.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Size alone cannot say either, since a lower mast and a topmast are both medium and a</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">A BLANK IN speed, hand, canvas OR tons IS NOT A DERIVATION. Each falls back to 1, which describes</t>
+          <t xml:space="preserve">            topgallant mast and a royal mast both large. The most is at most 5, all the renderer</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">a quick, handy, easily driven ship that can carry nothing, and is right for no class above a boat.</t>
+          <t xml:space="preserve">            draws up one mast, and has to be a mast her size and family can actually carry, which</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fill them in. Every other gameplay column has to be filled as well.</t>
+          <t xml:space="preserve">            the bench checks. Leave the figure off and any mast that fits goes in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bowsprit    yes or no. Whether she carries the spar at all.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">THE REFERENCE COLUMNS. Everything from `era` rightward is what the class WAS rather than what she</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">does in a fight: no fight reads any of it, `npm run import` writes it to src/shipref.js, and</t>
+          <t xml:space="preserve">blurb       one line a captain reads. May be left empty.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">`hullform.js` is the one reader. The fourteen marked (drawn) are how she is DRAWN, in the menu</t>
+          <t xml:space="preserve">A BLANK IN speed, hand, canvas OR tons IS NOT A DERIVATION. Each falls back to 1, which describes</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">model and at sea. The rest are recorded for whoever comes to refine her form and are read by</t>
+          <t xml:space="preserve">a quick, handy, easily driven ship that can carry nothing, and is right for no class above a boat.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">nothing yet, which is not the same as being free to invent: a wrong figure here is a wrong hull</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the day somebody does read it.</t>
+          <t xml:space="preserve">Fill them in. Every other gameplay column has to be filled as well.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THE REFERENCE COLUMNS. Everything from `era` rightward is what the class WAS rather than what she</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lengths are feet and weights are tons. bowFine, tumblehome, deadrise, sheer and castle are 1 to 5</t>
+          <t xml:space="preserve">does in a fight: no fight reads any of it, `npm run import` writes it to src/shipref.js, and</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">judgement scores, 1 for least and 5 for most.</t>
+          <t xml:space="preserve">`hullform.js` is the one reader. The fourteen marked (drawn) are how she is DRAWN, in the menu</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">model and at sea. The rest are recorded for whoever comes to refine her form and are read by</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve">era         the years she was in service, written as a range. Text rather than a number.</t>
+          <t xml:space="preserve">nothing yet, which is not the same as being free to invent: a wrong figure here is a wrong hull</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">region      where she was built and sailed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">role        what she was for.</t>
+          <t xml:space="preserve">the day somebody does read it.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">lod         (drawn) length on deck, feet. With beam, how big she is drawn in both views. Sizes are</t>
+          <t xml:space="preserve">Lengths are feet and weights are tons. bowFine, tumblehome, deadrise, sheer and castle are 1 to 5</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">            compressed around the galleon, so twice the length is not twice the ship on screen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lbp         length between perpendiculars, feet. The measured length, shorter than on deck.</t>
+          <t xml:space="preserve">judgement scores, 1 for least and 5 for most.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">beam        (drawn) extreme breadth, feet. Her drawn width, and with her length her collision</t>
+          <t xml:space="preserve">era         the years she was in service, written as a range. Text rather than a number.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">            ellipse in a fight.</t>
+          <t xml:space="preserve">region      where she was built and sailed.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">depth       depth of hold, feet: keelson to the deck above it.</t>
+          <t xml:space="preserve">role        what she was for.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">freeboard   (drawn) height of side above the water amidships, feet. The depth of side in the model.</t>
+          <t xml:space="preserve">lod         (drawn) length on deck, feet. With beam, how big she is drawn in both views. Sizes are</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">lb          length to beam, as a ratio. High is long and lean, low is short and beamy.</t>
+          <t xml:space="preserve">            compressed around the galleon, so twice the length is not twice the ship on screen.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd          beam to depth, as a ratio. High is shallow and beamy, low is deep and narrow.</t>
+          <t xml:space="preserve">lbp         length between perpendiculars, feet. The measured length, shorter than on deck.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">burthen     builder's old measurement tons: what she was rated to carry.</t>
+          <t xml:space="preserve">beam        (drawn) extreme breadth, feet. Her drawn width, and with her length her collision</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">disp        displacement, tons: what she actually weighs afloat.</t>
+          <t xml:space="preserve">            ellipse in a fight.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowFine     (drawn) how fine her entry is. 5 is a clipper's bow and 1 a carrack's. It narrows her</t>
+          <t xml:space="preserve">depth       depth of hold, feet: keelson to the deck above it.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">            bow and pulls her shoulders aft.</t>
+          <t xml:space="preserve">freeboard   (drawn) height of side above the water amidships, feet. The depth of side in the model.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">tumblehome  (drawn) how far her sides roll inward above the waterline. 5 is a fluyt.</t>
+          <t xml:space="preserve">lb          length to beam, as a ratio. High is long and lean, low is short and beamy.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">deadrise    how sharply her bottom rises from the keel. 1 is a flat floor.</t>
+          <t xml:space="preserve">bd          beam to depth, as a ratio. High is shallow and beamy, low is deep and narrow.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">sheer       (drawn) how much her deck sweeps up towards bow and stern.</t>
+          <t xml:space="preserve">burthen     builder's old measurement tons: what she was rated to carry.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">castle      (drawn) how built up her ends are. 1 is an open boat, 2 raises a quarterdeck, 3 and up</t>
+          <t xml:space="preserve">disp        displacement, tons: what she actually weighs afloat.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">            add a forecastle. It is also what a windowed stern needs before it shows any lights.</t>
+          <t xml:space="preserve">bowFine     (drawn) how fine her entry is. 5 is a clipper's bow and 1 a carrack's. It narrows her</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">stern       (drawn) the shape of her stern, as one of the named types. Scow, Round, Pear,</t>
+          <t xml:space="preserve">            bow and pulls her shoulders aft.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Elliptical, Raking transom, Overhanging and Square each have geometry of their own,</t>
+          <t xml:space="preserve">tumblehome  (drawn) how far her sides roll inward above the waterline. 5 is a fluyt.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">            and any other name draws a plain transom, which is what Transom and Gallery do. A name</t>
+          <t xml:space="preserve">deadrise    how sharply her bottom rises from the keel. 1 is a flat floor.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">            holding "gallery" or "castle" lights her stern windows if her castle is 3 or more.</t>
+          <t xml:space="preserve">sheer       (drawn) how much her deck sweeps up towards bow and stern.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">mastHeight  (drawn) how tall her rig stands, as a multiple of the galleon's. Scales her masts in</t>
+          <t xml:space="preserve">castle      (drawn) how built up her ends are. 1 is an open boat, 2 raises a quarterdeck, 3 and up</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">            both views.</t>
+          <t xml:space="preserve">            add a forecastle. It is also what a windowed stern needs before it shows any lights.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">decks       how many of her decks carry guns: 1, 1-2, 2, 2-3 or 3. Text, because a range is not a</t>
+          <t xml:space="preserve">stern       (drawn) the shape of her stern, as one of the named types. Scow, Round, Pear,</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">            number. Recorded description now: `battery` says deck by deck where her guns actually</t>
+          <t xml:space="preserve">            Elliptical, Raking transom, Overhanging and Square each have geometry of their own,</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">            stood, and that is what her ports are drawn from.</t>
+          <t xml:space="preserve">            and any other name draws a plain transom, which is what Transom and Gallery do. A name</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">wale        the thickness of her main wale, inches: the heavy belt of timber along her side.</t>
+          <t xml:space="preserve">            holding "gallery" or "castle" lights her stern windows if her castle is 3 or more.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">topside     the thickness of her topside planking, inches.</t>
+          <t xml:space="preserve">mastHeight  (drawn) how tall her rig stands, as a multiple of the galleon's. Scales her masts in</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">roomSpace   (drawn) room and space, feet: from one frame to the next. A gunport was framed on it,</t>
+          <t xml:space="preserve">            both views.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">            running a little over one space wide, so this is the size of every port she shows.</t>
+          <t xml:space="preserve">decks       how many of her decks carry guns: 1, 1-2, 2, 2-3 or 3. Text, because a range is not a</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">species     (drawn) what she was built of, which is also her colour: Oak, Live oak, Teak, Cedar or</t>
+          <t xml:space="preserve">            number. Recorded description now: `battery` says deck by deck where her guns actually</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Pine. Any other name is painted as oak.</t>
+          <t xml:space="preserve">            stood, and that is what her ports are drawn from.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">timber      (drawn) how dense that timber is, oak being 1. Denser timber reads a little darker.</t>
+          <t xml:space="preserve">wale        the thickness of her main wale, inches: the heavy belt of timber along her side.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve">crewMin     the fewest hands she could be worked with, as against the battle complement in `crew`.</t>
+          <t xml:space="preserve">topside     the thickness of her topside planking, inches.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t xml:space="preserve">cruise      her everyday speed, knots.</t>
+          <t xml:space="preserve">roomSpace   (drawn) room and space, feet: from one frame to the next. A gunport was framed on it,</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t xml:space="preserve">topSpeed    the best she was ever driven, knots.</t>
+          <t xml:space="preserve">            running a little over one space wide, so this is the size of every port she shows.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t xml:space="preserve">manoeuvre   how handy she was, 0 to 100. The reference's own score, and what `hand` came out of.</t>
+          <t xml:space="preserve">species     (drawn) what she was built of, which is also her colour: Oak, Live oak, Teak, Cedar or</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t xml:space="preserve">histGuns    (drawn) how many guns she really carried, of every sort. Half of them is exactly her</t>
+          <t xml:space="preserve">            Pine. Any other name is painted as oak.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t xml:space="preserve">            `broadside` bearing for every class in the fleet, which is how the ports and the guns</t>
+          <t xml:space="preserve">timber      (drawn) how dense that timber is, oak being 1. Denser timber reads a little darker.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t xml:space="preserve">            that fire out of them agree without the catalogue and the reference ever meeting.</t>
+          <t xml:space="preserve">crewMin     the fewest hands she could be worked with, as against the battle complement in `crew`.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t xml:space="preserve">            `battery` says where those guns stood and has to add up to this.</t>
+          <t xml:space="preserve">cruise      her everyday speed, knots.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery     (drawn) her establishment, deck by deck, as guns aboard rather than a side. Gun decks</t>
+          <t xml:space="preserve">topSpeed    the best she was ever driven, knots.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t xml:space="preserve">            first and lowest deck first, then what she carried on her upper works after a plus:</t>
+          <t xml:space="preserve">manoeuvre   how handy she was, 0 to 100. The reference's own score, and what `hand` came out of.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t xml:space="preserve">            "10" is a cutter's ten on one open deck, "28+8/2" a frigate with a gun deck of 28 and</t>
+          <t xml:space="preserve">histGuns    (drawn) how many guns she really carried, of every sort. Half of them is exactly her</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t xml:space="preserve">            ten more on her quarterdeck and forecastle, "28/28/28+12/4" a first rate. The figures</t>
+          <t xml:space="preserve">            `broadside` bearing for every class in the fleet, which is how the ports and the guns</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t xml:space="preserve">            sum to histGuns and every gun deck takes an even number, half of them a side.</t>
+          <t xml:space="preserve">            that fire out of them agree without the catalogue and the reference ever meeting.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t xml:space="preserve">            A GUN DECK AND AN UPPER WORKS ARE NOT THE SAME FITTING, which is the whole reason this</t>
+          <t xml:space="preserve">            `battery` says where those guns stood and has to add up to this.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t xml:space="preserve">            column exists. A gun deck is a continuous battery pierced through her side, so its</t>
+          <t xml:space="preserve">battery     (drawn) her establishment, deck by deck, as guns aboard rather than a side. Gun decks</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t xml:space="preserve">            ports run the length of her, under the castles the way a lower deck really did. Her</t>
+          <t xml:space="preserve">            first and lowest deck first, then what she carried on her upper works after a plus:</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t xml:space="preserve">            quarterdeck and forecastle guns stood in the open behind a bulwark, with no lidded</t>
+          <t xml:space="preserve">            "10" is a cutter's ten on one open deck, "28+8/2" a frigate with a gun deck of 28 and</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t xml:space="preserve">            port to show, and drawn as such they are what leaves a two-decker's waist empty.</t>
+          <t xml:space="preserve">            ten more on her quarterdeck and forecastle, "28/28/28+12/4" a first rate. The figures</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t xml:space="preserve">            After the plus, two figures are the quarterdeck and the forecastle in that order, with</t>
+          <t xml:space="preserve">            sum to histGuns and every gun deck takes an even number, half of them a side.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t xml:space="preserve">            her waist bare between them. One figure is a battery that ran the whole length of her</t>
+          <t xml:space="preserve">            A GUN DECK AND AN UPPER WORKS ARE NOT THE SAME FITTING, which is the whole reason this</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t xml:space="preserve">            upper works, which is what a spar-decked heavy frigate had. Write "2/0" rather than</t>
+          <t xml:space="preserve">            column exists. A gun deck is a continuous battery pierced through her side, so its</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t xml:space="preserve">            "2" for a ship who carried hers aft only.</t>
+          <t xml:space="preserve">            ports run the length of her, under the castles the way a lower deck really did. Her</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t xml:space="preserve">            A BOAT IS NOT PIERCED AT ALL. A lidded port is cut through her topside under the deck</t>
+          <t xml:space="preserve">            quarterdeck and forecastle guns stood in the open behind a bulwark, with no lidded</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t xml:space="preserve">            above it, and a hull with a castle score of 1 has neither, so her whole battery is</t>
+          <t xml:space="preserve">            port to show, and drawn as such they are what leaves a two-decker's waist empty.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t xml:space="preserve">            drawn standing at her rail however this column is written.</t>
+          <t xml:space="preserve">            After the plus, two figures are the quarterdeck and the forecastle in that order, with</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t xml:space="preserve">drawnLength (drawn) the length of her BESPOKE 3D model, in metres, stem to stern at the rail, and</t>
+          <t xml:space="preserve">            her waist bare between them. One figure is a battery that ran the whole length of her</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t xml:space="preserve">drawnBeam   (drawn) its extreme beam. Only a class with a model of her own in</t>
+          <t xml:space="preserve">            upper works, which is what a spar-decked heavy frigate had. Write "2/0" rather than</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t xml:space="preserve">            src/render3d/bespoke/ carries them; everybody else leaves both blank and is drawn from</t>
+          <t xml:space="preserve">            "2" for a ship who carried hers aft only.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t xml:space="preserve">            the figures above. Her collision ellipse at sea keeps the length the fleet's</t>
+          <t xml:space="preserve">            A BOAT IS NOT PIERCED AT ALL. A lidded port is cut through her topside under the deck</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t xml:space="preserve">            compression gives her and takes its beam from these two in proportion, so a ball bites</t>
+          <t xml:space="preserve">            above it, and a hull with a castle score of 1 has neither, so her whole battery is</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t xml:space="preserve">            where her planking is drawn and not outside it. The bespoke test holds them to the</t>
+          <t xml:space="preserve">            drawn standing at her rail however this column is written.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t xml:space="preserve">            model's own figures.</t>
+          <t xml:space="preserve">drawnLength (drawn) the length of her BESPOKE 3D model, in metres, stem to stern at the rail, and</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">drawnBeam   (drawn) its extreme beam. Only a class with a model of her own in</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Masts, from data/masts.tsv</t>
+          <t xml:space="preserve">            src/render3d/bespoke/ carries them; everybody else leaves both blank and is drawn from</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            the figures above. Her collision ellipse at sea keeps the length the fleet's</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t xml:space="preserve">THE MASTS. One row per type, and a type is a SHAPE OF RIG, not a size.</t>
+          <t xml:space="preserve">            compression gives her and takes its beam from these two in proportion, so a ball bites</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edit here, then: npm run import &amp;&amp; npm run catalogue</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A mast's berths are fixed the moment it is built and never change. That is the whole point of the</t>
+          <t xml:space="preserve">            where her planking is drawn and not outside it. The bespoke test holds them to the</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            model's own figures.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t xml:space="preserve">part: buying a mast is choosing what she will be able to carry, so a mast with one lugsail berth</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t xml:space="preserve">will never carry two square ones however much a captain spends. It is why the fleet wants a type</t>
+          <t xml:space="preserve">Masts, from data/masts.tsv</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t xml:space="preserve">per configuration rather than one mast with a number of slots.</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A TYPE IS NOT TIED TO A STATION. A mast that carries three square sails is that mast wherever she</t>
+          <t xml:space="preserve">THE MASTS. One row per type, and a type is a SHAPE OF RIG, not a size.</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Edit here, then: npm run import &amp;&amp; npm run catalogue</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t xml:space="preserve">steps it, so the fore and main of a brig are one part bought twice rather than two parts. What</t>
+          <t xml:space="preserve">A mast's berths are fixed the moment it is built and never change. That is the whole point of the</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t xml:space="preserve">decides where it can go is the size rung and nothing else.</t>
+          <t xml:space="preserve">part: buying a mast is choosing what she will be able to carry, so a mast with one lugsail berth</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">will never carry two square ones however much a captain spends. It is why the fleet wants a type</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t xml:space="preserve">BERTHS RUN DECK UPWARD, and a fore-and-aft driving sail sharing the lowest level with a course</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t xml:space="preserve">takes berth 0 with the square canvas above it. A spanker and a course are both set at the deck, one</t>
+          <t xml:space="preserve">per configuration rather than one mast with a number of slots.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t xml:space="preserve">abaft the mast and one on a yard across it, and the model has one sail to a band: putting the</t>
+          <t xml:space="preserve">A TYPE IS NOT TIED TO A STATION. A mast that carries three square sails is that mast wherever she</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t xml:space="preserve">spanker lowest is what keeps a brig's rig reading bottom to top the way she is really rigged.</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id       short camelCase name, unique.</t>
+          <t xml:space="preserve">steps it, so the fore and main of a brig are one part bought twice rather than two parts. What</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">decides where it can go is the size rung and nothing else.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t xml:space="preserve">name     what a captain reads.</t>
+          <t xml:space="preserve">BERTHS RUN DECK UPWARD, and a fore-and-aft driving sail sharing the lowest level with a course</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t xml:space="preserve">price    coins.</t>
+          <t xml:space="preserve">takes berth 0 with the square canvas above it. A spanker and a course are both set at the deck, one</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t xml:space="preserve">size     the SMALLEST socket it fits. A mast also fits any larger socket, which is a legal poor</t>
+          <t xml:space="preserve">abaft the mast and one on a yard across it, and the model has one sail to a band: putting the</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t xml:space="preserve">         choice rather than an error: sizes are boat, small, medium, large, heavy.</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t xml:space="preserve">spar     yes for a SPAR rather than a mast: a jibboom or a spritsail yard, which goes on the</t>
+          <t xml:space="preserve">spanker lowest is what keeps a brig's rig reading bottom to top the way she is really rigged.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t xml:space="preserve">         bowsprit and nowhere else. A spar and a mast are different sorts of thing and are</t>
+          <t xml:space="preserve">id       short camelCase name, unique.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t xml:space="preserve">         matched as such, or a jibboom would be legal as somebody's main mast.</t>
+          <t xml:space="preserve">name     what a captain reads.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t xml:space="preserve">family   the shape of rig this mast is, and a hull's socket says which families it takes, so a</t>
+          <t xml:space="preserve">price    coins.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t xml:space="preserve">         lug mast never steps in a frigate and a topgallant mast never steps in a lugger. One</t>
+          <t xml:space="preserve">size     the SMALLEST socket it fits. A mast also fits any larger socket, which is a legal poor</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t xml:space="preserve">         family to a mast, matched before the size rung is consulted:</t>
+          <t xml:space="preserve">         choice rather than an error: sizes are boat, small, medium, large, heavy.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t xml:space="preserve">           square     lower mast up to skysail mast, all square canvas: a ship's fore and main</t>
+          <t xml:space="preserve">spar     yes for a SPAR rather than a mast: a jibboom or a spritsail yard, which goes on the</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t xml:space="preserve">           spanker    a fore-and-aft driver under square canvas: a ship's mizzen, a cutter's main</t>
+          <t xml:space="preserve">         bowsprit and nowhere else. A spar and a mast are different sorts of thing and are</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t xml:space="preserve">           schooner   gaff sail with a square topsail over it</t>
+          <t xml:space="preserve">         matched as such, or a jibboom would be legal as somebody's main mast.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t xml:space="preserve">           gaff       gaff mainsail and gaff topsail</t>
+          <t xml:space="preserve">family   the shape of rig this mast is, and a hull's socket says which families it takes, so a</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t xml:space="preserve">           bermuda    one tall triangle</t>
+          <t xml:space="preserve">         lug mast never steps in a frigate and a topgallant mast never steps in a lugger. One</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t xml:space="preserve">           lateen     the lateen yard and the lateen mast</t>
+          <t xml:space="preserve">         family to a mast, matched before the size rung is consulted:</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t xml:space="preserve">           lug        lug mast and lug topmast</t>
+          <t xml:space="preserve">           square     lower mast up to skysail mast, all square canvas: a ship's fore and main</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t xml:space="preserve">           boat       pole and sprit masts, what an open boat steps</t>
+          <t xml:space="preserve">           spanker    a fore-and-aft driver under square canvas: a ship's mizzen, a cutter's main</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t xml:space="preserve">           headsails  the bowsprit spars that carry jibs and staysails</t>
+          <t xml:space="preserve">           schooner   gaff sail with a square topsail over it</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t xml:space="preserve">           spritsail  the old headgear slung under the bowsprit, a carrack's and a galleon's</t>
+          <t xml:space="preserve">           gaff       gaff mainsail and gaff topsail</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t xml:space="preserve">         Studdingsails boom out from square and schooner rig only; the other families never</t>
+          <t xml:space="preserve">           bermuda    one tall triangle</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t xml:space="preserve">         carried the booms for them.</t>
+          <t xml:space="preserve">           lateen     the lateen yard and the lateen mast</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t xml:space="preserve">height   how tall she stands as a share of a full mast at her station, 0 to 1. The renderer cuts</t>
+          <t xml:space="preserve">           lug        lug mast and lug topmast</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t xml:space="preserve">         the pole down to the canvas actually bent on it, so this is an upper bound, not a look.</t>
+          <t xml:space="preserve">           boat       pole and sprit masts, what an open boat steps</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t xml:space="preserve">berths   the sails she can carry, DECK UPWARD, as category labels separated by spaces.</t>
+          <t xml:space="preserve">           headsails  the bowsprit spars that carry jibs and staysails</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t xml:space="preserve">         LSQ large square   SSQ small square   TRI headsail   LAT lateen   GAF gaff   LUG lugsail</t>
+          <t xml:space="preserve">           spritsail  the old headgear slung under the bowsprit, a carrack's and a galleon's</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t xml:space="preserve">         Five is the most the renderer can place up one mast in bands of their own, and the bench</t>
+          <t xml:space="preserve">         Studdingsails boom out from square and schooner rig only; the other families never</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t xml:space="preserve">         fails a mast that asks for more.</t>
+          <t xml:space="preserve">         carried the booms for them.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t xml:space="preserve">         STU is a studdingsail and is NOT a berth. It booms out beyond a square sail already set,</t>
+          <t xml:space="preserve">height   how tall she stands as a share of a full mast at her station, 0 to 1. The renderer cuts</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t xml:space="preserve">         so it attaches to a sail rather than filling a place in the rig, and the bench refuses it.</t>
+          <t xml:space="preserve">         the pole down to the canvas actually bent on it, so this is an upper bound, not a look.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t xml:space="preserve">blurb    one line a captain reads.</t>
+          <t xml:space="preserve">berths   the sails she can carry, DECK UPWARD, as category labels separated by spaces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">         LSQ large square   SSQ small square   TRI headsail   LAT lateen   GAF gaff   LUG lugsail</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sails, from data/sails.tsv</t>
+          <t xml:space="preserve">         Five is the most the renderer can place up one mast in bands of their own, and the bench</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">         fails a mast that asks for more.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t xml:space="preserve">THE SAILS. One row per sail a captain can buy.</t>
+          <t xml:space="preserve">         STU is a studdingsail and is NOT a berth. It booms out beyond a square sail already set,</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edit here, then: npm run import &amp;&amp; npm run catalogue</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A sail belongs to ONE category and fits a berth of that category. That is the whole fitting rule.</t>
+          <t xml:space="preserve">         so it attaches to a sail rather than filling a place in the rig, and the bench refuses it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blurb    one line a captain reads.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Area is not the category: a topgallant is nearly four times a skysail and both are SSQ.</t>
+          <t xml:space="preserve">Sails, from data/sails.tsv</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t xml:space="preserve">  LSQ  Large square    courses, lower topsails            driving power, low on the mast</t>
+          <t xml:space="preserve">THE SAILS. One row per sail a captain can buy.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t xml:space="preserve">  SSQ  Small square    topgallants, royals, skysails,     light-air lift, high up</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                       spritsails, sprit-topsails</t>
+          <t xml:space="preserve">Edit here, then: npm run import &amp;&amp; npm run catalogue</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TRI  Headsail        jibs, flying jibs, staysails       set on a stay forward: balance, pointing</t>
+          <t xml:space="preserve">A sail belongs to ONE category and fits a berth of that category. That is the whole fitting rule.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t xml:space="preserve">  LAT  Lateen          lateen yards, Bermuda mainsails    triangular canvas driving from a mast</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  GAF  Gaff            gaff mainsails, spankers,          fore-and-aft drive aft, manoeuvre</t>
+          <t xml:space="preserve">Area is not the category: a topgallant is nearly four times a skysail and both are SSQ.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t xml:space="preserve">                       drivers, trysails, gaff topsails</t>
+          <t xml:space="preserve">  LSQ  Large square    courses, lower topsails            driving power, low on the mast</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t xml:space="preserve">  LUG  Lugsail         dipping and standing lug,          the main drive of a lugger</t>
+          <t xml:space="preserve">  SSQ  Small square    topgallants, royals, skysails,     light-air lift, high up</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t xml:space="preserve">                       lug topsail</t>
+          <t xml:space="preserve">                       spritsails, sprit-topsails</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STU  Studdingsail    boomed-out extensions             ADDITIVE. Not a berth: see below.</t>
+          <t xml:space="preserve">  TRI  Headsail        jibs, flying jibs, staysails       set on a stay forward: balance, pointing</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  LAT  Lateen          lateen yards, Bermuda mainsails    triangular canvas driving from a mast</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t xml:space="preserve">A LATEEN IS NOT A HEADSAIL. Both are triangles and they were one category until the bowsprit became</t>
+          <t xml:space="preserve">  GAF  Gaff            gaff mainsails, spankers,          fore-and-aft drive aft, manoeuvre</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t xml:space="preserve">a station: the moment a jib had a berth of its own a lateen fitted it and pulled better, so the</t>
+          <t xml:space="preserve">                       drivers, trysails, gaff topsails</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t xml:space="preserve">choice made itself. They do different work, so they are different categories.</t>
+          <t xml:space="preserve">  LUG  Lugsail         dipping and standing lug,          the main drive of a lugger</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                       lug topsail</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t xml:space="preserve">STU does not go in a berth. A studdingsail booms out beyond a square sail that is already set and</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t xml:space="preserve">its area comes off that sail, so it is an attachment rather than a place in the rig: a square sail</t>
+          <t xml:space="preserve">  STU  Studdingsail    boomed-out extensions             ADDITIVE. Not a berth: see below.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t xml:space="preserve">carries at most one, matched by LEVEL, and `npm run catalogue` still refuses a berth that asks for</t>
+          <t xml:space="preserve">A LATEEN IS NOT A HEADSAIL. Both are triangles and they were one category until the bowsprit became</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t xml:space="preserve">one, deliberately, so that a mast cannot pretend to carry studdingsails in a slot.</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id      short camelCase name, unique.</t>
+          <t xml:space="preserve">a station: the moment a jib had a berth of its own a lateen fitted it and pulled better, so the</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">choice made itself. They do different work, so they are different categories.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t xml:space="preserve">name    what a captain reads.</t>
+          <t xml:space="preserve">STU does not go in a berth. A studdingsail booms out beyond a square sail that is already set and</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t xml:space="preserve">kind    one of the seven labels above.</t>
+          <t xml:space="preserve">its area comes off that sail, so it is an attachment rather than a place in the rig: a square sail</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t xml:space="preserve">price   coins.</t>
+          <t xml:space="preserve">carries at most one, matched by LEVEL, and `npm run catalogue` still refuses a berth that asks for</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t xml:space="preserve">drive   what she pulls, as a share of a course's, which is why a course is exactly 1. Physical area</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        is where this number starts and the proportions are: course 1.00, lower topsail 0.70,</t>
+          <t xml:space="preserve">one, deliberately, so that a mast cannot pretend to carry studdingsails in a slot.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t xml:space="preserve">        topgallant 0.40, royal 0.22, skysail 0.12. Better cloth holds its shape and adds to it,</t>
+          <t xml:space="preserve">id      short camelCase name, unique.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t xml:space="preserve">        which is why two sails of one area can differ here.</t>
+          <t xml:space="preserve">name    what a captain reads.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t xml:space="preserve">        FOR A STUDDINGSAIL ONLY, drive is a share of the sail it booms out from (0.50 to 0.80),</t>
+          <t xml:space="preserve">kind    one of the seven labels above.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t xml:space="preserve">        because its area comes off that sail rather than off a place in the rig.</t>
+          <t xml:space="preserve">price   coins.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t xml:space="preserve">hand    what it does to her helm. Square canvas stiffens her, so it is negative; fore-and-aft</t>
+          <t xml:space="preserve">drive   what she pulls, as a share of a course's, which is why a course is exactly 1. Physical area</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t xml:space="preserve">        canvas helps her round, so it is positive.</t>
+          <t xml:space="preserve">        is where this number starts and the proportions are: course 1.00, lower topsail 0.70,</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t xml:space="preserve">level   STU only, and blank everywhere else. Which square sail up the mast it booms out from,</t>
+          <t xml:space="preserve">        topgallant 0.40, royal 0.22, skysail 0.12. Better cloth holds its shape and adds to it,</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t xml:space="preserve">        counting square canvas from the deck: 0 is the lowest, a course; 1 the topsail over it;</t>
+          <t xml:space="preserve">        which is why two sails of one area can differ here.</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t xml:space="preserve">        2 the topgallant. The berth number is not the level, because a driver mast's course sits</t>
+          <t xml:space="preserve">        FOR A STUDDINGSAIL ONLY, drive is a share of the sail it booms out from (0.50 to 0.80),</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t xml:space="preserve">        at berth 1 with a spanker under it.</t>
+          <t xml:space="preserve">        because its area comes off that sail rather than off a place in the rig.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t xml:space="preserve">blurb   one line a captain reads.</t>
+          <t xml:space="preserve">hand    what it does to her helm. Square canvas stiffens her, so it is negative; fore-and-aft</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        canvas helps her round, so it is positive.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t xml:space="preserve">Two grades of most of them: the plain one a captain can afford early, and a fine one in heavier</t>
+          <t xml:space="preserve">level   STU only, and blank everywhere else. Which square sail up the mast it booms out from,</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t xml:space="preserve">cloth that is strictly better and priced for it. Prices are placed against each other and have not</t>
+          <t xml:space="preserve">        counting square canvas from the deck: 0 is the lowest, a course; 1 the topsail over it;</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t xml:space="preserve">been tuned against what a voyage actually pays.</t>
+          <t xml:space="preserve">        2 the topgallant. The berth number is not the level, because a driver mast's course sits</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        at berth 1 with a spanker under it.</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guns, from data/guns.tsv</t>
+          <t xml:space="preserve">blurb   one line a captain reads.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t xml:space="preserve">THE GUNS. One row per piece a captain can buy.</t>
+          <t xml:space="preserve">Two grades of most of them: the plain one a captain can afford early, and a fine one in heavier</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edit here, then: npm run import &amp;&amp; npm run catalogue</t>
-        </is>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Guns fit BY THE PIECE up to what the hull bears, and `mount` says which of her counts a gun draws</t>
+          <t xml:space="preserve">cloth that is strictly better and priced for it. Prices are placed against each other and have not</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">been tuned against what a voyage actually pays.</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t xml:space="preserve">against. Broadside is counted A SIDE and mirrored, because that is how a volley fires: one</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t xml:space="preserve">carriage gun bought is one gun each side and two guns aboard.</t>
+          <t xml:space="preserve">Guns, from data/guns.tsv</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THE GUNS. One row per piece a captain can buy.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t xml:space="preserve">Muskets are not in this table and never will be. Small arms come off the crew she musters, with the</t>
-        </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t xml:space="preserve">swivels on her rail firing in the same volley, which is `rate()`'s business.</t>
+          <t xml:space="preserve">Edit here, then: npm run import &amp;&amp; npm run catalogue</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Guns fit BY THE PIECE up to what the hull bears, and `mount` says which of her counts a gun draws</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t xml:space="preserve">id      short camelCase name, unique.</t>
+          <t xml:space="preserve">against. Broadside is counted A SIDE and mirrored, because that is how a volley fires: one</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t xml:space="preserve">name    what a captain reads. A GUN IS NAMED BY THE WEIGHT OF HER BALL, IN NUMERALS: `32-pounder`,</t>
-        </is>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        not `Thirty two pounder`. A captain reads this list to compare ten pieces, and comparing</t>
+          <t xml:space="preserve">carriage gun bought is one gun each side and two guns aboard.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t xml:space="preserve">        them is arithmetic she should not have to do in words. It is the game's own rule about</t>
+          <t xml:space="preserve">Muskets are not in this table and never will be. Small arms come off the crew she musters, with the</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t xml:space="preserve">        numerals, and a shelf of guns is where the cost of breaking it shows worst.</t>
-        </is>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mount   broadside, bow or swivel.</t>
+          <t xml:space="preserve">swivels on her rail firing in the same volley, which is `rate()`'s business.</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t xml:space="preserve">price   coins.</t>
+          <t xml:space="preserve">id      short camelCase name, unique.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t xml:space="preserve">damage  what one ball takes off a hull.</t>
+          <t xml:space="preserve">name    what a captain reads. A GUN IS NAMED BY THE WEIGHT OF HER BALL, IN NUMERALS: `32-pounder`,</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t xml:space="preserve">reload  seconds between rounds. A mixed battery serves at the pace of its slowest piece.</t>
+          <t xml:space="preserve">        not `Thirty two pounder`. A captain reads this list to compare ten pieces, and comparing</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t xml:space="preserve">weight  what she carries for it. Enough of it takes the edge off her handling, which is the reason</t>
+          <t xml:space="preserve">        them is arithmetic she should not have to do in words. It is the game's own rule about</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t xml:space="preserve">        to leave a port empty.</t>
+          <t xml:space="preserve">        numerals, and a shelf of guns is where the cost of breaking it shows worst.</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t xml:space="preserve">group   swivels only, and blank everywhere else. How true one throws, as a share of a musket's own</t>
+          <t xml:space="preserve">mount   broadside, bow or swivel.</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t xml:space="preserve">        scatter: 1 is no better than the hands beside it, and smaller is tighter. A better swivel</t>
+          <t xml:space="preserve">price   coins.</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t xml:space="preserve">        never adds a ball to the volley; what quality buys is that the volley hits harder and lands</t>
+          <t xml:space="preserve">damage  what one ball takes off a hull.</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t xml:space="preserve">        closer to where the bow points, and this is the second half of that.</t>
+          <t xml:space="preserve">reload  seconds between rounds. A mixed battery serves at the pace of its slowest piece.</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weight  what she carries for it. Enough of it takes the edge off her handling, which is the reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        to leave a port empty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t xml:space="preserve">group   swivels only, and blank everywhere else. How true one throws, as a share of a musket's own</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        scatter: 1 is no better than the hands beside it, and smaller is tighter. A better swivel</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        never adds a ball to the volley; what quality buys is that the volley hits harder and lands</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        closer to where the bow points, and this is the second half of that.</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
         <is>
           <t xml:space="preserve">blurb   one line a captain reads.</t>
         </is>
@@ -2297,7 +2339,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">where she can step one, "station/size/family", space separated, bow aft. stations: bowsprit fore main mizzen bonaventure sizes:    boat small medium large heavy families: the shapes of rig the socket takes, joined with a plus: "main/medium/gaff+spanker". A mast carries one family in masts.tsv and only a mast of one of these goes in, so a frigate's fore takes square rig and nothing else however small the mast. families: square spanker schooner gaff bermuda lateen lug boat headsails spritsail The bowsprit takes a SPAR rather than a mast, which is what her headsails hang on. A socket that names no family takes any mast of its size, which is how the laid-up rows stand; the bench asks every class that sails to say what she takes. A fourth figure is the fewest sails a mast stepped there must carry: "fore/large/square/2" takes a topmast or taller and never a bare lower mast. Size alone cannot say it, since a lower mast and a topmast are both medium. Leave it off and any mast that fits goes in.</t>
+          <t xml:space="preserve">where she can step one, "station/size/family", space separated, bow aft. stations: bowsprit fore main mizzen bonaventure sizes:    boat small medium large heavy families: the shapes of rig the socket takes, joined with a plus: "main/medium/gaff+spanker". A mast carries one family in masts.tsv and only a mast of one of these goes in, so a frigate's fore takes square rig and nothing else however small the mast. families: square spanker schooner gaff bermuda lateen lug boat headsails spritsail The bowsprit takes a SPAR rather than a mast, which is what her headsails hang on. A socket that names no family takes any mast of its size, which is how the laid-up rows stand; the bench asks every class that sails to say what she takes. A fourth figure is how many sails a mast stepped there carries, counting every sail it can set: a square mast's square sails, a spanker mast's spanker and the square sails over it, a spar's headsails. "2" is two or more, so "fore/large/square/2" takes a topmast or taller and never a bare lower mast; "2-3" is two to three, so "fore/large/square/2-3" takes a topmast or a topgallant mast and never a royal mast. Size alone cannot say either, since a lower mast and a topmast are both medium and a topgallant mast and a royal mast both large. The most is at most 5, all the renderer draws up one mast, and has to be a mast her size and family can actually carry, which the bench checks. Leave the figure off and any mast that fits goes in.</t>
         </is>
       </c>
     </row>
@@ -5977,7 +6019,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowsprit/large/headsails fore/heavy/square main/heavy/square mizzen/large/spanker+lateen</t>
+          <t xml:space="preserve">bowsprit/small/headsails/1-2 fore/large/square/2-4 main/large/square/2-4 mizzen/heavy/spanker/1-5</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -6006,13 +6048,13 @@
         </is>
       </c>
       <c r="T14">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="U14">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="V14">
-        <v>42</v>
+        <v>40.5</v>
       </c>
       <c r="W14">
         <v>17.5</v>
@@ -6021,10 +6063,10 @@
         <v>7.5</v>
       </c>
       <c r="Y14">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="Z14">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="AA14">
         <v>980</v>
@@ -6095,6 +6137,12 @@
           <t xml:space="preserve">24/22+6/2</t>
         </is>
       </c>
+      <c r="AV14">
+        <v>45.29</v>
+      </c>
+      <c r="AW14">
+        <v>12.35</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6144,7 +6192,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowsprit/small/headsails fore/large/square/2 main/large/square/2 mizzen/heavy/spanker</t>
+          <t xml:space="preserve">bowsprit/small/headsails/1-2 fore/large/square/2-4 main/large/square/2-4 mizzen/heavy/spanker/1-5</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -6317,7 +6365,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowsprit/small/headsails fore/large/square/2 main/large/square/2 mizzen/heavy/spanker</t>
+          <t xml:space="preserve">bowsprit/small/headsails/1-2 fore/large/square/2-4 main/large/square/2-4 mizzen/heavy/spanker/1-5</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -6490,7 +6538,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowsprit/small/headsails fore/large/square/2 main/large/square/2 mizzen/heavy/spanker</t>
+          <t xml:space="preserve">bowsprit/small/headsails/1-2 fore/large/square/2-4 main/large/square/2-4 mizzen/heavy/spanker/1-5</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">

--- a/data/ships.xlsx
+++ b/data/ships.xlsx
@@ -5663,10 +5663,10 @@
         <v>260</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>1.015</v>
       </c>
       <c r="H12">
-        <v>0.83</v>
+        <v>0.837</v>
       </c>
       <c r="I12">
         <v>2.83</v>
@@ -5675,7 +5675,7 @@
         <v>96.3</v>
       </c>
       <c r="K12">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L12">
         <v>2</v>
@@ -5685,7 +5685,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowsprit/large/headsails fore/heavy/square main/heavy/square mizzen/large/spanker</t>
+          <t xml:space="preserve">bowsprit/small/headsails/1-2 fore/large/square/2-3 main/large/square/2-3 mizzen/large/spanker/2-4</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5714,13 +5714,13 @@
         </is>
       </c>
       <c r="T12">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="U12">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="V12">
-        <v>39</v>
+        <v>37.5</v>
       </c>
       <c r="W12">
         <v>13</v>
@@ -5729,10 +5729,10 @@
         <v>6.5</v>
       </c>
       <c r="Y12">
-        <v>3.74</v>
+        <v>3.73</v>
       </c>
       <c r="Z12">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AA12">
         <v>860</v>
@@ -5796,12 +5796,18 @@
         <v>59</v>
       </c>
       <c r="AT12">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t xml:space="preserve">28+8/2</t>
-        </is>
+          <t xml:space="preserve">26+12/2</t>
+        </is>
+      </c>
+      <c r="AV12">
+        <v>43.91</v>
+      </c>
+      <c r="AW12">
+        <v>11.44</v>
       </c>
     </row>
     <row r="13">

--- a/data/ships.xlsx
+++ b/data/ships.xlsx
@@ -5334,7 +5334,7 @@
         <v>0.88</v>
       </c>
       <c r="H10">
-        <v>0.89</v>
+        <v>0.905</v>
       </c>
       <c r="I10">
         <v>1.81</v>
@@ -5353,7 +5353,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowsprit/medium/headsails fore/large/square main/large/square mizzen/medium/spanker</t>
+          <t xml:space="preserve">bowsprit/small/headsails/1-2 fore/large/square/2-3 main/large/square/2-3 mizzen/large/spanker/2-4</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -5382,13 +5382,13 @@
         </is>
       </c>
       <c r="T10">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="U10">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="V10">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="W10">
         <v>11</v>
@@ -5397,10 +5397,10 @@
         <v>5.5</v>
       </c>
       <c r="Y10">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="Z10">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="AA10">
         <v>450</v>
@@ -5466,10 +5466,14 @@
       <c r="AT10">
         <v>24</v>
       </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22+2/0</t>
-        </is>
+      <c r="AU10">
+        <v>24</v>
+      </c>
+      <c r="AV10">
+        <v>34.77</v>
+      </c>
+      <c r="AW10">
+        <v>9.46</v>
       </c>
     </row>
     <row r="11">
